--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A66B66C9-EBD6-4F99-8DF6-A2238865C15B}"/>
+  <xr:revisionPtr revIDLastSave="52" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46ECB0C9-0CB7-4A23-B3FE-1C97FF6014FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D513"/>
+  <dimension ref="A1:D541"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -7618,7 +7618,399 @@
         <v>37.018177223205569</v>
       </c>
       <c r="D513" s="4">
-        <v>37.769319115779105</v>
+        <v>37.769225480328458</v>
+      </c>
+    </row>
+    <row r="514" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A514" s="1">
+        <v>46103.333333333336</v>
+      </c>
+      <c r="B514" s="4">
+        <v>30.980625073115032</v>
+      </c>
+      <c r="C514" s="4">
+        <v>35.602891677358876</v>
+      </c>
+      <c r="D514" s="4">
+        <v>36.342923255065585</v>
+      </c>
+    </row>
+    <row r="515" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A515" s="1">
+        <v>46103.375</v>
+      </c>
+      <c r="B515" s="4">
+        <v>30.9730080768466</v>
+      </c>
+      <c r="C515" s="4">
+        <v>36.533381838130495</v>
+      </c>
+      <c r="D515" s="4">
+        <v>36.769815096965061</v>
+      </c>
+    </row>
+    <row r="516" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A516" s="1">
+        <v>46103.416666666664</v>
+      </c>
+      <c r="B516" s="4">
+        <v>30.925950362450546</v>
+      </c>
+      <c r="C516" s="4">
+        <v>37.23925489425659</v>
+      </c>
+      <c r="D516" s="4">
+        <v>37.915847982150495</v>
+      </c>
+    </row>
+    <row r="517" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A517" s="1">
+        <v>46103.458333333336</v>
+      </c>
+      <c r="B517" s="4">
+        <v>30.985208325915867</v>
+      </c>
+      <c r="C517" s="4">
+        <v>37.309575038486059</v>
+      </c>
+      <c r="D517" s="4">
+        <v>37.959333754904208</v>
+      </c>
+    </row>
+    <row r="518" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A518" s="1">
+        <v>46103.5</v>
+      </c>
+      <c r="B518" s="4">
+        <v>31.091458082199097</v>
+      </c>
+      <c r="C518" s="4">
+        <v>37.405948057628812</v>
+      </c>
+      <c r="D518" s="4">
+        <v>38.052764762855332</v>
+      </c>
+    </row>
+    <row r="519" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A519" s="1">
+        <v>46103.541666666664</v>
+      </c>
+      <c r="B519" s="4">
+        <v>31.198333348168266</v>
+      </c>
+      <c r="C519" s="4">
+        <v>37.509431736809866</v>
+      </c>
+      <c r="D519" s="4">
+        <v>38.155231277828186</v>
+      </c>
+    </row>
+    <row r="520" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A520" s="1">
+        <v>46103.583333333336</v>
+      </c>
+      <c r="B520" s="4">
+        <v>31.314374897215103</v>
+      </c>
+      <c r="C520" s="4">
+        <v>37.577120129267378</v>
+      </c>
+      <c r="D520" s="4">
+        <v>38.256380958626934</v>
+      </c>
+    </row>
+    <row r="521" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A521" s="1">
+        <v>46103.625</v>
+      </c>
+      <c r="B521" s="4">
+        <v>31.357499493492973</v>
+      </c>
+      <c r="C521" s="4">
+        <v>37.631086929639181</v>
+      </c>
+      <c r="D521" s="4">
+        <v>38.274896205254116</v>
+      </c>
+    </row>
+    <row r="522" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A522" s="1">
+        <v>46103.666666666664</v>
+      </c>
+      <c r="B522" s="4">
+        <v>31.348140736115287</v>
+      </c>
+      <c r="C522" s="4">
+        <v>37.589850672086079</v>
+      </c>
+      <c r="D522" s="4">
+        <v>38.225006679821512</v>
+      </c>
+    </row>
+    <row r="523" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A523" s="1">
+        <v>46103.708333333336</v>
+      </c>
+      <c r="B523" s="4">
+        <v>31.30456746052473</v>
+      </c>
+      <c r="C523" s="4">
+        <v>37.504661553246635</v>
+      </c>
+      <c r="D523" s="4">
+        <v>38.194178113623565</v>
+      </c>
+    </row>
+    <row r="524" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A524" s="1">
+        <v>46103.75</v>
+      </c>
+      <c r="B524" s="4">
+        <v>31.202555850346883</v>
+      </c>
+      <c r="C524" s="4">
+        <v>37.402317626135691</v>
+      </c>
+      <c r="D524" s="4">
+        <v>38.058918387329847</v>
+      </c>
+    </row>
+    <row r="525" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A525" s="1">
+        <v>46103.791666666664</v>
+      </c>
+      <c r="B525" s="4">
+        <v>31.13992218123542</v>
+      </c>
+      <c r="C525" s="4">
+        <v>37.32132549285889</v>
+      </c>
+      <c r="D525" s="4">
+        <v>37.970277479514536</v>
+      </c>
+    </row>
+    <row r="526" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A526" s="1">
+        <v>46103.833333333336</v>
+      </c>
+      <c r="B526" s="4">
+        <v>31.10043977631463</v>
+      </c>
+      <c r="C526" s="4">
+        <v>37.306630166371662</v>
+      </c>
+      <c r="D526" s="4">
+        <v>37.927119835533091</v>
+      </c>
+    </row>
+    <row r="527" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A527" s="1">
+        <v>46103.875</v>
+      </c>
+      <c r="B527" s="4">
+        <v>31.080368762138562</v>
+      </c>
+      <c r="C527" s="4">
+        <v>37.267534862624274</v>
+      </c>
+      <c r="D527" s="4">
+        <v>37.888221510702259</v>
+      </c>
+    </row>
+    <row r="528" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A528" s="1">
+        <v>46103.916666666664</v>
+      </c>
+      <c r="B528" s="4">
+        <v>31.009075716214301</v>
+      </c>
+      <c r="C528" s="4">
+        <v>37.227886290020415</v>
+      </c>
+      <c r="D528" s="4">
+        <v>37.845343177313488</v>
+      </c>
+    </row>
+    <row r="529" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A529" s="1">
+        <v>46103.958333333336</v>
+      </c>
+      <c r="B529" s="4">
+        <v>30.974490969269361</v>
+      </c>
+      <c r="C529" s="4">
+        <v>37.197742901908029</v>
+      </c>
+      <c r="D529" s="4">
+        <v>37.81306525022638</v>
+      </c>
+    </row>
+    <row r="530" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A530" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B530" s="4">
+        <v>30.908540255935101</v>
+      </c>
+      <c r="C530" s="4">
+        <v>37.123103019685459</v>
+      </c>
+      <c r="D530" s="4">
+        <v>37.726397850878406</v>
+      </c>
+    </row>
+    <row r="531" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A531" s="1">
+        <v>46104.041666666664</v>
+      </c>
+      <c r="B531" s="4">
+        <v>30.881274286905924</v>
+      </c>
+      <c r="C531" s="4">
+        <v>37.088016051957098</v>
+      </c>
+      <c r="D531" s="4">
+        <v>37.722773266902522</v>
+      </c>
+    </row>
+    <row r="532" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A532" s="1">
+        <v>46104.083333333336</v>
+      </c>
+      <c r="B532" s="4">
+        <v>30.831666612625121</v>
+      </c>
+      <c r="C532" s="4">
+        <v>37.060442913903131</v>
+      </c>
+      <c r="D532" s="4">
+        <v>37.672139487911657</v>
+      </c>
+    </row>
+    <row r="533" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A533" s="1">
+        <v>46104.125</v>
+      </c>
+      <c r="B533" s="4">
+        <v>30.807187537352245</v>
+      </c>
+      <c r="C533" s="4">
+        <v>37.025075408485201</v>
+      </c>
+      <c r="D533" s="4">
+        <v>37.655270019501735</v>
+      </c>
+    </row>
+    <row r="534" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A534" s="1">
+        <v>46104.166666666664</v>
+      </c>
+      <c r="B534" s="4">
+        <v>30.84222953557968</v>
+      </c>
+      <c r="C534" s="4">
+        <v>37.054689969619112</v>
+      </c>
+      <c r="D534" s="4">
+        <v>37.676037401616249</v>
+      </c>
+    </row>
+    <row r="535" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A535" s="1">
+        <v>46104.208333333336</v>
+      </c>
+      <c r="B535" s="4">
+        <v>30.856352673799563</v>
+      </c>
+      <c r="C535" s="4">
+        <v>37.090416018168135</v>
+      </c>
+      <c r="D535" s="4">
+        <v>37.743606429118529</v>
+      </c>
+    </row>
+    <row r="536" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A536" s="1">
+        <v>46104.25</v>
+      </c>
+      <c r="B536" s="4">
+        <v>30.84443891720894</v>
+      </c>
+      <c r="C536" s="4">
+        <v>37.094010798136395</v>
+      </c>
+      <c r="D536" s="4">
+        <v>37.771132406467586</v>
+      </c>
+    </row>
+    <row r="537" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A537" s="1">
+        <v>46104.291666666664</v>
+      </c>
+      <c r="B537" s="4">
+        <v>30.857083129882813</v>
+      </c>
+      <c r="C537" s="4">
+        <v>37.184166463216144</v>
+      </c>
+      <c r="D537" s="4">
+        <v>37.810463574119936</v>
+      </c>
+    </row>
+    <row r="538" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A538" s="1">
+        <v>46104.333333333336</v>
+      </c>
+      <c r="B538" s="4">
+        <v>30.883332522710166</v>
+      </c>
+      <c r="C538" s="4">
+        <v>37.211562220255537</v>
+      </c>
+      <c r="D538" s="4">
+        <v>37.831025308895605</v>
+      </c>
+    </row>
+    <row r="539" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A539" s="1">
+        <v>46104.375</v>
+      </c>
+      <c r="B539" s="4">
+        <v>30.911502268648984</v>
+      </c>
+      <c r="C539" s="4">
+        <v>37.292968622843425</v>
+      </c>
+      <c r="D539" s="4">
+        <v>38.078037425235472</v>
+      </c>
+    </row>
+    <row r="540" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A540" s="1">
+        <v>46104.416666666664</v>
+      </c>
+      <c r="B540" s="4">
+        <v>30.964748061958115</v>
+      </c>
+      <c r="C540" s="4">
+        <v>37.342333265940347</v>
+      </c>
+      <c r="D540" s="4">
+        <v>37.997664881370682</v>
+      </c>
+    </row>
+    <row r="541" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A541" s="1">
+        <v>46104.458333333336</v>
+      </c>
+      <c r="B541" s="4">
+        <v>30.96808359781901</v>
+      </c>
+      <c r="C541" s="4">
+        <v>37.383740502870999</v>
+      </c>
+      <c r="D541" s="4">
+        <v>38.049857595893641</v>
       </c>
     </row>
   </sheetData>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46ECB0C9-0CB7-4A23-B3FE-1C97FF6014FE}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F09892-09F7-4D91-91FD-E748C97C6478}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D541"/>
+  <dimension ref="A1:D562"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -8013,6 +8017,300 @@
         <v>38.049857595893641</v>
       </c>
     </row>
+    <row r="542" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A542" s="1">
+        <v>46104.5</v>
+      </c>
+      <c r="B542" s="4">
+        <v>31.008374872207643</v>
+      </c>
+      <c r="C542" s="4">
+        <v>37.416791147248361</v>
+      </c>
+      <c r="D542" s="4">
+        <v>38.140842166570806</v>
+      </c>
+    </row>
+    <row r="543" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A543" s="1">
+        <v>46104.541666666664</v>
+      </c>
+      <c r="B543" s="4">
+        <v>31.159315581548782</v>
+      </c>
+      <c r="C543" s="4">
+        <v>37.519253624810112</v>
+      </c>
+      <c r="D543" s="4">
+        <v>38.183989349125817</v>
+      </c>
+    </row>
+    <row r="544" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A544" s="1">
+        <v>46104.583333333336</v>
+      </c>
+      <c r="B544" s="4">
+        <v>31.222142764500209</v>
+      </c>
+      <c r="C544" s="4">
+        <v>37.557764048528185</v>
+      </c>
+      <c r="D544" s="4">
+        <v>38.200948869391127</v>
+      </c>
+    </row>
+    <row r="545" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A545" s="1">
+        <v>46104.625</v>
+      </c>
+      <c r="B545" s="4">
+        <v>31.299012493741685</v>
+      </c>
+      <c r="C545" s="4">
+        <v>37.607510770739935</v>
+      </c>
+      <c r="D545" s="4">
+        <v>38.174337682886282</v>
+      </c>
+    </row>
+    <row r="546" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A546" s="1">
+        <v>46104.666666666664</v>
+      </c>
+      <c r="B546" s="4">
+        <v>31.334112445858942</v>
+      </c>
+      <c r="C546" s="4">
+        <v>37.614639596939085</v>
+      </c>
+      <c r="D546" s="4">
+        <v>38.248116117963256</v>
+      </c>
+    </row>
+    <row r="547" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A547" s="1">
+        <v>46104.708333333336</v>
+      </c>
+      <c r="B547" s="4">
+        <v>31.340000168482462</v>
+      </c>
+      <c r="C547" s="4">
+        <v>37.609606910634923</v>
+      </c>
+      <c r="D547" s="4">
+        <v>38.244174245407613</v>
+      </c>
+    </row>
+    <row r="548" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A548" s="1">
+        <v>46104.75</v>
+      </c>
+      <c r="B548" s="4">
+        <v>31.288674798276688</v>
+      </c>
+      <c r="C548" s="4">
+        <v>37.52935637689199</v>
+      </c>
+      <c r="D548" s="4">
+        <v>38.176679448456568</v>
+      </c>
+    </row>
+    <row r="549" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A549" s="1">
+        <v>46104.791666666664</v>
+      </c>
+      <c r="B549" s="4">
+        <v>31.223617300722335</v>
+      </c>
+      <c r="C549" s="4">
+        <v>37.479274888015823</v>
+      </c>
+      <c r="D549" s="4">
+        <v>38.076258871632788</v>
+      </c>
+    </row>
+    <row r="550" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A550" s="1">
+        <v>46104.833333333336</v>
+      </c>
+      <c r="B550" s="4">
+        <v>31.183333460489909</v>
+      </c>
+      <c r="C550" s="4">
+        <v>37.41019999520821</v>
+      </c>
+      <c r="D550" s="4">
+        <v>38.031670339291701</v>
+      </c>
+    </row>
+    <row r="551" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A551" s="1">
+        <v>46104.875</v>
+      </c>
+      <c r="B551" s="4">
+        <v>31.152029556092764</v>
+      </c>
+      <c r="C551" s="4">
+        <v>37.367190847926672</v>
+      </c>
+      <c r="D551" s="4">
+        <v>38.007317744096753</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A552" s="1">
+        <v>46104.916666666664</v>
+      </c>
+      <c r="B552" s="4">
+        <v>31.116595366341723</v>
+      </c>
+      <c r="C552" s="4">
+        <v>37.327139600118002</v>
+      </c>
+      <c r="D552" s="4">
+        <v>37.950616952393403</v>
+      </c>
+    </row>
+    <row r="553" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A553" s="1">
+        <v>46104.958333333336</v>
+      </c>
+      <c r="B553" s="4">
+        <v>31.05741666475932</v>
+      </c>
+      <c r="C553" s="4">
+        <v>37.275763543446857</v>
+      </c>
+      <c r="D553" s="4">
+        <v>37.888986549100927</v>
+      </c>
+    </row>
+    <row r="554" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A554" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B554" s="4">
+        <v>30.970416975021362</v>
+      </c>
+      <c r="C554" s="4">
+        <v>37.162096230189007</v>
+      </c>
+      <c r="D554" s="4">
+        <v>37.812905456510521</v>
+      </c>
+    </row>
+    <row r="555" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A555" s="1">
+        <v>46105.041666666664</v>
+      </c>
+      <c r="B555" s="4">
+        <v>30.957166814804076</v>
+      </c>
+      <c r="C555" s="4">
+        <v>37.174440129597983</v>
+      </c>
+      <c r="D555" s="4">
+        <v>37.80478222861128</v>
+      </c>
+    </row>
+    <row r="556" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A556" s="1">
+        <v>46105.083333333336</v>
+      </c>
+      <c r="B556" s="4">
+        <v>30.947458289464315</v>
+      </c>
+      <c r="C556" s="4">
+        <v>37.164886914359201</v>
+      </c>
+      <c r="D556" s="4">
+        <v>37.778432314678199</v>
+      </c>
+    </row>
+    <row r="557" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A557" s="1">
+        <v>46105.125</v>
+      </c>
+      <c r="B557" s="4">
+        <v>30.924958540598553</v>
+      </c>
+      <c r="C557" s="4">
+        <v>37.144617610507538</v>
+      </c>
+      <c r="D557" s="4">
+        <v>37.748105150664941</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A558" s="1">
+        <v>46105.166666666664</v>
+      </c>
+      <c r="B558" s="4">
+        <v>30.941319296095106</v>
+      </c>
+      <c r="C558" s="4">
+        <v>37.144836080641973</v>
+      </c>
+      <c r="D558" s="4">
+        <v>37.752173917265004</v>
+      </c>
+    </row>
+    <row r="559" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A559" s="1">
+        <v>46105.208333333336</v>
+      </c>
+      <c r="B559" s="4">
+        <v>30.92513894504971</v>
+      </c>
+      <c r="C559" s="4">
+        <v>37.131048579443068</v>
+      </c>
+      <c r="D559" s="4">
+        <v>37.739490894909729</v>
+      </c>
+    </row>
+    <row r="560" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A560" s="1">
+        <v>46105.25</v>
+      </c>
+      <c r="B560" s="4">
+        <v>30.920119206110638</v>
+      </c>
+      <c r="C560" s="4">
+        <v>37.164218044281007</v>
+      </c>
+      <c r="D560" s="4">
+        <v>37.741399269699478</v>
+      </c>
+    </row>
+    <row r="561" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A561" s="1">
+        <v>46105.291666666664</v>
+      </c>
+      <c r="B561" s="4">
+        <v>30.903839206695558</v>
+      </c>
+      <c r="C561" s="4">
+        <v>37.210104115804036</v>
+      </c>
+      <c r="D561" s="4">
+        <v>37.782552783536246</v>
+      </c>
+    </row>
+    <row r="562" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A562" s="1">
+        <v>46105.333333333336</v>
+      </c>
+      <c r="B562" s="4">
+        <v>30.937917041778565</v>
+      </c>
+      <c r="C562" s="4">
+        <v>37.211175500778928</v>
+      </c>
+      <c r="D562" s="4">
+        <v>37.83523475476261</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57F09892-09F7-4D91-91FD-E748C97C6478}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4DB0965-97CD-4C89-B734-7439EB9B82FC}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D562"/>
+  <dimension ref="A1:D585"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -8311,6 +8311,328 @@
         <v>37.83523475476261</v>
       </c>
     </row>
+    <row r="563" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A563" s="1">
+        <v>46105.375</v>
+      </c>
+      <c r="B563" s="4">
+        <v>30.919479316473009</v>
+      </c>
+      <c r="C563" s="4">
+        <v>37.253199607304161</v>
+      </c>
+      <c r="D563" s="4">
+        <v>37.893268431242937</v>
+      </c>
+    </row>
+    <row r="564" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A564" s="1">
+        <v>46105.416666666664</v>
+      </c>
+      <c r="B564" s="4">
+        <v>31.010677216450372</v>
+      </c>
+      <c r="C564" s="4">
+        <v>37.384791730244956</v>
+      </c>
+      <c r="D564" s="4">
+        <v>37.990833920700958</v>
+      </c>
+    </row>
+    <row r="565" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A565" s="1">
+        <v>46105.458333333336</v>
+      </c>
+      <c r="B565" s="4">
+        <v>31.116232585906982</v>
+      </c>
+      <c r="C565" s="4">
+        <v>37.506666723887129</v>
+      </c>
+      <c r="D565" s="4">
+        <v>38.126355715958809</v>
+      </c>
+    </row>
+    <row r="566" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A566" s="1">
+        <v>46105.5</v>
+      </c>
+      <c r="B566" s="4">
+        <v>31.229027700424194</v>
+      </c>
+      <c r="C566" s="4">
+        <v>37.614250574356468</v>
+      </c>
+      <c r="D566" s="4">
+        <v>38.25438605902049</v>
+      </c>
+    </row>
+    <row r="567" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A567" s="1">
+        <v>46105.541666666664</v>
+      </c>
+      <c r="B567" s="4">
+        <v>31.397083298365274</v>
+      </c>
+      <c r="C567" s="4">
+        <v>37.786230800702015</v>
+      </c>
+      <c r="D567" s="4">
+        <v>38.433467089563493</v>
+      </c>
+    </row>
+    <row r="568" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A568" s="1">
+        <v>46105.583333333336</v>
+      </c>
+      <c r="B568" s="4">
+        <v>31.495776404756487</v>
+      </c>
+      <c r="C568" s="4">
+        <v>37.864101640383403</v>
+      </c>
+      <c r="D568" s="4">
+        <v>38.523838118417999</v>
+      </c>
+    </row>
+    <row r="569" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A569" s="1">
+        <v>46105.625</v>
+      </c>
+      <c r="B569" s="4">
+        <v>31.555464481019538</v>
+      </c>
+      <c r="C569" s="4">
+        <v>37.907648885817757</v>
+      </c>
+      <c r="D569" s="4">
+        <v>38.511787512567309</v>
+      </c>
+    </row>
+    <row r="570" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A570" s="1">
+        <v>46105.666666666664</v>
+      </c>
+      <c r="B570" s="4">
+        <v>31.55646723457005</v>
+      </c>
+      <c r="C570" s="4">
+        <v>37.861048757462278</v>
+      </c>
+      <c r="D570" s="4">
+        <v>38.485560112216547</v>
+      </c>
+    </row>
+    <row r="571" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A571" s="1">
+        <v>46105.708333333336</v>
+      </c>
+      <c r="B571" s="4">
+        <v>31.480114625295002</v>
+      </c>
+      <c r="C571" s="4">
+        <v>37.793131887345091</v>
+      </c>
+      <c r="D571" s="4">
+        <v>38.443252143072492</v>
+      </c>
+    </row>
+    <row r="572" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A572" s="1">
+        <v>46105.75</v>
+      </c>
+      <c r="B572" s="4">
+        <v>31.383427009582519</v>
+      </c>
+      <c r="C572" s="4">
+        <v>37.704731564294725</v>
+      </c>
+      <c r="D572" s="4">
+        <v>38.331907099707493</v>
+      </c>
+    </row>
+    <row r="573" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A573" s="1">
+        <v>46105.791666666664</v>
+      </c>
+      <c r="B573" s="4">
+        <v>31.353325428412511</v>
+      </c>
+      <c r="C573" s="4">
+        <v>37.602093550364174</v>
+      </c>
+      <c r="D573" s="4">
+        <v>38.256055229273656</v>
+      </c>
+    </row>
+    <row r="574" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A574" s="1">
+        <v>46105.833333333336</v>
+      </c>
+      <c r="B574" s="4">
+        <v>31.296806891008973</v>
+      </c>
+      <c r="C574" s="4">
+        <v>37.507193017128188</v>
+      </c>
+      <c r="D574" s="4">
+        <v>38.11796493159045</v>
+      </c>
+    </row>
+    <row r="575" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A575" s="1">
+        <v>46105.875</v>
+      </c>
+      <c r="B575" s="4">
+        <v>31.239034258235584</v>
+      </c>
+      <c r="C575" s="4">
+        <v>37.435296157078859</v>
+      </c>
+      <c r="D575" s="4">
+        <v>38.034860384097669</v>
+      </c>
+    </row>
+    <row r="576" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A576" s="1">
+        <v>46105.916666666664</v>
+      </c>
+      <c r="B576" s="4">
+        <v>31.196111721462675</v>
+      </c>
+      <c r="C576" s="4">
+        <v>37.404354883511857</v>
+      </c>
+      <c r="D576" s="4">
+        <v>37.993153765858246</v>
+      </c>
+    </row>
+    <row r="577" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A577" s="1">
+        <v>46105.958333333336</v>
+      </c>
+      <c r="B577" s="4">
+        <v>31.116909914546543</v>
+      </c>
+      <c r="C577" s="4">
+        <v>37.287552253723149</v>
+      </c>
+      <c r="D577" s="4">
+        <v>37.952344260276028</v>
+      </c>
+    </row>
+    <row r="578" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A578" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B578" s="4">
+        <v>31.042395250002542</v>
+      </c>
+      <c r="C578" s="4">
+        <v>37.197884565989177</v>
+      </c>
+      <c r="D578" s="4">
+        <v>37.868546356839772</v>
+      </c>
+    </row>
+    <row r="579" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A579" s="1">
+        <v>46106.041666666664</v>
+      </c>
+      <c r="B579" s="4">
+        <v>31.006666469573975</v>
+      </c>
+      <c r="C579" s="4">
+        <v>37.17140556971232</v>
+      </c>
+      <c r="D579" s="4">
+        <v>37.815898981244764</v>
+      </c>
+    </row>
+    <row r="580" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A580" s="1">
+        <v>46106.083333333336</v>
+      </c>
+      <c r="B580" s="4">
+        <v>30.961041863759359</v>
+      </c>
+      <c r="C580" s="4">
+        <v>37.118052088419596</v>
+      </c>
+      <c r="D580" s="4">
+        <v>37.755417346488912</v>
+      </c>
+    </row>
+    <row r="581" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A581" s="1">
+        <v>46106.125</v>
+      </c>
+      <c r="B581" s="4">
+        <v>30.924166536331178</v>
+      </c>
+      <c r="C581" s="4">
+        <v>37.087156244913736</v>
+      </c>
+      <c r="D581" s="4">
+        <v>37.748452935276759</v>
+      </c>
+    </row>
+    <row r="582" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A582" s="1">
+        <v>46106.166666666664</v>
+      </c>
+      <c r="B582" s="4">
+        <v>30.905816964614083</v>
+      </c>
+      <c r="C582" s="4">
+        <v>37.050570224580312</v>
+      </c>
+      <c r="D582" s="4">
+        <v>37.715459245517039</v>
+      </c>
+    </row>
+    <row r="583" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A583" s="1">
+        <v>46106.208333333336</v>
+      </c>
+      <c r="B583" s="4">
+        <v>30.91314034828773</v>
+      </c>
+      <c r="C583" s="4">
+        <v>37.061139001392178</v>
+      </c>
+      <c r="D583" s="4">
+        <v>37.722638869260635</v>
+      </c>
+    </row>
+    <row r="584" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A584" s="1">
+        <v>46106.25</v>
+      </c>
+      <c r="B584" s="4">
+        <v>30.888541364669798</v>
+      </c>
+      <c r="C584" s="4">
+        <v>37.061191828607797</v>
+      </c>
+      <c r="D584" s="4">
+        <v>37.706363806239857</v>
+      </c>
+    </row>
+    <row r="585" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A585" s="1">
+        <v>46106.291666666664</v>
+      </c>
+      <c r="B585" s="4">
+        <v>30.875</v>
+      </c>
+      <c r="C585" s="4">
+        <v>37.075727562888041</v>
+      </c>
+      <c r="D585" s="4">
+        <v>37.743735687913841</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="56" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4DB0965-97CD-4C89-B734-7439EB9B82FC}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF2207A0-0D8C-4B4A-9F6C-11729931AC57}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -111,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D585"/>
+  <dimension ref="A1:D591"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -8633,6 +8629,90 @@
         <v>37.743735687913841</v>
       </c>
     </row>
+    <row r="586" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A586" s="1">
+        <v>46106.333333333336</v>
+      </c>
+      <c r="B586" s="4">
+        <v>30.905624437332154</v>
+      </c>
+      <c r="C586" s="4">
+        <v>37.101368704296299</v>
+      </c>
+      <c r="D586" s="4">
+        <v>37.792703912067893</v>
+      </c>
+    </row>
+    <row r="587" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A587" s="1">
+        <v>46106.375</v>
+      </c>
+      <c r="B587" s="4">
+        <v>30.940624856948851</v>
+      </c>
+      <c r="C587" s="4">
+        <v>37.189456571851451</v>
+      </c>
+      <c r="D587" s="4">
+        <v>37.865284857296274</v>
+      </c>
+    </row>
+    <row r="588" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A588" s="1">
+        <v>46106.416666666664</v>
+      </c>
+      <c r="B588" s="4">
+        <v>31.041249910990398</v>
+      </c>
+      <c r="C588" s="4">
+        <v>37.324761853899268</v>
+      </c>
+      <c r="D588" s="4">
+        <v>37.973126670947153</v>
+      </c>
+    </row>
+    <row r="589" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A589" s="1">
+        <v>46106.458333333336</v>
+      </c>
+      <c r="B589" s="4">
+        <v>31.125297898337955</v>
+      </c>
+      <c r="C589" s="4">
+        <v>37.447738499734918</v>
+      </c>
+      <c r="D589" s="4">
+        <v>38.119077792677352</v>
+      </c>
+    </row>
+    <row r="590" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A590" s="1">
+        <v>46106.5</v>
+      </c>
+      <c r="B590" s="4">
+        <v>31.2271607312702</v>
+      </c>
+      <c r="C590" s="4">
+        <v>37.582886067024468</v>
+      </c>
+      <c r="D590" s="4">
+        <v>38.234722046995998</v>
+      </c>
+    </row>
+    <row r="591" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A591" s="1">
+        <v>46106.541666666664</v>
+      </c>
+      <c r="B591" s="4">
+        <v>31.369666431744893</v>
+      </c>
+      <c r="C591" s="4">
+        <v>37.751771241142642</v>
+      </c>
+      <c r="D591" s="4">
+        <v>38.379339759686879</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="58" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF2207A0-0D8C-4B4A-9F6C-11729931AC57}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B79CA267-F21F-4B34-8910-D02BBB080BD9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D591"/>
+  <dimension ref="A1:D612"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -8713,6 +8713,300 @@
         <v>38.379339759686879</v>
       </c>
     </row>
+    <row r="592" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A592" s="1">
+        <v>46106.583333333336</v>
+      </c>
+      <c r="B592" s="4">
+        <v>31.486636649237738</v>
+      </c>
+      <c r="C592" s="4">
+        <v>37.842097562732121</v>
+      </c>
+      <c r="D592" s="4">
+        <v>38.480802478721259</v>
+      </c>
+    </row>
+    <row r="593" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A593" s="1">
+        <v>46106.625</v>
+      </c>
+      <c r="B593" s="4">
+        <v>31.587905054622226</v>
+      </c>
+      <c r="C593" s="4">
+        <v>37.936214702678782</v>
+      </c>
+      <c r="D593" s="4">
+        <v>38.576786824156841</v>
+      </c>
+    </row>
+    <row r="594" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A594" s="1">
+        <v>46106.666666666664</v>
+      </c>
+      <c r="B594" s="4">
+        <v>31.587256900469463</v>
+      </c>
+      <c r="C594" s="4">
+        <v>37.91033363785855</v>
+      </c>
+      <c r="D594" s="4">
+        <v>38.585582657285947</v>
+      </c>
+    </row>
+    <row r="595" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A595" s="1">
+        <v>46106.708333333336</v>
+      </c>
+      <c r="B595" s="4">
+        <v>31.545361842427937</v>
+      </c>
+      <c r="C595" s="4">
+        <v>37.872795338100858</v>
+      </c>
+      <c r="D595" s="4">
+        <v>38.509560911956974</v>
+      </c>
+    </row>
+    <row r="596" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A596" s="1">
+        <v>46106.75</v>
+      </c>
+      <c r="B596" s="4">
+        <v>31.528422500973655</v>
+      </c>
+      <c r="C596" s="4">
+        <v>37.82387168142531</v>
+      </c>
+      <c r="D596" s="4">
+        <v>38.470319326785734</v>
+      </c>
+    </row>
+    <row r="597" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A597" s="1">
+        <v>46106.791666666664</v>
+      </c>
+      <c r="B597" s="4">
+        <v>31.435208257039388</v>
+      </c>
+      <c r="C597" s="4">
+        <v>37.685364675521853</v>
+      </c>
+      <c r="D597" s="4">
+        <v>38.3632354148234</v>
+      </c>
+    </row>
+    <row r="598" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A598" s="1">
+        <v>46106.833333333336</v>
+      </c>
+      <c r="B598" s="4">
+        <v>31.328957891464235</v>
+      </c>
+      <c r="C598" s="4">
+        <v>37.580770082826973</v>
+      </c>
+      <c r="D598" s="4">
+        <v>38.240885972128638</v>
+      </c>
+    </row>
+    <row r="599" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A599" s="1">
+        <v>46106.875</v>
+      </c>
+      <c r="B599" s="4">
+        <v>31.281845721744357</v>
+      </c>
+      <c r="C599" s="4">
+        <v>37.49020719174986</v>
+      </c>
+      <c r="D599" s="4">
+        <v>38.137408696656628</v>
+      </c>
+    </row>
+    <row r="600" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A600" s="1">
+        <v>46106.916666666664</v>
+      </c>
+      <c r="B600" s="4">
+        <v>31.220029964901155</v>
+      </c>
+      <c r="C600" s="4">
+        <v>37.411689923604328</v>
+      </c>
+      <c r="D600" s="4">
+        <v>38.042118866439544</v>
+      </c>
+    </row>
+    <row r="601" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A601" s="1">
+        <v>46106.958333333336</v>
+      </c>
+      <c r="B601" s="4">
+        <v>31.150083389282226</v>
+      </c>
+      <c r="C601" s="4">
+        <v>37.339551982879641</v>
+      </c>
+      <c r="D601" s="4">
+        <v>37.989891895694605</v>
+      </c>
+    </row>
+    <row r="602" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A602" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B602" s="4">
+        <v>31.121583550771078</v>
+      </c>
+      <c r="C602" s="4">
+        <v>37.290040818238872</v>
+      </c>
+      <c r="D602" s="4">
+        <v>37.940837361524316</v>
+      </c>
+    </row>
+    <row r="603" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A603" s="1">
+        <v>46107.041666666664</v>
+      </c>
+      <c r="B603" s="4">
+        <v>31.120417340596518</v>
+      </c>
+      <c r="C603" s="4">
+        <v>37.278052608783426</v>
+      </c>
+      <c r="D603" s="4">
+        <v>37.944657944507149</v>
+      </c>
+    </row>
+    <row r="604" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A604" s="1">
+        <v>46107.083333333336</v>
+      </c>
+      <c r="B604" s="4">
+        <v>31.080387322107949</v>
+      </c>
+      <c r="C604" s="4">
+        <v>37.196097989236151</v>
+      </c>
+      <c r="D604" s="4">
+        <v>37.906823236893203</v>
+      </c>
+    </row>
+    <row r="605" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A605" s="1">
+        <v>46107.125</v>
+      </c>
+      <c r="B605" s="4">
+        <v>31.04523803393046</v>
+      </c>
+      <c r="C605" s="4">
+        <v>37.180902148561422</v>
+      </c>
+      <c r="D605" s="4">
+        <v>37.866024177977458</v>
+      </c>
+    </row>
+    <row r="606" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A606" s="1">
+        <v>46107.166666666664</v>
+      </c>
+      <c r="B606" s="4">
+        <v>31.025041427612305</v>
+      </c>
+      <c r="C606" s="4">
+        <v>37.163832413522826</v>
+      </c>
+      <c r="D606" s="4">
+        <v>37.830495535381253</v>
+      </c>
+    </row>
+    <row r="607" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A607" s="1">
+        <v>46107.208333333336</v>
+      </c>
+      <c r="B607" s="4">
+        <v>30.996416721343994</v>
+      </c>
+      <c r="C607" s="4">
+        <v>37.148775959014891</v>
+      </c>
+      <c r="D607" s="4">
+        <v>37.790402626639654</v>
+      </c>
+    </row>
+    <row r="608" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A608" s="1">
+        <v>46107.25</v>
+      </c>
+      <c r="B608" s="4">
+        <v>30.983073127269744</v>
+      </c>
+      <c r="C608" s="4">
+        <v>37.150397040446599</v>
+      </c>
+      <c r="D608" s="4">
+        <v>37.799823185387808</v>
+      </c>
+    </row>
+    <row r="609" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A609" s="1">
+        <v>46107.291666666664</v>
+      </c>
+      <c r="B609" s="4">
+        <v>30.97838563521703</v>
+      </c>
+      <c r="C609" s="4">
+        <v>37.163381674126086</v>
+      </c>
+      <c r="D609" s="4">
+        <v>37.80300635462612</v>
+      </c>
+    </row>
+    <row r="610" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A610" s="1">
+        <v>46107.333333333336</v>
+      </c>
+      <c r="B610" s="4">
+        <v>30.987515866450778</v>
+      </c>
+      <c r="C610" s="4">
+        <v>37.174736439947985</v>
+      </c>
+      <c r="D610" s="4">
+        <v>37.83447458982468</v>
+      </c>
+    </row>
+    <row r="611" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A611" s="1">
+        <v>46107.375</v>
+      </c>
+      <c r="B611" s="4">
+        <v>31.033992468542468</v>
+      </c>
+      <c r="C611" s="4">
+        <v>37.241709938579135</v>
+      </c>
+      <c r="D611" s="4">
+        <v>37.883022185252827</v>
+      </c>
+    </row>
+    <row r="612" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A612" s="1">
+        <v>46107.416666666664</v>
+      </c>
+      <c r="B612" s="4">
+        <v>31.07569362770483</v>
+      </c>
+      <c r="C612" s="4">
+        <v>37.353124879201253</v>
+      </c>
+      <c r="D612" s="4">
+        <v>37.994098016034023</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="60" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B79CA267-F21F-4B34-8910-D02BBB080BD9}"/>
+  <xr:revisionPtr revIDLastSave="62" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D8DDE5-4A01-4599-A6EB-2B8222EF7918}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D612"/>
+  <dimension ref="A1:D633"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -9007,6 +9007,300 @@
         <v>37.994098016034023</v>
       </c>
     </row>
+    <row r="613" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A613" s="1">
+        <v>46107.458333333336</v>
+      </c>
+      <c r="B613" s="4">
+        <v>31.165089150837488</v>
+      </c>
+      <c r="C613" s="4">
+        <v>37.465600926948319</v>
+      </c>
+      <c r="D613" s="4">
+        <v>38.143087540120135</v>
+      </c>
+    </row>
+    <row r="614" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A614" s="1">
+        <v>46107.5</v>
+      </c>
+      <c r="B614" s="4">
+        <v>31.288332843780516</v>
+      </c>
+      <c r="C614" s="4">
+        <v>37.615869626131925</v>
+      </c>
+      <c r="D614" s="4">
+        <v>38.300134343245119</v>
+      </c>
+    </row>
+    <row r="615" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A615" s="1">
+        <v>46107.541666666664</v>
+      </c>
+      <c r="B615" s="4">
+        <v>31.432291666666668</v>
+      </c>
+      <c r="C615" s="4">
+        <v>37.784571918911404</v>
+      </c>
+      <c r="D615" s="4">
+        <v>38.424171314147188</v>
+      </c>
+    </row>
+    <row r="616" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A616" s="1">
+        <v>46107.583333333336</v>
+      </c>
+      <c r="B616" s="4">
+        <v>31.563398663089387</v>
+      </c>
+      <c r="C616" s="4">
+        <v>37.948266982357914</v>
+      </c>
+      <c r="D616" s="4">
+        <v>38.574419516414117</v>
+      </c>
+    </row>
+    <row r="617" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A617" s="1">
+        <v>46107.625</v>
+      </c>
+      <c r="B617" s="4">
+        <v>31.708809770856586</v>
+      </c>
+      <c r="C617" s="4">
+        <v>38.09301681374059</v>
+      </c>
+      <c r="D617" s="4">
+        <v>38.710335066459642</v>
+      </c>
+    </row>
+    <row r="618" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A618" s="1">
+        <v>46107.666666666664</v>
+      </c>
+      <c r="B618" s="4">
+        <v>31.706249698003134</v>
+      </c>
+      <c r="C618" s="4">
+        <v>38.109605864116126</v>
+      </c>
+      <c r="D618" s="4">
+        <v>38.744395471511446</v>
+      </c>
+    </row>
+    <row r="619" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A619" s="1">
+        <v>46107.708333333336</v>
+      </c>
+      <c r="B619" s="4">
+        <v>31.662707757949828</v>
+      </c>
+      <c r="C619" s="4">
+        <v>38.016847996484664</v>
+      </c>
+      <c r="D619" s="4">
+        <v>38.658304631792781</v>
+      </c>
+    </row>
+    <row r="620" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A620" s="1">
+        <v>46107.75</v>
+      </c>
+      <c r="B620" s="4">
+        <v>31.603853935665555</v>
+      </c>
+      <c r="C620" s="4">
+        <v>37.921127294611047</v>
+      </c>
+      <c r="D620" s="4">
+        <v>38.551818587648143</v>
+      </c>
+    </row>
+    <row r="621" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A621" s="1">
+        <v>46107.791666666664</v>
+      </c>
+      <c r="B621" s="4">
+        <v>31.494062413109674</v>
+      </c>
+      <c r="C621" s="4">
+        <v>37.797471389064086</v>
+      </c>
+      <c r="D621" s="4">
+        <v>38.429543143018691</v>
+      </c>
+    </row>
+    <row r="622" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A622" s="1">
+        <v>46107.833333333336</v>
+      </c>
+      <c r="B622" s="4">
+        <v>31.391638634999595</v>
+      </c>
+      <c r="C622" s="4">
+        <v>37.666686919672571</v>
+      </c>
+      <c r="D622" s="4">
+        <v>38.326616979628923</v>
+      </c>
+    </row>
+    <row r="623" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A623" s="1">
+        <v>46107.875</v>
+      </c>
+      <c r="B623" s="4">
+        <v>31.332944657007854</v>
+      </c>
+      <c r="C623" s="4">
+        <v>37.581538366599268</v>
+      </c>
+      <c r="D623" s="4">
+        <v>38.224083692194704</v>
+      </c>
+    </row>
+    <row r="624" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A624" s="1">
+        <v>46107.916666666664</v>
+      </c>
+      <c r="B624" s="4">
+        <v>31.286177628835041</v>
+      </c>
+      <c r="C624" s="4">
+        <v>37.512421623865762</v>
+      </c>
+      <c r="D624" s="4">
+        <v>38.174530376398017</v>
+      </c>
+    </row>
+    <row r="625" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A625" s="1">
+        <v>46107.958333333336</v>
+      </c>
+      <c r="B625" s="4">
+        <v>31.237083559566074</v>
+      </c>
+      <c r="C625" s="4">
+        <v>37.453698062896727</v>
+      </c>
+      <c r="D625" s="4">
+        <v>38.09969681962933</v>
+      </c>
+    </row>
+    <row r="626" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A626" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B626" s="4">
+        <v>31.22630564159817</v>
+      </c>
+      <c r="C626" s="4">
+        <v>37.386705807844798</v>
+      </c>
+      <c r="D626" s="4">
+        <v>38.078257764120266</v>
+      </c>
+    </row>
+    <row r="627" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A627" s="1">
+        <v>46108.041666666664</v>
+      </c>
+      <c r="B627" s="4">
+        <v>31.233381816546121</v>
+      </c>
+      <c r="C627" s="4">
+        <v>37.383859399954481</v>
+      </c>
+      <c r="D627" s="4">
+        <v>38.053824860203164</v>
+      </c>
+    </row>
+    <row r="628" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A628" s="1">
+        <v>46108.083333333336</v>
+      </c>
+      <c r="B628" s="4">
+        <v>31.194062511126202</v>
+      </c>
+      <c r="C628" s="4">
+        <v>37.384316805430821</v>
+      </c>
+      <c r="D628" s="4">
+        <v>38.030497523845689</v>
+      </c>
+    </row>
+    <row r="629" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A629" s="1">
+        <v>46108.125</v>
+      </c>
+      <c r="B629" s="4">
+        <v>31.171562894185385</v>
+      </c>
+      <c r="C629" s="4">
+        <v>37.302671278090706</v>
+      </c>
+      <c r="D629" s="4">
+        <v>37.958931107618952</v>
+      </c>
+    </row>
+    <row r="630" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A630" s="1">
+        <v>46108.166666666664</v>
+      </c>
+      <c r="B630" s="4">
+        <v>31.067534605662029</v>
+      </c>
+      <c r="C630" s="4">
+        <v>37.221710353427461</v>
+      </c>
+      <c r="D630" s="4">
+        <v>37.888021641837227</v>
+      </c>
+    </row>
+    <row r="631" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A631" s="1">
+        <v>46108.208333333336</v>
+      </c>
+      <c r="B631" s="4">
+        <v>31.00090266863505</v>
+      </c>
+      <c r="C631" s="4">
+        <v>37.160842162238225</v>
+      </c>
+      <c r="D631" s="4">
+        <v>37.840018446755572</v>
+      </c>
+    </row>
+    <row r="632" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A632" s="1">
+        <v>46108.25</v>
+      </c>
+      <c r="B632" s="4">
+        <v>30.989884413613215</v>
+      </c>
+      <c r="C632" s="4">
+        <v>37.150052083333335</v>
+      </c>
+      <c r="D632" s="4">
+        <v>37.811957667497609</v>
+      </c>
+    </row>
+    <row r="633" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A633" s="1">
+        <v>46108.291666666664</v>
+      </c>
+      <c r="B633" s="4">
+        <v>30.960649937509221</v>
+      </c>
+      <c r="C633" s="4">
+        <v>37.134182394118532</v>
+      </c>
+      <c r="D633" s="4">
+        <v>37.783646810557848</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="62" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2D8DDE5-4A01-4599-A6EB-2B8222EF7918}"/>
+  <xr:revisionPtr revIDLastSave="64" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54FA4B75-2B6B-43E4-8CE4-A773D1471A0E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D633"/>
+  <dimension ref="A1:D729"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -9292,13 +9296,1357 @@
         <v>46108.291666666664</v>
       </c>
       <c r="B633" s="4">
-        <v>30.960649937509221</v>
+        <v>30.958285157443484</v>
       </c>
       <c r="C633" s="4">
         <v>37.134182394118532</v>
       </c>
       <c r="D633" s="4">
         <v>37.783646810557848</v>
+      </c>
+    </row>
+    <row r="634" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A634" s="1">
+        <v>46108.333333333336</v>
+      </c>
+      <c r="B634" s="4">
+        <v>30.967105765091745</v>
+      </c>
+      <c r="C634" s="4">
+        <v>37.134893810181389</v>
+      </c>
+      <c r="D634" s="4">
+        <v>37.799010008397396</v>
+      </c>
+    </row>
+    <row r="635" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A635" s="1">
+        <v>46108.375</v>
+      </c>
+      <c r="B635" s="4">
+        <v>31.015142503537628</v>
+      </c>
+      <c r="C635" s="4">
+        <v>37.223795534315563</v>
+      </c>
+      <c r="D635" s="4">
+        <v>37.885347679066435</v>
+      </c>
+    </row>
+    <row r="636" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A636" s="1">
+        <v>46108.416666666664</v>
+      </c>
+      <c r="B636" s="4">
+        <v>31.134589326274288</v>
+      </c>
+      <c r="C636" s="4">
+        <v>37.393488199837741</v>
+      </c>
+      <c r="D636" s="4">
+        <v>38.072430818875027</v>
+      </c>
+    </row>
+    <row r="637" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A637" s="1">
+        <v>46108.458333333336</v>
+      </c>
+      <c r="B637" s="4">
+        <v>31.232494652378662</v>
+      </c>
+      <c r="C637" s="4">
+        <v>37.532129613090966</v>
+      </c>
+      <c r="D637" s="4">
+        <v>38.188485922085135</v>
+      </c>
+    </row>
+    <row r="638" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A638" s="1">
+        <v>46108.5</v>
+      </c>
+      <c r="B638" s="4">
+        <v>31.366416486104331</v>
+      </c>
+      <c r="C638" s="4">
+        <v>37.662856086095175</v>
+      </c>
+      <c r="D638" s="4">
+        <v>38.332659727776544</v>
+      </c>
+    </row>
+    <row r="639" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A639" s="1">
+        <v>46108.541666666664</v>
+      </c>
+      <c r="B639" s="4">
+        <v>31.541291324297585</v>
+      </c>
+      <c r="C639" s="4">
+        <v>37.867217048009238</v>
+      </c>
+      <c r="D639" s="4">
+        <v>38.50650052466829</v>
+      </c>
+    </row>
+    <row r="640" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A640" s="1">
+        <v>46108.583333333336</v>
+      </c>
+      <c r="B640" s="4">
+        <v>31.658333245913187</v>
+      </c>
+      <c r="C640" s="4">
+        <v>38.015370345115663</v>
+      </c>
+      <c r="D640" s="4">
+        <v>38.653671267143608</v>
+      </c>
+    </row>
+    <row r="641" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A641" s="1">
+        <v>46108.625</v>
+      </c>
+      <c r="B641" s="4">
+        <v>31.728205460768482</v>
+      </c>
+      <c r="C641" s="4">
+        <v>38.089505759874982</v>
+      </c>
+      <c r="D641" s="4">
+        <v>38.718133375255086</v>
+      </c>
+    </row>
+    <row r="642" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A642" s="1">
+        <v>46108.666666666664</v>
+      </c>
+      <c r="B642" s="4">
+        <v>31.759422416190056</v>
+      </c>
+      <c r="C642" s="4">
+        <v>38.163072954813636</v>
+      </c>
+      <c r="D642" s="4">
+        <v>38.789903331481398</v>
+      </c>
+    </row>
+    <row r="643" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A643" s="1">
+        <v>46108.708333333336</v>
+      </c>
+      <c r="B643" s="4">
+        <v>31.74673992109738</v>
+      </c>
+      <c r="C643" s="4">
+        <v>38.121114600499475</v>
+      </c>
+      <c r="D643" s="4">
+        <v>38.760690041692705</v>
+      </c>
+    </row>
+    <row r="644" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A644" s="1">
+        <v>46108.75</v>
+      </c>
+      <c r="B644" s="4">
+        <v>31.702611837500619</v>
+      </c>
+      <c r="C644" s="4">
+        <v>38.063051811854045</v>
+      </c>
+      <c r="D644" s="4">
+        <v>38.727612437312594</v>
+      </c>
+    </row>
+    <row r="645" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A645" s="1">
+        <v>46108.791666666664</v>
+      </c>
+      <c r="B645" s="4">
+        <v>31.609403530034154</v>
+      </c>
+      <c r="C645" s="4">
+        <v>37.980691541944239</v>
+      </c>
+      <c r="D645" s="4">
+        <v>38.614926557866745</v>
+      </c>
+    </row>
+    <row r="646" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A646" s="1">
+        <v>46108.833333333336</v>
+      </c>
+      <c r="B646" s="4">
+        <v>31.531533790357184</v>
+      </c>
+      <c r="C646" s="4">
+        <v>37.881912484850197</v>
+      </c>
+      <c r="D646" s="4">
+        <v>38.497548191888775</v>
+      </c>
+    </row>
+    <row r="647" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A647" s="1">
+        <v>46108.875</v>
+      </c>
+      <c r="B647" s="4">
+        <v>31.450478855339256</v>
+      </c>
+      <c r="C647" s="4">
+        <v>37.763937428792318</v>
+      </c>
+      <c r="D647" s="4">
+        <v>38.403575575290773</v>
+      </c>
+    </row>
+    <row r="648" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A648" s="1">
+        <v>46108.916666666664</v>
+      </c>
+      <c r="B648" s="4">
+        <v>31.410520992708634</v>
+      </c>
+      <c r="C648" s="4">
+        <v>37.699759801228844</v>
+      </c>
+      <c r="D648" s="4">
+        <v>38.319411041794943</v>
+      </c>
+    </row>
+    <row r="649" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A649" s="1">
+        <v>46108.958333333336</v>
+      </c>
+      <c r="B649" s="4">
+        <v>31.359625107447307</v>
+      </c>
+      <c r="C649" s="4">
+        <v>37.611472661567461</v>
+      </c>
+      <c r="D649" s="4">
+        <v>38.235471815191048</v>
+      </c>
+    </row>
+    <row r="650" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A650" s="1">
+        <v>46109</v>
+      </c>
+      <c r="B650" s="4">
+        <v>31.307916678322687</v>
+      </c>
+      <c r="C650" s="4">
+        <v>37.539203906781744</v>
+      </c>
+      <c r="D650" s="4">
+        <v>38.157201479738411</v>
+      </c>
+    </row>
+    <row r="651" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A651" s="1">
+        <v>46109.041666666664</v>
+      </c>
+      <c r="B651" s="4">
+        <v>31.259375129805672</v>
+      </c>
+      <c r="C651" s="4">
+        <v>37.485083249409996</v>
+      </c>
+      <c r="D651" s="4">
+        <v>38.102587066732966</v>
+      </c>
+    </row>
+    <row r="652" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A652" s="1">
+        <v>46109.083333333336</v>
+      </c>
+      <c r="B652" s="4">
+        <v>31.246607027735028</v>
+      </c>
+      <c r="C652" s="4">
+        <v>37.453966654141745</v>
+      </c>
+      <c r="D652" s="4">
+        <v>38.072051370863015</v>
+      </c>
+    </row>
+    <row r="653" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A653" s="1">
+        <v>46109.125</v>
+      </c>
+      <c r="B653" s="4">
+        <v>31.24762900443304</v>
+      </c>
+      <c r="C653" s="4">
+        <v>37.435669080416361</v>
+      </c>
+      <c r="D653" s="4">
+        <v>38.036469988274369</v>
+      </c>
+    </row>
+    <row r="654" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A654" s="1">
+        <v>46109.166666666664</v>
+      </c>
+      <c r="B654" s="4">
+        <v>31.208055909474691</v>
+      </c>
+      <c r="C654" s="4">
+        <v>37.425437755584717</v>
+      </c>
+      <c r="D654" s="4">
+        <v>38.002798142341369</v>
+      </c>
+    </row>
+    <row r="655" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A655" s="1">
+        <v>46109.208333333336</v>
+      </c>
+      <c r="B655" s="4">
+        <v>31.192167273097567</v>
+      </c>
+      <c r="C655" s="4">
+        <v>37.403556999933151</v>
+      </c>
+      <c r="D655" s="4">
+        <v>38.028823409581655</v>
+      </c>
+    </row>
+    <row r="656" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A656" s="1">
+        <v>46109.25</v>
+      </c>
+      <c r="B656" s="4">
+        <v>31.16906332174937</v>
+      </c>
+      <c r="C656" s="4">
+        <v>37.376704052516395</v>
+      </c>
+      <c r="D656" s="4">
+        <v>37.97596546605422</v>
+      </c>
+    </row>
+    <row r="657" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A657" s="1">
+        <v>46109.291666666664</v>
+      </c>
+      <c r="B657" s="4">
+        <v>31.123542022705077</v>
+      </c>
+      <c r="C657" s="4">
+        <v>37.340637590317499</v>
+      </c>
+      <c r="D657" s="4">
+        <v>37.979847308300585</v>
+      </c>
+    </row>
+    <row r="658" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A658" s="1">
+        <v>46109.333333333336</v>
+      </c>
+      <c r="B658" s="4">
+        <v>31.172083997726439</v>
+      </c>
+      <c r="C658" s="4">
+        <v>37.395712284814742</v>
+      </c>
+      <c r="D658" s="4">
+        <v>38.034938097104494</v>
+      </c>
+    </row>
+    <row r="659" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A659" s="1">
+        <v>46109.375</v>
+      </c>
+      <c r="B659" s="4">
+        <v>31.229514137903848</v>
+      </c>
+      <c r="C659" s="4">
+        <v>37.443628533681235</v>
+      </c>
+      <c r="D659" s="4">
+        <v>38.068448925531591</v>
+      </c>
+    </row>
+    <row r="660" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A660" s="1">
+        <v>46109.416666666664</v>
+      </c>
+      <c r="B660" s="4">
+        <v>31.260277700424194</v>
+      </c>
+      <c r="C660" s="4">
+        <v>37.505156485239667</v>
+      </c>
+      <c r="D660" s="4">
+        <v>38.149779208546498</v>
+      </c>
+    </row>
+    <row r="661" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A661" s="1">
+        <v>46109.458333333336</v>
+      </c>
+      <c r="B661" s="4">
+        <v>31.321666733423868</v>
+      </c>
+      <c r="C661" s="4">
+        <v>37.576803457736972</v>
+      </c>
+      <c r="D661" s="4">
+        <v>38.247113940317732</v>
+      </c>
+    </row>
+    <row r="662" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A662" s="1">
+        <v>46109.5</v>
+      </c>
+      <c r="B662" s="4">
+        <v>31.385208264986673</v>
+      </c>
+      <c r="C662" s="4">
+        <v>37.674532888995273</v>
+      </c>
+      <c r="D662" s="4">
+        <v>38.342078674941504</v>
+      </c>
+    </row>
+    <row r="663" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A663" s="1">
+        <v>46109.541666666664</v>
+      </c>
+      <c r="B663" s="4">
+        <v>31.52958357334137</v>
+      </c>
+      <c r="C663" s="4">
+        <v>37.861006843778824</v>
+      </c>
+      <c r="D663" s="4">
+        <v>38.529594400712227</v>
+      </c>
+    </row>
+    <row r="664" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A664" s="1">
+        <v>46109.583333333336</v>
+      </c>
+      <c r="B664" s="4">
+        <v>31.638541634877523</v>
+      </c>
+      <c r="C664" s="4">
+        <v>37.976502632238926</v>
+      </c>
+      <c r="D664" s="4">
+        <v>38.619481110211538</v>
+      </c>
+    </row>
+    <row r="665" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A665" s="1">
+        <v>46109.625</v>
+      </c>
+      <c r="B665" s="4">
+        <v>31.648749669392902</v>
+      </c>
+      <c r="C665" s="4">
+        <v>37.995814797409579</v>
+      </c>
+      <c r="D665" s="4">
+        <v>38.655388078356751</v>
+      </c>
+    </row>
+    <row r="666" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A666" s="1">
+        <v>46109.666666666664</v>
+      </c>
+      <c r="B666" s="4">
+        <v>31.663844906943186</v>
+      </c>
+      <c r="C666" s="4">
+        <v>38.035616943571306</v>
+      </c>
+      <c r="D666" s="4">
+        <v>38.66290790392226</v>
+      </c>
+    </row>
+    <row r="667" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A667" s="1">
+        <v>46109.708333333336</v>
+      </c>
+      <c r="B667" s="4">
+        <v>31.703446676012071</v>
+      </c>
+      <c r="C667" s="4">
+        <v>38.070763778686526</v>
+      </c>
+      <c r="D667" s="4">
+        <v>38.661648785144557</v>
+      </c>
+    </row>
+    <row r="668" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A668" s="1">
+        <v>46109.75</v>
+      </c>
+      <c r="B668" s="4">
+        <v>31.749007346895006</v>
+      </c>
+      <c r="C668" s="4">
+        <v>38.165907423836842</v>
+      </c>
+      <c r="D668" s="4">
+        <v>38.756731883835187</v>
+      </c>
+    </row>
+    <row r="669" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A669" s="1">
+        <v>46109.791666666664</v>
+      </c>
+      <c r="B669" s="4">
+        <v>31.702729002634683</v>
+      </c>
+      <c r="C669" s="4">
+        <v>38.104586808340891</v>
+      </c>
+      <c r="D669" s="4">
+        <v>38.726926171888621</v>
+      </c>
+    </row>
+    <row r="670" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A670" s="1">
+        <v>46109.833333333336</v>
+      </c>
+      <c r="B670" s="4">
+        <v>31.607638641198477</v>
+      </c>
+      <c r="C670" s="4">
+        <v>37.964536132812498</v>
+      </c>
+      <c r="D670" s="4">
+        <v>38.584961103725284</v>
+      </c>
+    </row>
+    <row r="671" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A671" s="1">
+        <v>46109.875</v>
+      </c>
+      <c r="B671" s="4">
+        <v>31.571041953563689</v>
+      </c>
+      <c r="C671" s="4">
+        <v>37.918812592824302</v>
+      </c>
+      <c r="D671" s="4">
+        <v>38.511706613511492</v>
+      </c>
+    </row>
+    <row r="672" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A672" s="1">
+        <v>46109.916666666664</v>
+      </c>
+      <c r="B672" s="4">
+        <v>31.537499936421714</v>
+      </c>
+      <c r="C672" s="4">
+        <v>37.846260070800781</v>
+      </c>
+      <c r="D672" s="4">
+        <v>38.468149148476641</v>
+      </c>
+    </row>
+    <row r="673" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A673" s="1">
+        <v>46109.958333333336</v>
+      </c>
+      <c r="B673" s="4">
+        <v>31.447125043869018</v>
+      </c>
+      <c r="C673" s="4">
+        <v>37.709291701846652</v>
+      </c>
+      <c r="D673" s="4">
+        <v>38.340749780039353</v>
+      </c>
+    </row>
+    <row r="674" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A674" s="1">
+        <v>46110</v>
+      </c>
+      <c r="B674" s="4">
+        <v>31.321157722007936</v>
+      </c>
+      <c r="C674" s="4">
+        <v>37.585568063826784</v>
+      </c>
+      <c r="D674" s="4">
+        <v>38.226184451890106</v>
+      </c>
+    </row>
+    <row r="675" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A675" s="1">
+        <v>46110.041666666664</v>
+      </c>
+      <c r="B675" s="4">
+        <v>31.279217033851438</v>
+      </c>
+      <c r="C675" s="4">
+        <v>37.51485868635632</v>
+      </c>
+      <c r="D675" s="4">
+        <v>38.154467320661965</v>
+      </c>
+    </row>
+    <row r="676" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A676" s="1">
+        <v>46110.083333333336</v>
+      </c>
+      <c r="B676" s="4">
+        <v>31.196041949590047</v>
+      </c>
+      <c r="C676" s="4">
+        <v>37.414947986602783</v>
+      </c>
+      <c r="D676" s="4">
+        <v>38.04177123458927</v>
+      </c>
+    </row>
+    <row r="677" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A677" s="1">
+        <v>46110.125</v>
+      </c>
+      <c r="B677" s="4">
+        <v>31.115417003631592</v>
+      </c>
+      <c r="C677" s="4">
+        <v>37.325469207763675</v>
+      </c>
+      <c r="D677" s="4">
+        <v>37.959158705520629</v>
+      </c>
+    </row>
+    <row r="678" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A678" s="1">
+        <v>46110.166666666664</v>
+      </c>
+      <c r="B678" s="4">
+        <v>31.113750569025676</v>
+      </c>
+      <c r="C678" s="4">
+        <v>37.318385410308835</v>
+      </c>
+      <c r="D678" s="4">
+        <v>37.938998531959577</v>
+      </c>
+    </row>
+    <row r="679" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A679" s="1">
+        <v>46110.208333333336</v>
+      </c>
+      <c r="B679" s="4">
+        <v>31.085750137964883</v>
+      </c>
+      <c r="C679" s="4">
+        <v>37.283150815963744</v>
+      </c>
+      <c r="D679" s="4">
+        <v>37.893479260376644</v>
+      </c>
+    </row>
+    <row r="680" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A680" s="1">
+        <v>46110.25</v>
+      </c>
+      <c r="B680" s="4">
+        <v>31.08335216999054</v>
+      </c>
+      <c r="C680" s="4">
+        <v>37.290776554743452</v>
+      </c>
+      <c r="D680" s="4">
+        <v>37.885199024540682</v>
+      </c>
+    </row>
+    <row r="681" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A681" s="1">
+        <v>46110.291666666664</v>
+      </c>
+      <c r="B681" s="4">
+        <v>31.064375581616673</v>
+      </c>
+      <c r="C681" s="4">
+        <v>37.154380337397257</v>
+      </c>
+      <c r="D681" s="4">
+        <v>37.903381193987741</v>
+      </c>
+    </row>
+    <row r="682" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A682" s="1">
+        <v>46110.333333333336</v>
+      </c>
+      <c r="B682" s="4">
+        <v>31.079467359243655</v>
+      </c>
+      <c r="C682" s="4">
+        <v>35.70530285546274</v>
+      </c>
+      <c r="D682" s="4">
+        <v>36.529424520748137</v>
+      </c>
+    </row>
+    <row r="683" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A683" s="1">
+        <v>46110.375</v>
+      </c>
+      <c r="B683" s="4">
+        <v>31.120292097727457</v>
+      </c>
+      <c r="C683" s="4">
+        <v>36.588577559500031</v>
+      </c>
+      <c r="D683" s="4">
+        <v>36.978450881414524</v>
+      </c>
+    </row>
+    <row r="684" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A684" s="1">
+        <v>46110.416666666664</v>
+      </c>
+      <c r="B684" s="4">
+        <v>31.171791197458901</v>
+      </c>
+      <c r="C684" s="4">
+        <v>37.425879563225642</v>
+      </c>
+      <c r="D684" s="4">
+        <v>38.095642066743459</v>
+      </c>
+    </row>
+    <row r="685" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A685" s="1">
+        <v>46110.458333333336</v>
+      </c>
+      <c r="B685" s="4">
+        <v>31.228076874904147</v>
+      </c>
+      <c r="C685" s="4">
+        <v>37.473922091590033</v>
+      </c>
+      <c r="D685" s="4">
+        <v>38.164483188337634</v>
+      </c>
+    </row>
+    <row r="686" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A686" s="1">
+        <v>46110.5</v>
+      </c>
+      <c r="B686" s="4">
+        <v>31.310048258610259</v>
+      </c>
+      <c r="C686" s="4">
+        <v>37.560939618746438</v>
+      </c>
+      <c r="D686" s="4">
+        <v>38.238549722073024</v>
+      </c>
+    </row>
+    <row r="687" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A687" s="1">
+        <v>46110.541666666664</v>
+      </c>
+      <c r="B687" s="4">
+        <v>31.427708641688028</v>
+      </c>
+      <c r="C687" s="4">
+        <v>37.711115267541672</v>
+      </c>
+      <c r="D687" s="4">
+        <v>38.358351261165438</v>
+      </c>
+    </row>
+    <row r="688" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A688" s="1">
+        <v>46110.583333333336</v>
+      </c>
+      <c r="B688" s="4">
+        <v>31.514821393149237</v>
+      </c>
+      <c r="C688" s="4">
+        <v>37.83190731169686</v>
+      </c>
+      <c r="D688" s="4">
+        <v>38.473160807216573</v>
+      </c>
+    </row>
+    <row r="689" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A689" s="1">
+        <v>46110.625</v>
+      </c>
+      <c r="B689" s="4">
+        <v>31.578094984236216</v>
+      </c>
+      <c r="C689" s="4">
+        <v>37.899422614687971</v>
+      </c>
+      <c r="D689" s="4">
+        <v>38.55239619312372</v>
+      </c>
+    </row>
+    <row r="690" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A690" s="1">
+        <v>46110.666666666664</v>
+      </c>
+      <c r="B690" s="4">
+        <v>31.55589742171459</v>
+      </c>
+      <c r="C690" s="4">
+        <v>37.894071857929227</v>
+      </c>
+      <c r="D690" s="4">
+        <v>38.584611860882937</v>
+      </c>
+    </row>
+    <row r="691" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A691" s="1">
+        <v>46110.708333333336</v>
+      </c>
+      <c r="B691" s="4">
+        <v>31.395769314888199</v>
+      </c>
+      <c r="C691" s="4">
+        <v>37.754603278636935</v>
+      </c>
+      <c r="D691" s="4">
+        <v>38.44852278257158</v>
+      </c>
+    </row>
+    <row r="692" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A692" s="1">
+        <v>46110.75</v>
+      </c>
+      <c r="B692" s="4">
+        <v>31.326288639133814</v>
+      </c>
+      <c r="C692" s="4">
+        <v>37.685976505279541</v>
+      </c>
+      <c r="D692" s="4">
+        <v>38.362671300726959</v>
+      </c>
+    </row>
+    <row r="693" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A693" s="1">
+        <v>46110.791666666664</v>
+      </c>
+      <c r="B693" s="4">
+        <v>31.323590163695506</v>
+      </c>
+      <c r="C693" s="4">
+        <v>37.708723926544188</v>
+      </c>
+      <c r="D693" s="4">
+        <v>38.332154524106961</v>
+      </c>
+    </row>
+    <row r="694" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A694" s="1">
+        <v>46110.833333333336</v>
+      </c>
+      <c r="B694" s="4">
+        <v>31.364166720708212</v>
+      </c>
+      <c r="C694" s="4">
+        <v>37.738906192779538</v>
+      </c>
+      <c r="D694" s="4">
+        <v>38.320495576480511</v>
+      </c>
+    </row>
+    <row r="695" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A695" s="1">
+        <v>46110.875</v>
+      </c>
+      <c r="B695" s="4">
+        <v>31.334355949633046</v>
+      </c>
+      <c r="C695" s="4">
+        <v>37.680609475998651</v>
+      </c>
+      <c r="D695" s="4">
+        <v>38.318559147970426</v>
+      </c>
+    </row>
+    <row r="696" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A696" s="1">
+        <v>46110.916666666664</v>
+      </c>
+      <c r="B696" s="4">
+        <v>31.32564375472791</v>
+      </c>
+      <c r="C696" s="4">
+        <v>37.659219544068037</v>
+      </c>
+      <c r="D696" s="4">
+        <v>38.283455684435054</v>
+      </c>
+    </row>
+    <row r="697" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A697" s="1">
+        <v>46110.958333333336</v>
+      </c>
+      <c r="B697" s="4">
+        <v>31.311249876022337</v>
+      </c>
+      <c r="C697" s="4">
+        <v>37.616451573805371</v>
+      </c>
+      <c r="D697" s="4">
+        <v>38.220872891365424</v>
+      </c>
+    </row>
+    <row r="698" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A698" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B698" s="4">
+        <v>31.293333276112875</v>
+      </c>
+      <c r="C698" s="4">
+        <v>37.593719056447348</v>
+      </c>
+      <c r="D698" s="4">
+        <v>38.190677278887378</v>
+      </c>
+    </row>
+    <row r="699" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A699" s="1">
+        <v>46111.041666666664</v>
+      </c>
+      <c r="B699" s="4">
+        <v>31.244791618982951</v>
+      </c>
+      <c r="C699" s="4">
+        <v>37.531406084696449</v>
+      </c>
+      <c r="D699" s="4">
+        <v>38.133343845747319</v>
+      </c>
+    </row>
+    <row r="700" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A700" s="1">
+        <v>46111.083333333336</v>
+      </c>
+      <c r="B700" s="4">
+        <v>31.223465789448131</v>
+      </c>
+      <c r="C700" s="4">
+        <v>37.49097321339142</v>
+      </c>
+      <c r="D700" s="4">
+        <v>38.127851284263805</v>
+      </c>
+    </row>
+    <row r="701" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A701" s="1">
+        <v>46111.125</v>
+      </c>
+      <c r="B701" s="4">
+        <v>31.256950635621042</v>
+      </c>
+      <c r="C701" s="4">
+        <v>37.482434132334951</v>
+      </c>
+      <c r="D701" s="4">
+        <v>38.079591609594701</v>
+      </c>
+    </row>
+    <row r="702" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A702" s="1">
+        <v>46111.166666666664</v>
+      </c>
+      <c r="B702" s="4">
+        <v>31.240645848910013</v>
+      </c>
+      <c r="C702" s="4">
+        <v>37.484412465776714</v>
+      </c>
+      <c r="D702" s="4">
+        <v>38.080876624776359</v>
+      </c>
+    </row>
+    <row r="703" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A703" s="1">
+        <v>46111.208333333336</v>
+      </c>
+      <c r="B703" s="4">
+        <v>31.202928491616859</v>
+      </c>
+      <c r="C703" s="4">
+        <v>37.467716198875785</v>
+      </c>
+      <c r="D703" s="4">
+        <v>38.064478688397841</v>
+      </c>
+    </row>
+    <row r="704" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A704" s="1">
+        <v>46111.25</v>
+      </c>
+      <c r="B704" s="4">
+        <v>31.167051991438253</v>
+      </c>
+      <c r="C704" s="4">
+        <v>37.416781628018327</v>
+      </c>
+      <c r="D704" s="4">
+        <v>38.045427659722641</v>
+      </c>
+    </row>
+    <row r="705" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A705" s="1">
+        <v>46111.291666666664</v>
+      </c>
+      <c r="B705" s="4">
+        <v>31.128835623941303</v>
+      </c>
+      <c r="C705" s="4">
+        <v>37.407440117730033</v>
+      </c>
+      <c r="D705" s="4">
+        <v>38.019199683508987</v>
+      </c>
+    </row>
+    <row r="706" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A706" s="1">
+        <v>46111.333333333336</v>
+      </c>
+      <c r="B706" s="4">
+        <v>31.129915418742616</v>
+      </c>
+      <c r="C706" s="4">
+        <v>37.391878640916616</v>
+      </c>
+      <c r="D706" s="4">
+        <v>38.008232272321052</v>
+      </c>
+    </row>
+    <row r="707" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A707" s="1">
+        <v>46111.375</v>
+      </c>
+      <c r="B707" s="4">
+        <v>31.168125200271607</v>
+      </c>
+      <c r="C707" s="4">
+        <v>37.434848672548931</v>
+      </c>
+      <c r="D707" s="4">
+        <v>37.952073774934895</v>
+      </c>
+    </row>
+    <row r="708" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A708" s="1">
+        <v>46111.416666666664</v>
+      </c>
+      <c r="B708" s="4">
+        <v>31.243333435058595</v>
+      </c>
+      <c r="C708" s="4">
+        <v>37.508267839749657</v>
+      </c>
+      <c r="D708" s="4">
+        <v>38.000808277202374</v>
+      </c>
+    </row>
+    <row r="709" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A709" s="1">
+        <v>46111.458333333336</v>
+      </c>
+      <c r="B709" s="4">
+        <v>31.267499780654909</v>
+      </c>
+      <c r="C709" s="4">
+        <v>37.537694950103763</v>
+      </c>
+      <c r="D709" s="4">
+        <v>38.112267587661528</v>
+      </c>
+    </row>
+    <row r="710" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A710" s="1">
+        <v>46111.5</v>
+      </c>
+      <c r="B710" s="4">
+        <v>31.292985969119602</v>
+      </c>
+      <c r="C710" s="4">
+        <v>37.611253392961288</v>
+      </c>
+      <c r="D710" s="4">
+        <v>38.165182726810492</v>
+      </c>
+    </row>
+    <row r="711" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A711" s="1">
+        <v>46111.541666666664</v>
+      </c>
+      <c r="B711" s="4">
+        <v>31.393680320845711</v>
+      </c>
+      <c r="C711" s="4">
+        <v>37.684097194478973</v>
+      </c>
+      <c r="D711" s="4">
+        <v>38.245223916234899</v>
+      </c>
+    </row>
+    <row r="712" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A712" s="1">
+        <v>46111.583333333336</v>
+      </c>
+      <c r="B712" s="4">
+        <v>31.452291576067605</v>
+      </c>
+      <c r="C712" s="4">
+        <v>37.773829540339378</v>
+      </c>
+      <c r="D712" s="4">
+        <v>38.560325549189358</v>
+      </c>
+    </row>
+    <row r="713" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A713" s="1">
+        <v>46111.625</v>
+      </c>
+      <c r="B713" s="4">
+        <v>31.384397899709043</v>
+      </c>
+      <c r="C713" s="4">
+        <v>37.729517950755536</v>
+      </c>
+      <c r="D713" s="4">
+        <v>38.637308716511278</v>
+      </c>
+    </row>
+    <row r="714" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A714" s="1">
+        <v>46111.666666666664</v>
+      </c>
+      <c r="B714" s="4">
+        <v>31.381482937153464</v>
+      </c>
+      <c r="C714" s="4">
+        <v>37.763892700663362</v>
+      </c>
+      <c r="D714" s="4">
+        <v>38.605027030771126</v>
+      </c>
+    </row>
+    <row r="715" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A715" s="1">
+        <v>46111.708333333336</v>
+      </c>
+      <c r="B715" s="4">
+        <v>31.401254399135862</v>
+      </c>
+      <c r="C715" s="4">
+        <v>37.785529581705731</v>
+      </c>
+      <c r="D715" s="4">
+        <v>38.610342854786744</v>
+      </c>
+    </row>
+    <row r="716" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A716" s="1">
+        <v>46111.75</v>
+      </c>
+      <c r="B716" s="4">
+        <v>31.456637582955537</v>
+      </c>
+      <c r="C716" s="4">
+        <v>37.886371103922528</v>
+      </c>
+      <c r="D716" s="4">
+        <v>38.690480827185645</v>
+      </c>
+    </row>
+    <row r="717" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A717" s="1">
+        <v>46111.791666666664</v>
+      </c>
+      <c r="B717" s="4">
+        <v>31.416955742129577</v>
+      </c>
+      <c r="C717" s="4">
+        <v>37.868964071627019</v>
+      </c>
+      <c r="D717" s="4">
+        <v>38.688184816143774</v>
+      </c>
+    </row>
+    <row r="718" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A718" s="1">
+        <v>46111.833333333336</v>
+      </c>
+      <c r="B718" s="4">
+        <v>31.396377576722038</v>
+      </c>
+      <c r="C718" s="4">
+        <v>37.827749457182705</v>
+      </c>
+      <c r="D718" s="4">
+        <v>38.638627099662123</v>
+      </c>
+    </row>
+    <row r="719" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A719" s="1">
+        <v>46111.875</v>
+      </c>
+      <c r="B719" s="4">
+        <v>31.34738011441679</v>
+      </c>
+      <c r="C719" s="4">
+        <v>37.789432730498135</v>
+      </c>
+      <c r="D719" s="4">
+        <v>38.592688385821603</v>
+      </c>
+    </row>
+    <row r="720" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A720" s="1">
+        <v>46111.916666666664</v>
+      </c>
+      <c r="B720" s="4">
+        <v>31.297643866905798</v>
+      </c>
+      <c r="C720" s="4">
+        <v>37.684200943840878</v>
+      </c>
+      <c r="D720" s="4">
+        <v>38.525001400373725</v>
+      </c>
+    </row>
+    <row r="721" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A721" s="1">
+        <v>46111.958333333336</v>
+      </c>
+      <c r="B721" s="4">
+        <v>31.300837408579309</v>
+      </c>
+      <c r="C721" s="4">
+        <v>37.648669359419081</v>
+      </c>
+      <c r="D721" s="4">
+        <v>38.4638228503458</v>
+      </c>
+    </row>
+    <row r="722" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A722" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B722" s="4">
+        <v>31.238932559887569</v>
+      </c>
+      <c r="C722" s="4">
+        <v>37.604942120446097</v>
+      </c>
+      <c r="D722" s="4">
+        <v>38.396159525890454</v>
+      </c>
+    </row>
+    <row r="723" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A723" s="1">
+        <v>46112.041666666664</v>
+      </c>
+      <c r="B723" s="4">
+        <v>31.304438239903675</v>
+      </c>
+      <c r="C723" s="4">
+        <v>37.621146106719969</v>
+      </c>
+      <c r="D723" s="4">
+        <v>38.461108255003815</v>
+      </c>
+    </row>
+    <row r="724" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A724" s="1">
+        <v>46112.083333333336</v>
+      </c>
+      <c r="B724" s="4">
+        <v>31.339589059507695</v>
+      </c>
+      <c r="C724" s="4">
+        <v>37.660677401224774</v>
+      </c>
+      <c r="D724" s="4">
+        <v>38.479273934910438</v>
+      </c>
+    </row>
+    <row r="725" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A725" s="1">
+        <v>46112.125</v>
+      </c>
+      <c r="B725" s="4">
+        <v>31.335530542604854</v>
+      </c>
+      <c r="C725" s="4">
+        <v>37.616015651490954</v>
+      </c>
+      <c r="D725" s="4">
+        <v>38.442289944671046</v>
+      </c>
+    </row>
+    <row r="726" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A726" s="1">
+        <v>46112.166666666664</v>
+      </c>
+      <c r="B726" s="4">
+        <v>31.310208527247109</v>
+      </c>
+      <c r="C726" s="4">
+        <v>37.582370413674248</v>
+      </c>
+      <c r="D726" s="4">
+        <v>38.401538462737797</v>
+      </c>
+    </row>
+    <row r="727" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A727" s="1">
+        <v>46112.208333333336</v>
+      </c>
+      <c r="B727" s="4">
+        <v>31.269375101725259</v>
+      </c>
+      <c r="C727" s="4">
+        <v>37.552082920074461</v>
+      </c>
+      <c r="D727" s="4">
+        <v>38.37121125211884</v>
+      </c>
+    </row>
+    <row r="728" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A728" s="1">
+        <v>46112.25</v>
+      </c>
+      <c r="B728" s="4">
+        <v>31.214583365122476</v>
+      </c>
+      <c r="C728" s="4">
+        <v>37.516562541325889</v>
+      </c>
+      <c r="D728" s="4">
+        <v>38.334883365021035</v>
+      </c>
+    </row>
+    <row r="729" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A729" s="1">
+        <v>46112.291666666664</v>
+      </c>
+      <c r="B729" s="4">
+        <v>31.183958768844604</v>
+      </c>
+      <c r="C729" s="4">
+        <v>37.488229552904762</v>
+      </c>
+      <c r="D729" s="4">
+        <v>38.306704313168197</v>
       </c>
     </row>
   </sheetData>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="64" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54FA4B75-2B6B-43E4-8CE4-A773D1471A0E}"/>
+  <xr:revisionPtr revIDLastSave="66" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D69F05-C7D7-47E5-8410-8C820C77C984}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D729"/>
+  <dimension ref="A1:D740"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -10649,6 +10649,160 @@
         <v>38.306704313168197</v>
       </c>
     </row>
+    <row r="730" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A730" s="1">
+        <v>46112.333333333336</v>
+      </c>
+      <c r="B730" s="4">
+        <v>31.182458629608153</v>
+      </c>
+      <c r="C730" s="4">
+        <v>37.496546434133478</v>
+      </c>
+      <c r="D730" s="4">
+        <v>38.329079308444278</v>
+      </c>
+    </row>
+    <row r="731" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A731" s="1">
+        <v>46112.375</v>
+      </c>
+      <c r="B731" s="4">
+        <v>31.208062348365782</v>
+      </c>
+      <c r="C731" s="4">
+        <v>37.524308348924684</v>
+      </c>
+      <c r="D731" s="4">
+        <v>38.420637569116231</v>
+      </c>
+    </row>
+    <row r="732" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A732" s="1">
+        <v>46112.416666666664</v>
+      </c>
+      <c r="B732" s="4">
+        <v>31.295521235466005</v>
+      </c>
+      <c r="C732" s="4">
+        <v>37.622558706778065</v>
+      </c>
+      <c r="D732" s="4">
+        <v>38.48687648902775</v>
+      </c>
+    </row>
+    <row r="733" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A733" s="1">
+        <v>46112.458333333336</v>
+      </c>
+      <c r="B733" s="4">
+        <v>31.354107332229614</v>
+      </c>
+      <c r="C733" s="4">
+        <v>37.674085567615656</v>
+      </c>
+      <c r="D733" s="4">
+        <v>38.555087509766508</v>
+      </c>
+    </row>
+    <row r="734" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A734" s="1">
+        <v>46112.5</v>
+      </c>
+      <c r="B734" s="4">
+        <v>31.41651816368103</v>
+      </c>
+      <c r="C734" s="4">
+        <v>37.760851336216582</v>
+      </c>
+      <c r="D734" s="4">
+        <v>38.631667152194261</v>
+      </c>
+    </row>
+    <row r="735" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A735" s="1">
+        <v>46112.541666666664</v>
+      </c>
+      <c r="B735" s="4">
+        <v>31.517444210052489</v>
+      </c>
+      <c r="C735" s="4">
+        <v>37.826318491138693</v>
+      </c>
+      <c r="D735" s="4">
+        <v>38.70343227439114</v>
+      </c>
+    </row>
+    <row r="736" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A736" s="1">
+        <v>46112.583333333336</v>
+      </c>
+      <c r="B736" s="4">
+        <v>31.509373626130998</v>
+      </c>
+      <c r="C736" s="4">
+        <v>37.850173674689401</v>
+      </c>
+      <c r="D736" s="4">
+        <v>38.754771462330197</v>
+      </c>
+    </row>
+    <row r="737" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A737" s="1">
+        <v>46112.625</v>
+      </c>
+      <c r="B737" s="4">
+        <v>31.580682144743026</v>
+      </c>
+      <c r="C737" s="4">
+        <v>37.940312480926515</v>
+      </c>
+      <c r="D737" s="4">
+        <v>38.769285867479113</v>
+      </c>
+    </row>
+    <row r="738" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A738" s="1">
+        <v>46112.666666666664</v>
+      </c>
+      <c r="B738" s="4">
+        <v>31.669375197092691</v>
+      </c>
+      <c r="C738" s="4">
+        <v>38.006684271494549</v>
+      </c>
+      <c r="D738" s="4">
+        <v>38.685357184578329</v>
+      </c>
+    </row>
+    <row r="739" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A739" s="1">
+        <v>46112.708333333336</v>
+      </c>
+      <c r="B739" s="4">
+        <v>31.715694665908813</v>
+      </c>
+      <c r="C739" s="4">
+        <v>38.067691001892086</v>
+      </c>
+      <c r="D739" s="4">
+        <v>38.724238346631473</v>
+      </c>
+    </row>
+    <row r="740" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A740" s="1">
+        <v>46112.75</v>
+      </c>
+      <c r="B740" s="4">
+        <v>31.672916873296103</v>
+      </c>
+      <c r="C740" s="4">
+        <v>38.039974552288385</v>
+      </c>
+      <c r="D740" s="4">
+        <v>38.703362648899855</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="66" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D2D69F05-C7D7-47E5-8410-8C820C77C984}"/>
+  <xr:revisionPtr revIDLastSave="68" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB40DA91-75B5-4AC8-880E-2C8AC16F48E8}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-16560" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -434,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D740"/>
+  <dimension ref="A1:D762"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -10797,10 +10797,318 @@
         <v>31.672916873296103</v>
       </c>
       <c r="C740" s="4">
-        <v>38.039974552288385</v>
+        <v>38.039506707872661</v>
       </c>
       <c r="D740" s="4">
         <v>38.703362648899855</v>
+      </c>
+    </row>
+    <row r="741" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A741" s="1">
+        <v>46112.791666666664</v>
+      </c>
+      <c r="B741" s="4">
+        <v>31.643680667877199</v>
+      </c>
+      <c r="C741" s="4">
+        <v>38.041766569727947</v>
+      </c>
+      <c r="D741" s="4">
+        <v>38.665188738321277</v>
+      </c>
+    </row>
+    <row r="742" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A742" s="1">
+        <v>46112.833333333336</v>
+      </c>
+      <c r="B742" s="4">
+        <v>31.534674963633215</v>
+      </c>
+      <c r="C742" s="4">
+        <v>37.967043956120811</v>
+      </c>
+      <c r="D742" s="4">
+        <v>38.615688970274164</v>
+      </c>
+    </row>
+    <row r="743" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A743" s="1">
+        <v>46112.875</v>
+      </c>
+      <c r="B743" s="4">
+        <v>31.460741844495136</v>
+      </c>
+      <c r="C743" s="4">
+        <v>37.863758794466655</v>
+      </c>
+      <c r="D743" s="4">
+        <v>38.515678978759595</v>
+      </c>
+    </row>
+    <row r="744" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A744" s="1">
+        <v>46112.916666666664</v>
+      </c>
+      <c r="B744" s="4">
+        <v>31.443545249688665</v>
+      </c>
+      <c r="C744" s="4">
+        <v>37.81106176862157</v>
+      </c>
+      <c r="D744" s="4">
+        <v>38.399967375396024</v>
+      </c>
+    </row>
+    <row r="745" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A745" s="1">
+        <v>46112.958333333336</v>
+      </c>
+      <c r="B745" s="4">
+        <v>31.454069455233018</v>
+      </c>
+      <c r="C745" s="4">
+        <v>37.821506571679947</v>
+      </c>
+      <c r="D745" s="4">
+        <v>38.391371246119107</v>
+      </c>
+    </row>
+    <row r="746" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A746" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B746" s="4">
+        <v>31.468636231268608</v>
+      </c>
+      <c r="C746" s="4">
+        <v>37.798541577657062</v>
+      </c>
+      <c r="D746" s="4">
+        <v>38.383903432374289</v>
+      </c>
+    </row>
+    <row r="747" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A747" s="1">
+        <v>46113.041666666664</v>
+      </c>
+      <c r="B747" s="4">
+        <v>31.414375066757202</v>
+      </c>
+      <c r="C747" s="4">
+        <v>37.725989627838132</v>
+      </c>
+      <c r="D747" s="4">
+        <v>38.320543015475963</v>
+      </c>
+    </row>
+    <row r="748" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A748" s="1">
+        <v>46113.083333333336</v>
+      </c>
+      <c r="B748" s="4">
+        <v>31.365125292142231</v>
+      </c>
+      <c r="C748" s="4">
+        <v>37.677351988686453</v>
+      </c>
+      <c r="D748" s="4">
+        <v>38.312664137254359</v>
+      </c>
+    </row>
+    <row r="749" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A749" s="1">
+        <v>46113.125</v>
+      </c>
+      <c r="B749" s="4">
+        <v>31.399041857719421</v>
+      </c>
+      <c r="C749" s="4">
+        <v>37.672350460217324</v>
+      </c>
+      <c r="D749" s="4">
+        <v>38.289127062708907</v>
+      </c>
+    </row>
+    <row r="750" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A750" s="1">
+        <v>46113.166666666664</v>
+      </c>
+      <c r="B750" s="4">
+        <v>31.387083464198643</v>
+      </c>
+      <c r="C750" s="4">
+        <v>37.668682738881053</v>
+      </c>
+      <c r="D750" s="4">
+        <v>38.272254388017146</v>
+      </c>
+    </row>
+    <row r="751" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A751" s="1">
+        <v>46113.208333333336</v>
+      </c>
+      <c r="B751" s="4">
+        <v>31.362708523538377</v>
+      </c>
+      <c r="C751" s="4">
+        <v>37.647396119435626</v>
+      </c>
+      <c r="D751" s="4">
+        <v>38.251111726833329</v>
+      </c>
+    </row>
+    <row r="752" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A752" s="1">
+        <v>46113.25</v>
+      </c>
+      <c r="B752" s="4">
+        <v>31.315104436874389</v>
+      </c>
+      <c r="C752" s="4">
+        <v>37.611354192097984</v>
+      </c>
+      <c r="D752" s="4">
+        <v>38.276399330309019</v>
+      </c>
+    </row>
+    <row r="753" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A753" s="1">
+        <v>46113.291666666664</v>
+      </c>
+      <c r="B753" s="4">
+        <v>31.263907565616424</v>
+      </c>
+      <c r="C753" s="4">
+        <v>37.558502092903197</v>
+      </c>
+      <c r="D753" s="4">
+        <v>38.229370587664256</v>
+      </c>
+    </row>
+    <row r="754" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A754" s="1">
+        <v>46113.333333333336</v>
+      </c>
+      <c r="B754" s="4">
+        <v>31.260710233506703</v>
+      </c>
+      <c r="C754" s="4">
+        <v>37.570451386227866</v>
+      </c>
+      <c r="D754" s="4">
+        <v>38.229759998752968</v>
+      </c>
+    </row>
+    <row r="755" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A755" s="1">
+        <v>46113.375</v>
+      </c>
+      <c r="B755" s="4">
+        <v>31.265486081441242</v>
+      </c>
+      <c r="C755" s="4">
+        <v>37.627812290191649</v>
+      </c>
+      <c r="D755" s="4">
+        <v>38.256855406195669</v>
+      </c>
+    </row>
+    <row r="756" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A756" s="1">
+        <v>46113.416666666664</v>
+      </c>
+      <c r="B756" s="4">
+        <v>31.355700135548908</v>
+      </c>
+      <c r="C756" s="4">
+        <v>37.670930584271751</v>
+      </c>
+      <c r="D756" s="4">
+        <v>38.308709017893669</v>
+      </c>
+    </row>
+    <row r="757" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A757" s="1">
+        <v>46113.458333333336</v>
+      </c>
+      <c r="B757" s="4">
+        <v>31.364300067901613</v>
+      </c>
+      <c r="C757" s="4">
+        <v>37.683968166510262</v>
+      </c>
+      <c r="D757" s="4">
+        <v>38.360556007101003</v>
+      </c>
+    </row>
+    <row r="758" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A758" s="1">
+        <v>46113.5</v>
+      </c>
+      <c r="B758" s="4">
+        <v>31.448805335362753</v>
+      </c>
+      <c r="C758" s="4">
+        <v>37.756728581587474</v>
+      </c>
+      <c r="D758" s="4">
+        <v>38.441717505234273</v>
+      </c>
+    </row>
+    <row r="759" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A759" s="1">
+        <v>46113.541666666664</v>
+      </c>
+      <c r="B759" s="4">
+        <v>31.563833265304567</v>
+      </c>
+      <c r="C759" s="4">
+        <v>37.871601621309914</v>
+      </c>
+      <c r="D759" s="4">
+        <v>38.533781800204501</v>
+      </c>
+    </row>
+    <row r="760" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A760" s="1">
+        <v>46113.583333333336</v>
+      </c>
+      <c r="B760" s="4">
+        <v>31.635037222886698</v>
+      </c>
+      <c r="C760" s="4">
+        <v>37.919797178904219</v>
+      </c>
+      <c r="D760" s="4">
+        <v>38.600524844278432</v>
+      </c>
+    </row>
+    <row r="761" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A761" s="1">
+        <v>46113.625</v>
+      </c>
+      <c r="B761" s="4">
+        <v>31.750656887506828</v>
+      </c>
+      <c r="C761" s="4">
+        <v>38.014681787490844</v>
+      </c>
+      <c r="D761" s="4">
+        <v>38.68166828700938</v>
+      </c>
+    </row>
+    <row r="762" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A762" s="1">
+        <v>46113.666666666664</v>
+      </c>
+      <c r="B762" s="4">
+        <v>31.833541627724966</v>
+      </c>
+      <c r="C762" s="4">
+        <v>38.129512903425429</v>
+      </c>
+      <c r="D762" s="4">
+        <v>38.772703769217436</v>
       </c>
     </row>
   </sheetData>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="68" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB40DA91-75B5-4AC8-880E-2C8AC16F48E8}"/>
+  <xr:revisionPtr revIDLastSave="70" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DEFCDB-4F4D-40D5-B0A4-E5A8D44D2790}"/>
   <bookViews>
     <workbookView xWindow="-16560" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -111,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D762"/>
+  <dimension ref="A1:D903"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -11111,6 +11107,1980 @@
         <v>38.772703769217436</v>
       </c>
     </row>
+    <row r="763" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A763" s="1">
+        <v>46113.708333333336</v>
+      </c>
+      <c r="B763" s="4">
+        <v>31.849166568120321</v>
+      </c>
+      <c r="C763" s="4">
+        <v>38.159392462836372</v>
+      </c>
+      <c r="D763" s="4">
+        <v>38.819658411739752</v>
+      </c>
+    </row>
+    <row r="764" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A764" s="1">
+        <v>46113.75</v>
+      </c>
+      <c r="B764" s="4">
+        <v>31.784147905580927</v>
+      </c>
+      <c r="C764" s="4">
+        <v>38.105810855683828</v>
+      </c>
+      <c r="D764" s="4">
+        <v>38.751473345574823</v>
+      </c>
+    </row>
+    <row r="765" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A765" s="1">
+        <v>46113.791666666664</v>
+      </c>
+      <c r="B765" s="4">
+        <v>31.739803321175764</v>
+      </c>
+      <c r="C765" s="4">
+        <v>38.088509610039843</v>
+      </c>
+      <c r="D765" s="4">
+        <v>38.747010167169826</v>
+      </c>
+    </row>
+    <row r="766" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A766" s="1">
+        <v>46113.833333333336</v>
+      </c>
+      <c r="B766" s="4">
+        <v>31.687646438394275</v>
+      </c>
+      <c r="C766" s="4">
+        <v>38.039169301986696</v>
+      </c>
+      <c r="D766" s="4">
+        <v>38.721620416149364</v>
+      </c>
+    </row>
+    <row r="767" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A767" s="1">
+        <v>46113.875</v>
+      </c>
+      <c r="B767" s="4">
+        <v>31.610564331213634</v>
+      </c>
+      <c r="C767" s="4">
+        <v>37.973541069030759</v>
+      </c>
+      <c r="D767" s="4">
+        <v>38.666772947458945</v>
+      </c>
+    </row>
+    <row r="768" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A768" s="1">
+        <v>46113.916666666664</v>
+      </c>
+      <c r="B768" s="4">
+        <v>31.557156803029955</v>
+      </c>
+      <c r="C768" s="4">
+        <v>37.909062067667641</v>
+      </c>
+      <c r="D768" s="4">
+        <v>38.571369372133503</v>
+      </c>
+    </row>
+    <row r="769" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A769" s="1">
+        <v>46113.958333333336</v>
+      </c>
+      <c r="B769" s="4">
+        <v>31.539778989734074</v>
+      </c>
+      <c r="C769" s="4">
+        <v>37.862968408493771</v>
+      </c>
+      <c r="D769" s="4">
+        <v>38.49543036394568</v>
+      </c>
+    </row>
+    <row r="770" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A770" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B770" s="4">
+        <v>31.565069405237832</v>
+      </c>
+      <c r="C770" s="4">
+        <v>37.881041658492315</v>
+      </c>
+      <c r="D770" s="4">
+        <v>38.485627068595818</v>
+      </c>
+    </row>
+    <row r="771" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A771" s="1">
+        <v>46114.041666666664</v>
+      </c>
+      <c r="B771" s="4">
+        <v>31.531692606210708</v>
+      </c>
+      <c r="C771" s="4">
+        <v>37.851693524254692</v>
+      </c>
+      <c r="D771" s="4">
+        <v>38.511389076516039</v>
+      </c>
+    </row>
+    <row r="772" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A772" s="1">
+        <v>46114.083333333336</v>
+      </c>
+      <c r="B772" s="4">
+        <v>31.514223741292952</v>
+      </c>
+      <c r="C772" s="4">
+        <v>37.85546259839311</v>
+      </c>
+      <c r="D772" s="4">
+        <v>38.504329468489338</v>
+      </c>
+    </row>
+    <row r="773" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A773" s="1">
+        <v>46114.125</v>
+      </c>
+      <c r="B773" s="4">
+        <v>31.484916880925496</v>
+      </c>
+      <c r="C773" s="4">
+        <v>37.816698927757066</v>
+      </c>
+      <c r="D773" s="4">
+        <v>38.464384442674607</v>
+      </c>
+    </row>
+    <row r="774" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A774" s="1">
+        <v>46114.166666666664</v>
+      </c>
+      <c r="B774" s="4">
+        <v>31.474028158187867</v>
+      </c>
+      <c r="C774" s="4">
+        <v>37.775990009307861</v>
+      </c>
+      <c r="D774" s="4">
+        <v>38.417820342593508</v>
+      </c>
+    </row>
+    <row r="775" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A775" s="1">
+        <v>46114.208333333336</v>
+      </c>
+      <c r="B775" s="4">
+        <v>31.463628947734833</v>
+      </c>
+      <c r="C775" s="4">
+        <v>37.798020394643146</v>
+      </c>
+      <c r="D775" s="4">
+        <v>38.42044359696591</v>
+      </c>
+    </row>
+    <row r="776" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A776" s="1">
+        <v>46114.25</v>
+      </c>
+      <c r="B776" s="4">
+        <v>31.470870566935766</v>
+      </c>
+      <c r="C776" s="4">
+        <v>37.797656599680586</v>
+      </c>
+      <c r="D776" s="4">
+        <v>38.407268850157834</v>
+      </c>
+    </row>
+    <row r="777" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A777" s="1">
+        <v>46114.291666666664</v>
+      </c>
+      <c r="B777" s="4">
+        <v>31.375176705128304</v>
+      </c>
+      <c r="C777" s="4">
+        <v>37.738169742765876</v>
+      </c>
+      <c r="D777" s="4">
+        <v>38.387014467655945</v>
+      </c>
+    </row>
+    <row r="778" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A778" s="1">
+        <v>46114.333333333336</v>
+      </c>
+      <c r="B778" s="4">
+        <v>31.326504705570365</v>
+      </c>
+      <c r="C778" s="4">
+        <v>37.67766373043969</v>
+      </c>
+      <c r="D778" s="4">
+        <v>38.328355819713387</v>
+      </c>
+    </row>
+    <row r="779" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A779" s="1">
+        <v>46114.375</v>
+      </c>
+      <c r="B779" s="4">
+        <v>31.287057060003281</v>
+      </c>
+      <c r="C779" s="4">
+        <v>37.625499986012777</v>
+      </c>
+      <c r="D779" s="4">
+        <v>38.311114714621212</v>
+      </c>
+    </row>
+    <row r="780" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A780" s="1">
+        <v>46114.416666666664</v>
+      </c>
+      <c r="B780" s="4">
+        <v>31.323671728372574</v>
+      </c>
+      <c r="C780" s="4">
+        <v>37.719771022796628</v>
+      </c>
+      <c r="D780" s="4">
+        <v>38.376669394703839</v>
+      </c>
+    </row>
+    <row r="781" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A781" s="1">
+        <v>46114.458333333336</v>
+      </c>
+      <c r="B781" s="4">
+        <v>31.409062353769936</v>
+      </c>
+      <c r="C781" s="4">
+        <v>37.772801342010496</v>
+      </c>
+      <c r="D781" s="4">
+        <v>38.468954549467185</v>
+      </c>
+    </row>
+    <row r="782" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A782" s="1">
+        <v>46114.5</v>
+      </c>
+      <c r="B782" s="4">
+        <v>31.492291482289634</v>
+      </c>
+      <c r="C782" s="4">
+        <v>37.826978858311968</v>
+      </c>
+      <c r="D782" s="4">
+        <v>38.517489154144869</v>
+      </c>
+    </row>
+    <row r="783" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A783" s="1">
+        <v>46114.541666666664</v>
+      </c>
+      <c r="B783" s="4">
+        <v>31.593263875113593</v>
+      </c>
+      <c r="C783" s="4">
+        <v>37.91285388628642</v>
+      </c>
+      <c r="D783" s="4">
+        <v>38.57927563613562</v>
+      </c>
+    </row>
+    <row r="784" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A784" s="1">
+        <v>46114.583333333336</v>
+      </c>
+      <c r="B784" s="4">
+        <v>31.624246000865149</v>
+      </c>
+      <c r="C784" s="4">
+        <v>37.921720002492272</v>
+      </c>
+      <c r="D784" s="4">
+        <v>38.607752794605503</v>
+      </c>
+    </row>
+    <row r="785" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A785" s="1">
+        <v>46114.625</v>
+      </c>
+      <c r="B785" s="4">
+        <v>31.638219068163917</v>
+      </c>
+      <c r="C785" s="4">
+        <v>37.91492697397868</v>
+      </c>
+      <c r="D785" s="4">
+        <v>38.601346229408392</v>
+      </c>
+    </row>
+    <row r="786" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A786" s="1">
+        <v>46114.666666666664</v>
+      </c>
+      <c r="B786" s="4">
+        <v>31.701979414621988</v>
+      </c>
+      <c r="C786" s="4">
+        <v>37.959398616888585</v>
+      </c>
+      <c r="D786" s="4">
+        <v>38.628597035344519</v>
+      </c>
+    </row>
+    <row r="787" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A787" s="1">
+        <v>46114.708333333336</v>
+      </c>
+      <c r="B787" s="4">
+        <v>31.715323026718632</v>
+      </c>
+      <c r="C787" s="4">
+        <v>38.003393747867683</v>
+      </c>
+      <c r="D787" s="4">
+        <v>38.656295067174987</v>
+      </c>
+    </row>
+    <row r="788" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A788" s="1">
+        <v>46114.75</v>
+      </c>
+      <c r="B788" s="4">
+        <v>31.686249125621419</v>
+      </c>
+      <c r="C788" s="4">
+        <v>38.002192378766608</v>
+      </c>
+      <c r="D788" s="4">
+        <v>38.671631243093884</v>
+      </c>
+    </row>
+    <row r="789" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A789" s="1">
+        <v>46114.791666666664</v>
+      </c>
+      <c r="B789" s="4">
+        <v>31.674052377180622</v>
+      </c>
+      <c r="C789" s="4">
+        <v>37.989760604771703</v>
+      </c>
+      <c r="D789" s="4">
+        <v>38.645790878790351</v>
+      </c>
+    </row>
+    <row r="790" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A790" s="1">
+        <v>46114.833333333336</v>
+      </c>
+      <c r="B790" s="4">
+        <v>31.686307282881305</v>
+      </c>
+      <c r="C790" s="4">
+        <v>38.013636589661616</v>
+      </c>
+      <c r="D790" s="4">
+        <v>38.668437745886578</v>
+      </c>
+    </row>
+    <row r="791" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A791" s="1">
+        <v>46114.875</v>
+      </c>
+      <c r="B791" s="4">
+        <v>31.679318607214725</v>
+      </c>
+      <c r="C791" s="4">
+        <v>38.043763940063592</v>
+      </c>
+      <c r="D791" s="4">
+        <v>38.699820219209109</v>
+      </c>
+    </row>
+    <row r="792" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A792" s="1">
+        <v>46114.916666666664</v>
+      </c>
+      <c r="B792" s="4">
+        <v>31.670208009084067</v>
+      </c>
+      <c r="C792" s="4">
+        <v>38.038356024878368</v>
+      </c>
+      <c r="D792" s="4">
+        <v>38.677578002619946</v>
+      </c>
+    </row>
+    <row r="793" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A793" s="1">
+        <v>46114.958333333336</v>
+      </c>
+      <c r="B793" s="4">
+        <v>31.628593583901722</v>
+      </c>
+      <c r="C793" s="4">
+        <v>37.966572891871131</v>
+      </c>
+      <c r="D793" s="4">
+        <v>38.600867404846319</v>
+      </c>
+    </row>
+    <row r="794" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A794" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B794" s="4">
+        <v>31.522007056077321</v>
+      </c>
+      <c r="C794" s="4">
+        <v>37.894416662851967</v>
+      </c>
+      <c r="D794" s="4">
+        <v>38.551397207978653</v>
+      </c>
+    </row>
+    <row r="795" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A795" s="1">
+        <v>46115.041666666664</v>
+      </c>
+      <c r="B795" s="4">
+        <v>31.47606650988261</v>
+      </c>
+      <c r="C795" s="4">
+        <v>37.832847065395782</v>
+      </c>
+      <c r="D795" s="4">
+        <v>38.492349006143399</v>
+      </c>
+    </row>
+    <row r="796" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A796" s="1">
+        <v>46115.083333333336</v>
+      </c>
+      <c r="B796" s="4">
+        <v>31.482916927337648</v>
+      </c>
+      <c r="C796" s="4">
+        <v>37.85183991326226</v>
+      </c>
+      <c r="D796" s="4">
+        <v>38.483120227047316</v>
+      </c>
+    </row>
+    <row r="797" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A797" s="1">
+        <v>46115.125</v>
+      </c>
+      <c r="B797" s="4">
+        <v>31.501958382924396</v>
+      </c>
+      <c r="C797" s="4">
+        <v>37.839965131547714</v>
+      </c>
+      <c r="D797" s="4">
+        <v>38.469471616961741</v>
+      </c>
+    </row>
+    <row r="798" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A798" s="1">
+        <v>46115.166666666664</v>
+      </c>
+      <c r="B798" s="4">
+        <v>31.508596953286066</v>
+      </c>
+      <c r="C798" s="4">
+        <v>37.835902934604221</v>
+      </c>
+      <c r="D798" s="4">
+        <v>38.452103496293937</v>
+      </c>
+    </row>
+    <row r="799" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A799" s="1">
+        <v>46115.208333333336</v>
+      </c>
+      <c r="B799" s="4">
+        <v>31.471041472752891</v>
+      </c>
+      <c r="C799" s="4">
+        <v>37.83414183298747</v>
+      </c>
+      <c r="D799" s="4">
+        <v>38.459414534494279</v>
+      </c>
+    </row>
+    <row r="800" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A800" s="1">
+        <v>46115.25</v>
+      </c>
+      <c r="B800" s="4">
+        <v>31.427396019299824</v>
+      </c>
+      <c r="C800" s="4">
+        <v>37.767007773717246</v>
+      </c>
+      <c r="D800" s="4">
+        <v>38.432913533511929</v>
+      </c>
+    </row>
+    <row r="801" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A801" s="1">
+        <v>46115.291666666664</v>
+      </c>
+      <c r="B801" s="4">
+        <v>31.464271299044292</v>
+      </c>
+      <c r="C801" s="4">
+        <v>37.832132318692324</v>
+      </c>
+      <c r="D801" s="4">
+        <v>38.496924793172994</v>
+      </c>
+    </row>
+    <row r="802" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A802" s="1">
+        <v>46115.333333333336</v>
+      </c>
+      <c r="B802" s="4">
+        <v>31.489118160936567</v>
+      </c>
+      <c r="C802" s="4">
+        <v>37.893506065596881</v>
+      </c>
+      <c r="D802" s="4">
+        <v>38.512326006852568</v>
+      </c>
+    </row>
+    <row r="803" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A803" s="1">
+        <v>46115.375</v>
+      </c>
+      <c r="B803" s="4">
+        <v>31.516163218021394</v>
+      </c>
+      <c r="C803" s="4">
+        <v>37.910207737816705</v>
+      </c>
+      <c r="D803" s="4">
+        <v>38.552645131177272</v>
+      </c>
+    </row>
+    <row r="804" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A804" s="1">
+        <v>46115.416666666664</v>
+      </c>
+      <c r="B804" s="4">
+        <v>31.54043400949902</v>
+      </c>
+      <c r="C804" s="4">
+        <v>37.949100884524256</v>
+      </c>
+      <c r="D804" s="4">
+        <v>38.616017795242023</v>
+      </c>
+    </row>
+    <row r="805" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A805" s="1">
+        <v>46115.458333333336</v>
+      </c>
+      <c r="B805" s="4">
+        <v>31.604931248558891</v>
+      </c>
+      <c r="C805" s="4">
+        <v>37.994687984928945</v>
+      </c>
+      <c r="D805" s="4">
+        <v>38.665121346678418</v>
+      </c>
+    </row>
+    <row r="806" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A806" s="1">
+        <v>46115.5</v>
+      </c>
+      <c r="B806" s="4">
+        <v>31.757900535143339</v>
+      </c>
+      <c r="C806" s="4">
+        <v>38.12388973916066</v>
+      </c>
+      <c r="D806" s="4">
+        <v>38.777685737815517</v>
+      </c>
+    </row>
+    <row r="807" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A807" s="1">
+        <v>46115.541666666664</v>
+      </c>
+      <c r="B807" s="4">
+        <v>31.868349429888607</v>
+      </c>
+      <c r="C807" s="4">
+        <v>38.218467618904867</v>
+      </c>
+      <c r="D807" s="4">
+        <v>38.869128588188204</v>
+      </c>
+    </row>
+    <row r="808" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A808" s="1">
+        <v>46115.583333333336</v>
+      </c>
+      <c r="B808" s="4">
+        <v>31.899999618530273</v>
+      </c>
+      <c r="C808" s="4">
+        <v>38.243121495701018</v>
+      </c>
+      <c r="D808" s="4">
+        <v>38.915016462183878</v>
+      </c>
+    </row>
+    <row r="809" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A809" s="1">
+        <v>46115.625</v>
+      </c>
+      <c r="B809" s="4">
+        <v>31.895306062698364</v>
+      </c>
+      <c r="C809" s="4">
+        <v>38.21333733354296</v>
+      </c>
+      <c r="D809" s="4">
+        <v>38.903698598371726</v>
+      </c>
+    </row>
+    <row r="810" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A810" s="1">
+        <v>46115.666666666664</v>
+      </c>
+      <c r="B810" s="4">
+        <v>31.887818431854249</v>
+      </c>
+      <c r="C810" s="4">
+        <v>38.193932224909467</v>
+      </c>
+      <c r="D810" s="4">
+        <v>38.885069986111795</v>
+      </c>
+    </row>
+    <row r="811" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A811" s="1">
+        <v>46115.708333333336</v>
+      </c>
+      <c r="B811" s="4">
+        <v>31.907708231608073</v>
+      </c>
+      <c r="C811" s="4">
+        <v>38.184765863418576</v>
+      </c>
+      <c r="D811" s="4">
+        <v>38.839594849728698</v>
+      </c>
+    </row>
+    <row r="812" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A812" s="1">
+        <v>46115.75</v>
+      </c>
+      <c r="B812" s="4">
+        <v>31.834125130971273</v>
+      </c>
+      <c r="C812" s="4">
+        <v>38.134330529433029</v>
+      </c>
+      <c r="D812" s="4">
+        <v>38.779910386031887</v>
+      </c>
+    </row>
+    <row r="813" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A813" s="1">
+        <v>46115.791666666664</v>
+      </c>
+      <c r="B813" s="4">
+        <v>31.69837540626526</v>
+      </c>
+      <c r="C813" s="4">
+        <v>38.033096291957754</v>
+      </c>
+      <c r="D813" s="4">
+        <v>38.668244506787154</v>
+      </c>
+    </row>
+    <row r="814" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A814" s="1">
+        <v>46115.833333333336</v>
+      </c>
+      <c r="B814" s="4">
+        <v>31.631232877572376</v>
+      </c>
+      <c r="C814" s="4">
+        <v>37.943946297168729</v>
+      </c>
+      <c r="D814" s="4">
+        <v>38.620750797213653</v>
+      </c>
+    </row>
+    <row r="815" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A815" s="1">
+        <v>46115.875</v>
+      </c>
+      <c r="B815" s="4">
+        <v>31.592885132630666</v>
+      </c>
+      <c r="C815" s="4">
+        <v>37.928626541296644</v>
+      </c>
+      <c r="D815" s="4">
+        <v>38.550154552839729</v>
+      </c>
+    </row>
+    <row r="816" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A816" s="1">
+        <v>46115.916666666664</v>
+      </c>
+      <c r="B816" s="4">
+        <v>31.593510704774122</v>
+      </c>
+      <c r="C816" s="4">
+        <v>37.922140594231074</v>
+      </c>
+      <c r="D816" s="4">
+        <v>38.552211239749411</v>
+      </c>
+    </row>
+    <row r="817" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A817" s="1">
+        <v>46115.958333333336</v>
+      </c>
+      <c r="B817" s="4">
+        <v>31.6213305974618</v>
+      </c>
+      <c r="C817" s="4">
+        <v>37.948118643058365</v>
+      </c>
+      <c r="D817" s="4">
+        <v>38.553083915410063</v>
+      </c>
+    </row>
+    <row r="818" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A818" s="1">
+        <v>46116</v>
+      </c>
+      <c r="B818" s="4">
+        <v>31.612129969067045</v>
+      </c>
+      <c r="C818" s="4">
+        <v>37.948654037051732</v>
+      </c>
+      <c r="D818" s="4">
+        <v>38.566995913790372</v>
+      </c>
+    </row>
+    <row r="819" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A819" s="1">
+        <v>46116.041666666664</v>
+      </c>
+      <c r="B819" s="4">
+        <v>31.610996124479506</v>
+      </c>
+      <c r="C819" s="4">
+        <v>37.943398985787049</v>
+      </c>
+      <c r="D819" s="4">
+        <v>38.591719004095069</v>
+      </c>
+    </row>
+    <row r="820" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A820" s="1">
+        <v>46116.083333333336</v>
+      </c>
+      <c r="B820" s="4">
+        <v>31.589270734786986</v>
+      </c>
+      <c r="C820" s="4">
+        <v>37.913545331500821</v>
+      </c>
+      <c r="D820" s="4">
+        <v>38.55496039682523</v>
+      </c>
+    </row>
+    <row r="821" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A821" s="1">
+        <v>46116.125</v>
+      </c>
+      <c r="B821" s="4">
+        <v>31.554160372416177</v>
+      </c>
+      <c r="C821" s="4">
+        <v>37.876671835581462</v>
+      </c>
+      <c r="D821" s="4">
+        <v>38.529355815541109</v>
+      </c>
+    </row>
+    <row r="822" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A822" s="1">
+        <v>46116.166666666664</v>
+      </c>
+      <c r="B822" s="4">
+        <v>31.489508538775972</v>
+      </c>
+      <c r="C822" s="4">
+        <v>37.810393061864943</v>
+      </c>
+      <c r="D822" s="4">
+        <v>38.463324450575243</v>
+      </c>
+    </row>
+    <row r="823" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A823" s="1">
+        <v>46116.208333333336</v>
+      </c>
+      <c r="B823" s="4">
+        <v>31.46322091344803</v>
+      </c>
+      <c r="C823" s="4">
+        <v>37.770849876998874</v>
+      </c>
+      <c r="D823" s="4">
+        <v>38.440926199107693</v>
+      </c>
+    </row>
+    <row r="824" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A824" s="1">
+        <v>46116.25</v>
+      </c>
+      <c r="B824" s="4">
+        <v>31.41411717278617</v>
+      </c>
+      <c r="C824" s="4">
+        <v>37.759656143501665</v>
+      </c>
+      <c r="D824" s="4">
+        <v>38.397608414711939</v>
+      </c>
+    </row>
+    <row r="825" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A825" s="1">
+        <v>46116.291666666664</v>
+      </c>
+      <c r="B825" s="4">
+        <v>31.377923014669708</v>
+      </c>
+      <c r="C825" s="4">
+        <v>37.747913109915601</v>
+      </c>
+      <c r="D825" s="4">
+        <v>38.385309699209145</v>
+      </c>
+    </row>
+    <row r="826" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A826" s="1">
+        <v>46116.333333333336</v>
+      </c>
+      <c r="B826" s="4">
+        <v>31.379924214969982</v>
+      </c>
+      <c r="C826" s="4">
+        <v>37.754771156311037</v>
+      </c>
+      <c r="D826" s="4">
+        <v>38.416517322525586</v>
+      </c>
+    </row>
+    <row r="827" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A827" s="1">
+        <v>46116.375</v>
+      </c>
+      <c r="B827" s="4">
+        <v>31.404872113007766</v>
+      </c>
+      <c r="C827" s="4">
+        <v>37.789267480638294</v>
+      </c>
+      <c r="D827" s="4">
+        <v>38.477363801148201</v>
+      </c>
+    </row>
+    <row r="828" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A828" s="1">
+        <v>46116.416666666664</v>
+      </c>
+      <c r="B828" s="4">
+        <v>31.465197731626681</v>
+      </c>
+      <c r="C828" s="4">
+        <v>37.857795361412897</v>
+      </c>
+      <c r="D828" s="4">
+        <v>38.534107540240576</v>
+      </c>
+    </row>
+    <row r="829" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A829" s="1">
+        <v>46116.458333333336</v>
+      </c>
+      <c r="B829" s="4">
+        <v>31.569166849277636</v>
+      </c>
+      <c r="C829" s="4">
+        <v>37.962010620117184</v>
+      </c>
+      <c r="D829" s="4">
+        <v>38.624081995837216</v>
+      </c>
+    </row>
+    <row r="830" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A830" s="1">
+        <v>46116.5</v>
+      </c>
+      <c r="B830" s="4">
+        <v>31.658472500907049</v>
+      </c>
+      <c r="C830" s="4">
+        <v>38.054604277928675</v>
+      </c>
+      <c r="D830" s="4">
+        <v>38.759557535537638</v>
+      </c>
+    </row>
+    <row r="831" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A831" s="1">
+        <v>46116.541666666664</v>
+      </c>
+      <c r="B831" s="4">
+        <v>31.740327353704544</v>
+      </c>
+      <c r="C831" s="4">
+        <v>38.132499806086223</v>
+      </c>
+      <c r="D831" s="4">
+        <v>38.812122653164558</v>
+      </c>
+    </row>
+    <row r="832" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A832" s="1">
+        <v>46116.583333333336</v>
+      </c>
+      <c r="B832" s="4">
+        <v>31.774880811146325</v>
+      </c>
+      <c r="C832" s="4">
+        <v>38.137813107172647</v>
+      </c>
+      <c r="D832" s="4">
+        <v>38.818603970031255</v>
+      </c>
+    </row>
+    <row r="833" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A833" s="1">
+        <v>46116.625</v>
+      </c>
+      <c r="B833" s="4">
+        <v>31.817976170494443</v>
+      </c>
+      <c r="C833" s="4">
+        <v>38.148072417577104</v>
+      </c>
+      <c r="D833" s="4">
+        <v>38.846968316969274</v>
+      </c>
+    </row>
+    <row r="834" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A834" s="1">
+        <v>46116.666666666664</v>
+      </c>
+      <c r="B834" s="4">
+        <v>31.879107080187115</v>
+      </c>
+      <c r="C834" s="4">
+        <v>38.200787367644139</v>
+      </c>
+      <c r="D834" s="4">
+        <v>38.892867807684276</v>
+      </c>
+    </row>
+    <row r="835" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A835" s="1">
+        <v>46116.708333333336</v>
+      </c>
+      <c r="B835" s="4">
+        <v>31.889374611112807</v>
+      </c>
+      <c r="C835" s="4">
+        <v>38.188421515005601</v>
+      </c>
+      <c r="D835" s="4">
+        <v>38.870077448267054</v>
+      </c>
+    </row>
+    <row r="836" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A836" s="1">
+        <v>46116.75</v>
+      </c>
+      <c r="B836" s="4">
+        <v>31.820291974809436</v>
+      </c>
+      <c r="C836" s="4">
+        <v>38.144229799906412</v>
+      </c>
+      <c r="D836" s="4">
+        <v>38.814759090803321</v>
+      </c>
+    </row>
+    <row r="837" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A837" s="1">
+        <v>46116.791666666664</v>
+      </c>
+      <c r="B837" s="4">
+        <v>31.777161937289769</v>
+      </c>
+      <c r="C837" s="4">
+        <v>38.104565595697473</v>
+      </c>
+      <c r="D837" s="4">
+        <v>38.763748217996984</v>
+      </c>
+    </row>
+    <row r="838" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A838" s="1">
+        <v>46116.833333333336</v>
+      </c>
+      <c r="B838" s="4">
+        <v>31.699143494500053</v>
+      </c>
+      <c r="C838" s="4">
+        <v>38.02464239685623</v>
+      </c>
+      <c r="D838" s="4">
+        <v>38.698266538776103</v>
+      </c>
+    </row>
+    <row r="839" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A839" s="1">
+        <v>46116.875</v>
+      </c>
+      <c r="B839" s="4">
+        <v>31.693084694045819</v>
+      </c>
+      <c r="C839" s="4">
+        <v>37.986713631947836</v>
+      </c>
+      <c r="D839" s="4">
+        <v>38.644539202136649</v>
+      </c>
+    </row>
+    <row r="840" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A840" s="1">
+        <v>46116.916666666664</v>
+      </c>
+      <c r="B840" s="4">
+        <v>31.661944261625703</v>
+      </c>
+      <c r="C840" s="4">
+        <v>37.985693911350133</v>
+      </c>
+      <c r="D840" s="4">
+        <v>38.603783659985446</v>
+      </c>
+    </row>
+    <row r="841" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A841" s="1">
+        <v>46116.958333333336</v>
+      </c>
+      <c r="B841" s="4">
+        <v>31.639689600039752</v>
+      </c>
+      <c r="C841" s="4">
+        <v>37.954842937353888</v>
+      </c>
+      <c r="D841" s="4">
+        <v>38.582042688792939</v>
+      </c>
+    </row>
+    <row r="842" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A842" s="1">
+        <v>46117</v>
+      </c>
+      <c r="B842" s="4">
+        <v>31.591602459116878</v>
+      </c>
+      <c r="C842" s="4">
+        <v>37.902395584469751</v>
+      </c>
+      <c r="D842" s="4">
+        <v>38.547886385602865</v>
+      </c>
+    </row>
+    <row r="843" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A843" s="1">
+        <v>46117.041666666664</v>
+      </c>
+      <c r="B843" s="4">
+        <v>31.532732672161526</v>
+      </c>
+      <c r="C843" s="4">
+        <v>37.869166514987043</v>
+      </c>
+      <c r="D843" s="4">
+        <v>38.518818354840903</v>
+      </c>
+    </row>
+    <row r="844" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A844" s="1">
+        <v>46117.083333333336</v>
+      </c>
+      <c r="B844" s="4">
+        <v>31.523516798019408</v>
+      </c>
+      <c r="C844" s="4">
+        <v>37.835781447092693</v>
+      </c>
+      <c r="D844" s="4">
+        <v>38.498654685091751</v>
+      </c>
+    </row>
+    <row r="845" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A845" s="1">
+        <v>46117.125</v>
+      </c>
+      <c r="B845" s="4">
+        <v>31.502617211143175</v>
+      </c>
+      <c r="C845" s="4">
+        <v>37.816510465410019</v>
+      </c>
+      <c r="D845" s="4">
+        <v>38.464240037962945</v>
+      </c>
+    </row>
+    <row r="846" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A846" s="1">
+        <v>46117.166666666664</v>
+      </c>
+      <c r="B846" s="4">
+        <v>31.520674481590589</v>
+      </c>
+      <c r="C846" s="4">
+        <v>37.841666357252336</v>
+      </c>
+      <c r="D846" s="4">
+        <v>38.44996130396256</v>
+      </c>
+    </row>
+    <row r="847" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A847" s="1">
+        <v>46117.208333333336</v>
+      </c>
+      <c r="B847" s="4">
+        <v>31.558062559763592</v>
+      </c>
+      <c r="C847" s="4">
+        <v>37.880312137603759</v>
+      </c>
+      <c r="D847" s="4">
+        <v>38.461719960174904</v>
+      </c>
+    </row>
+    <row r="848" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A848" s="1">
+        <v>46117.25</v>
+      </c>
+      <c r="B848" s="4">
+        <v>31.502396154403687</v>
+      </c>
+      <c r="C848" s="4">
+        <v>37.862031269073483</v>
+      </c>
+      <c r="D848" s="4">
+        <v>38.506129287121844</v>
+      </c>
+    </row>
+    <row r="849" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A849" s="1">
+        <v>46117.291666666664</v>
+      </c>
+      <c r="B849" s="4">
+        <v>31.487500015894572</v>
+      </c>
+      <c r="C849" s="4">
+        <v>37.73020833333333</v>
+      </c>
+      <c r="D849" s="4">
+        <v>38.496333139902028</v>
+      </c>
+    </row>
+    <row r="850" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A850" s="1">
+        <v>46117.333333333336</v>
+      </c>
+      <c r="B850" s="4">
+        <v>31.509999720255532</v>
+      </c>
+      <c r="C850" s="4">
+        <v>36.26444910897149</v>
+      </c>
+      <c r="D850" s="4">
+        <v>37.126381542332389</v>
+      </c>
+    </row>
+    <row r="851" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A851" s="1">
+        <v>46117.375</v>
+      </c>
+      <c r="B851" s="4">
+        <v>31.537186325112284</v>
+      </c>
+      <c r="C851" s="4">
+        <v>37.426874955495201</v>
+      </c>
+      <c r="D851" s="4">
+        <v>37.802157549635972</v>
+      </c>
+    </row>
+    <row r="852" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A852" s="1">
+        <v>46117.416666666664</v>
+      </c>
+      <c r="B852" s="4">
+        <v>31.568980021225777</v>
+      </c>
+      <c r="C852" s="4">
+        <v>37.998333779970807</v>
+      </c>
+      <c r="D852" s="4">
+        <v>38.649530316532868</v>
+      </c>
+    </row>
+    <row r="853" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A853" s="1">
+        <v>46117.458333333336</v>
+      </c>
+      <c r="B853" s="4">
+        <v>31.649672626313706</v>
+      </c>
+      <c r="C853" s="4">
+        <v>38.075156455569797</v>
+      </c>
+      <c r="D853" s="4">
+        <v>38.758922431058252</v>
+      </c>
+    </row>
+    <row r="854" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A854" s="1">
+        <v>46117.5</v>
+      </c>
+      <c r="B854" s="4">
+        <v>31.741785789671397</v>
+      </c>
+      <c r="C854" s="4">
+        <v>38.161968572404646</v>
+      </c>
+      <c r="D854" s="4">
+        <v>38.828525617234305</v>
+      </c>
+    </row>
+    <row r="855" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A855" s="1">
+        <v>46117.541666666664</v>
+      </c>
+      <c r="B855" s="4">
+        <v>31.782083193461101</v>
+      </c>
+      <c r="C855" s="4">
+        <v>38.211885821024573</v>
+      </c>
+      <c r="D855" s="4">
+        <v>38.892508431629992</v>
+      </c>
+    </row>
+    <row r="856" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A856" s="1">
+        <v>46117.583333333336</v>
+      </c>
+      <c r="B856" s="4">
+        <v>31.861341509501141</v>
+      </c>
+      <c r="C856" s="4">
+        <v>38.230885616938274</v>
+      </c>
+      <c r="D856" s="4">
+        <v>38.929390572912453</v>
+      </c>
+    </row>
+    <row r="857" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A857" s="1">
+        <v>46117.625</v>
+      </c>
+      <c r="B857" s="4">
+        <v>31.944804547945658</v>
+      </c>
+      <c r="C857" s="4">
+        <v>38.293094148635866</v>
+      </c>
+      <c r="D857" s="4">
+        <v>38.953679328877712</v>
+      </c>
+    </row>
+    <row r="858" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A858" s="1">
+        <v>46117.666666666664</v>
+      </c>
+      <c r="B858" s="4">
+        <v>32.055728856722517</v>
+      </c>
+      <c r="C858" s="4">
+        <v>38.392322756449381</v>
+      </c>
+      <c r="D858" s="4">
+        <v>39.039307553468745</v>
+      </c>
+    </row>
+    <row r="859" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A859" s="1">
+        <v>46117.708333333336</v>
+      </c>
+      <c r="B859" s="4">
+        <v>32.079999446868896</v>
+      </c>
+      <c r="C859" s="4">
+        <v>38.39184908866882</v>
+      </c>
+      <c r="D859" s="4">
+        <v>39.045718857299313</v>
+      </c>
+    </row>
+    <row r="860" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A860" s="1">
+        <v>46117.75</v>
+      </c>
+      <c r="B860" s="4">
+        <v>32.001416231791175</v>
+      </c>
+      <c r="C860" s="4">
+        <v>38.329707104629939</v>
+      </c>
+      <c r="D860" s="4">
+        <v>38.959010099869559</v>
+      </c>
+    </row>
+    <row r="861" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A861" s="1">
+        <v>46117.791666666664</v>
+      </c>
+      <c r="B861" s="4">
+        <v>31.955011747678121</v>
+      </c>
+      <c r="C861" s="4">
+        <v>38.282519580258267</v>
+      </c>
+      <c r="D861" s="4">
+        <v>38.896068842940373</v>
+      </c>
+    </row>
+    <row r="862" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A862" s="1">
+        <v>46117.833333333336</v>
+      </c>
+      <c r="B862" s="4">
+        <v>31.910067086508782</v>
+      </c>
+      <c r="C862" s="4">
+        <v>38.226913873354597</v>
+      </c>
+      <c r="D862" s="4">
+        <v>38.857278010798225</v>
+      </c>
+    </row>
+    <row r="863" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A863" s="1">
+        <v>46117.875</v>
+      </c>
+      <c r="B863" s="4">
+        <v>31.86732320809605</v>
+      </c>
+      <c r="C863" s="4">
+        <v>38.180003079308406</v>
+      </c>
+      <c r="D863" s="4">
+        <v>38.797740428380074</v>
+      </c>
+    </row>
+    <row r="864" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A864" s="1">
+        <v>46117.916666666664</v>
+      </c>
+      <c r="B864" s="4">
+        <v>31.80297752883699</v>
+      </c>
+      <c r="C864" s="4">
+        <v>38.122935055021259</v>
+      </c>
+      <c r="D864" s="4">
+        <v>38.741890164441607</v>
+      </c>
+    </row>
+    <row r="865" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A865" s="1">
+        <v>46117.958333333336</v>
+      </c>
+      <c r="B865" s="4">
+        <v>31.761453101634981</v>
+      </c>
+      <c r="C865" s="4">
+        <v>38.068275704459538</v>
+      </c>
+      <c r="D865" s="4">
+        <v>38.730680598932068</v>
+      </c>
+    </row>
+    <row r="866" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A866" s="1">
+        <v>46118</v>
+      </c>
+      <c r="B866" s="4">
+        <v>31.716749785741172</v>
+      </c>
+      <c r="C866" s="4">
+        <v>38.020040850247732</v>
+      </c>
+      <c r="D866" s="4">
+        <v>38.670951134135251</v>
+      </c>
+    </row>
+    <row r="867" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A867" s="1">
+        <v>46118.041666666664</v>
+      </c>
+      <c r="B867" s="4">
+        <v>31.693611420525446</v>
+      </c>
+      <c r="C867" s="4">
+        <v>37.991697369278342</v>
+      </c>
+      <c r="D867" s="4">
+        <v>38.632926436034971</v>
+      </c>
+    </row>
+    <row r="868" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A868" s="1">
+        <v>46118.083333333336</v>
+      </c>
+      <c r="B868" s="4">
+        <v>31.667430761125352</v>
+      </c>
+      <c r="C868" s="4">
+        <v>37.969764915307366</v>
+      </c>
+      <c r="D868" s="4">
+        <v>38.607037100862399</v>
+      </c>
+    </row>
+    <row r="869" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A869" s="1">
+        <v>46118.125</v>
+      </c>
+      <c r="B869" s="4">
+        <v>31.630000283983019</v>
+      </c>
+      <c r="C869" s="4">
+        <v>37.928166688283284</v>
+      </c>
+      <c r="D869" s="4">
+        <v>38.570064126149241</v>
+      </c>
+    </row>
+    <row r="870" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A870" s="1">
+        <v>46118.166666666664</v>
+      </c>
+      <c r="B870" s="4">
+        <v>31.60246557659573</v>
+      </c>
+      <c r="C870" s="4">
+        <v>37.911232937706842</v>
+      </c>
+      <c r="D870" s="4">
+        <v>38.538414710362751</v>
+      </c>
+    </row>
+    <row r="871" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A871" s="1">
+        <v>46118.208333333336</v>
+      </c>
+      <c r="B871" s="4">
+        <v>31.579618257946439</v>
+      </c>
+      <c r="C871" s="4">
+        <v>37.91378479003906</v>
+      </c>
+      <c r="D871" s="4">
+        <v>38.529714444478351</v>
+      </c>
+    </row>
+    <row r="872" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A872" s="1">
+        <v>46118.25</v>
+      </c>
+      <c r="B872" s="4">
+        <v>31.574153877990419</v>
+      </c>
+      <c r="C872" s="4">
+        <v>37.894193039065094</v>
+      </c>
+      <c r="D872" s="4">
+        <v>38.523318847792595</v>
+      </c>
+    </row>
+    <row r="873" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A873" s="1">
+        <v>46118.291666666664</v>
+      </c>
+      <c r="B873" s="4">
+        <v>31.544990477125022</v>
+      </c>
+      <c r="C873" s="4">
+        <v>37.914738465290448</v>
+      </c>
+      <c r="D873" s="4">
+        <v>38.506349409951987</v>
+      </c>
+    </row>
+    <row r="874" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A874" s="1">
+        <v>46118.333333333336</v>
+      </c>
+      <c r="B874" s="4">
+        <v>31.585855934165771</v>
+      </c>
+      <c r="C874" s="4">
+        <v>37.953750085830691</v>
+      </c>
+      <c r="D874" s="4">
+        <v>38.586362141348452</v>
+      </c>
+    </row>
+    <row r="875" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A875" s="1">
+        <v>46118.375</v>
+      </c>
+      <c r="B875" s="4">
+        <v>31.635625267028807</v>
+      </c>
+      <c r="C875" s="4">
+        <v>38.001197687784831</v>
+      </c>
+      <c r="D875" s="4">
+        <v>38.669424658899572</v>
+      </c>
+    </row>
+    <row r="876" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A876" s="1">
+        <v>46118.416666666664</v>
+      </c>
+      <c r="B876" s="4">
+        <v>31.706250143051147</v>
+      </c>
+      <c r="C876" s="4">
+        <v>38.132343705495195</v>
+      </c>
+      <c r="D876" s="4">
+        <v>38.800246852575384</v>
+      </c>
+    </row>
+    <row r="877" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A877" s="1">
+        <v>46118.458333333336</v>
+      </c>
+      <c r="B877" s="4">
+        <v>31.864687466621398</v>
+      </c>
+      <c r="C877" s="4">
+        <v>38.281531149546304</v>
+      </c>
+      <c r="D877" s="4">
+        <v>38.919646438851473</v>
+      </c>
+    </row>
+    <row r="878" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A878" s="1">
+        <v>46118.5</v>
+      </c>
+      <c r="B878" s="4">
+        <v>31.954895536104839</v>
+      </c>
+      <c r="C878" s="4">
+        <v>38.39794870376587</v>
+      </c>
+      <c r="D878" s="4">
+        <v>38.994591087530097</v>
+      </c>
+    </row>
+    <row r="879" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A879" s="1">
+        <v>46118.541666666664</v>
+      </c>
+      <c r="B879" s="4">
+        <v>32.008020305633544</v>
+      </c>
+      <c r="C879" s="4">
+        <v>38.417135588328044</v>
+      </c>
+      <c r="D879" s="4">
+        <v>39.076109368180084</v>
+      </c>
+    </row>
+    <row r="880" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A880" s="1">
+        <v>46118.583333333336</v>
+      </c>
+      <c r="B880" s="4">
+        <v>32.033137541922969</v>
+      </c>
+      <c r="C880" s="4">
+        <v>38.423137871424359</v>
+      </c>
+      <c r="D880" s="4">
+        <v>39.055434336959166</v>
+      </c>
+    </row>
+    <row r="881" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A881" s="1">
+        <v>46118.625</v>
+      </c>
+      <c r="B881" s="4">
+        <v>32.044554837347313</v>
+      </c>
+      <c r="C881" s="4">
+        <v>38.396505519231155</v>
+      </c>
+      <c r="D881" s="4">
+        <v>39.021941473495694</v>
+      </c>
+    </row>
+    <row r="882" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A882" s="1">
+        <v>46118.666666666664</v>
+      </c>
+      <c r="B882" s="4">
+        <v>32.007737831842327</v>
+      </c>
+      <c r="C882" s="4">
+        <v>38.333976264317833</v>
+      </c>
+      <c r="D882" s="4">
+        <v>38.962906110746751</v>
+      </c>
+    </row>
+    <row r="883" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A883" s="1">
+        <v>46118.708333333336</v>
+      </c>
+      <c r="B883" s="4">
+        <v>32.074492638608312</v>
+      </c>
+      <c r="C883" s="4">
+        <v>38.365338055292767</v>
+      </c>
+      <c r="D883" s="4">
+        <v>38.964747014389602</v>
+      </c>
+    </row>
+    <row r="884" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A884" s="1">
+        <v>46118.75</v>
+      </c>
+      <c r="B884" s="4">
+        <v>32.031262934089163</v>
+      </c>
+      <c r="C884" s="4">
+        <v>38.34906959987822</v>
+      </c>
+      <c r="D884" s="4">
+        <v>38.924383322392679</v>
+      </c>
+    </row>
+    <row r="885" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A885" s="1">
+        <v>46118.791666666664</v>
+      </c>
+      <c r="B885" s="4">
+        <v>31.935374818378026</v>
+      </c>
+      <c r="C885" s="4">
+        <v>38.265461681910928</v>
+      </c>
+      <c r="D885" s="4">
+        <v>38.805387448393859</v>
+      </c>
+    </row>
+    <row r="886" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A886" s="1">
+        <v>46118.833333333336</v>
+      </c>
+      <c r="B886" s="4">
+        <v>31.923124621709189</v>
+      </c>
+      <c r="C886" s="4">
+        <v>38.250846118927001</v>
+      </c>
+      <c r="D886" s="4">
+        <v>38.796425249832446</v>
+      </c>
+    </row>
+    <row r="887" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A887" s="1">
+        <v>46118.875</v>
+      </c>
+      <c r="B887" s="4">
+        <v>31.893957932790119</v>
+      </c>
+      <c r="C887" s="4">
+        <v>38.187019596099852</v>
+      </c>
+      <c r="D887" s="4">
+        <v>38.76503796160894</v>
+      </c>
+    </row>
+    <row r="888" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A888" s="1">
+        <v>46118.916666666664</v>
+      </c>
+      <c r="B888" s="4">
+        <v>31.836927012602487</v>
+      </c>
+      <c r="C888" s="4">
+        <v>38.147708129882815</v>
+      </c>
+      <c r="D888" s="4">
+        <v>38.715663472143426</v>
+      </c>
+    </row>
+    <row r="889" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A889" s="1">
+        <v>46118.958333333336</v>
+      </c>
+      <c r="B889" s="4">
+        <v>31.800989631811778</v>
+      </c>
+      <c r="C889" s="4">
+        <v>38.085143121083576</v>
+      </c>
+      <c r="D889" s="4">
+        <v>38.684657025368928</v>
+      </c>
+    </row>
+    <row r="890" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A890" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B890" s="4">
+        <v>31.747291707992552</v>
+      </c>
+      <c r="C890" s="4">
+        <v>38.040231908162433</v>
+      </c>
+      <c r="D890" s="4">
+        <v>38.638023284640283</v>
+      </c>
+    </row>
+    <row r="891" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A891" s="1">
+        <v>46119.041666666664</v>
+      </c>
+      <c r="B891" s="4">
+        <v>31.732083606719971</v>
+      </c>
+      <c r="C891" s="4">
+        <v>38.029243329366047</v>
+      </c>
+      <c r="D891" s="4">
+        <v>38.618448845135049</v>
+      </c>
+    </row>
+    <row r="892" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A892" s="1">
+        <v>46119.083333333336</v>
+      </c>
+      <c r="B892" s="4">
+        <v>31.73663673400879</v>
+      </c>
+      <c r="C892" s="4">
+        <v>38.043819157282513</v>
+      </c>
+      <c r="D892" s="4">
+        <v>38.607787380691036</v>
+      </c>
+    </row>
+    <row r="893" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A893" s="1">
+        <v>46119.125</v>
+      </c>
+      <c r="B893" s="4">
+        <v>31.860515610376993</v>
+      </c>
+      <c r="C893" s="4">
+        <v>38.162665033340453</v>
+      </c>
+      <c r="D893" s="4">
+        <v>38.676612844406748</v>
+      </c>
+    </row>
+    <row r="894" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A894" s="1">
+        <v>46119.166666666664</v>
+      </c>
+      <c r="B894" s="4">
+        <v>31.872222455342612</v>
+      </c>
+      <c r="C894" s="4">
+        <v>38.182385667165121</v>
+      </c>
+      <c r="D894" s="4">
+        <v>38.744600901328717</v>
+      </c>
+    </row>
+    <row r="895" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A895" s="1">
+        <v>46119.208333333336</v>
+      </c>
+      <c r="B895" s="4">
+        <v>31.859166860580444</v>
+      </c>
+      <c r="C895" s="4">
+        <v>38.182774643670946</v>
+      </c>
+      <c r="D895" s="4">
+        <v>38.75499419233482</v>
+      </c>
+    </row>
+    <row r="896" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A896" s="1">
+        <v>46119.25</v>
+      </c>
+      <c r="B896" s="4">
+        <v>31.875</v>
+      </c>
+      <c r="C896" s="4">
+        <v>38.199359452156791</v>
+      </c>
+      <c r="D896" s="4">
+        <v>38.75434637376086</v>
+      </c>
+    </row>
+    <row r="897" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A897" s="1">
+        <v>46119.291666666664</v>
+      </c>
+      <c r="B897" s="4">
+        <v>31.831180047988891</v>
+      </c>
+      <c r="C897" s="4">
+        <v>38.181718977292377</v>
+      </c>
+      <c r="D897" s="4">
+        <v>38.71121773131356</v>
+      </c>
+    </row>
+    <row r="898" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A898" s="1">
+        <v>46119.333333333336</v>
+      </c>
+      <c r="B898" s="4">
+        <v>31.779600735505422</v>
+      </c>
+      <c r="C898" s="4">
+        <v>38.149109164151284</v>
+      </c>
+      <c r="D898" s="4">
+        <v>38.592661699146419</v>
+      </c>
+    </row>
+    <row r="899" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A899" s="1">
+        <v>46119.375</v>
+      </c>
+      <c r="B899" s="4">
+        <v>31.874635549386344</v>
+      </c>
+      <c r="C899" s="4">
+        <v>38.283650851972176</v>
+      </c>
+      <c r="D899" s="4">
+        <v>38.456244553631258</v>
+      </c>
+    </row>
+    <row r="900" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A900" s="1">
+        <v>46119.416666666664</v>
+      </c>
+      <c r="B900" s="4">
+        <v>32.102082602183025</v>
+      </c>
+      <c r="C900" s="4">
+        <v>38.515198294321699</v>
+      </c>
+      <c r="D900" s="4">
+        <v>38.383252471135378</v>
+      </c>
+    </row>
+    <row r="901" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A901" s="1">
+        <v>46119.458333333336</v>
+      </c>
+      <c r="B901" s="4">
+        <v>32.124791717529298</v>
+      </c>
+      <c r="C901" s="4">
+        <v>38.568759822845458</v>
+      </c>
+      <c r="D901" s="4">
+        <v>38.46647688814523</v>
+      </c>
+    </row>
+    <row r="902" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A902" s="1">
+        <v>46119.5</v>
+      </c>
+      <c r="B902" s="4">
+        <v>32.147999846140543</v>
+      </c>
+      <c r="C902" s="4">
+        <v>38.620547080039977</v>
+      </c>
+      <c r="D902" s="4">
+        <v>38.477683928689835</v>
+      </c>
+    </row>
+    <row r="903" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A903" s="1">
+        <v>46119.541666666664</v>
+      </c>
+      <c r="B903" s="4">
+        <v>32.172750263214112</v>
+      </c>
+      <c r="C903" s="4">
+        <v>38.628168066342674</v>
+      </c>
+      <c r="D903" s="4">
+        <v>38.506362652507548</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="70" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D3DEFCDB-4F4D-40D5-B0A4-E5A8D44D2790}"/>
+  <xr:revisionPtr revIDLastSave="72" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53287BEE-B80B-48E3-AD0D-477F29B0DE09}"/>
   <bookViews>
     <workbookView xWindow="-16560" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
@@ -111,6 +111,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -430,7 +434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D903"/>
+  <dimension ref="A1:D937"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -13081,6 +13085,482 @@
         <v>38.506362652507548</v>
       </c>
     </row>
+    <row r="904" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A904" s="1">
+        <v>46119.583333333336</v>
+      </c>
+      <c r="B904" s="4">
+        <v>32.220291169484454</v>
+      </c>
+      <c r="C904" s="4">
+        <v>38.666492493947345</v>
+      </c>
+      <c r="D904" s="4">
+        <v>38.580102258757179</v>
+      </c>
+    </row>
+    <row r="905" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A905" s="1">
+        <v>46119.625</v>
+      </c>
+      <c r="B905" s="4">
+        <v>32.221511414993643</v>
+      </c>
+      <c r="C905" s="4">
+        <v>38.664074577548639</v>
+      </c>
+      <c r="D905" s="4">
+        <v>38.545399744562445</v>
+      </c>
+    </row>
+    <row r="906" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A906" s="1">
+        <v>46119.666666666664</v>
+      </c>
+      <c r="B906" s="4">
+        <v>32.271117947529227</v>
+      </c>
+      <c r="C906" s="4">
+        <v>38.694413643090058</v>
+      </c>
+      <c r="D906" s="4">
+        <v>38.543887786359491</v>
+      </c>
+    </row>
+    <row r="907" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A907" s="1">
+        <v>46119.708333333336</v>
+      </c>
+      <c r="B907" s="4">
+        <v>32.248661422948722</v>
+      </c>
+      <c r="C907" s="4">
+        <v>38.661180326673723</v>
+      </c>
+      <c r="D907" s="4">
+        <v>38.518073369705043</v>
+      </c>
+    </row>
+    <row r="908" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A908" s="1">
+        <v>46119.75</v>
+      </c>
+      <c r="B908" s="4">
+        <v>32.149958299001057</v>
+      </c>
+      <c r="C908" s="4">
+        <v>38.536391079425812</v>
+      </c>
+      <c r="D908" s="4">
+        <v>38.425548247565409</v>
+      </c>
+    </row>
+    <row r="909" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A909" s="1">
+        <v>46119.791666666664</v>
+      </c>
+      <c r="B909" s="4">
+        <v>32.064583333333331</v>
+      </c>
+      <c r="C909" s="4">
+        <v>38.400647946198781</v>
+      </c>
+      <c r="D909" s="4">
+        <v>38.295954228738943</v>
+      </c>
+    </row>
+    <row r="910" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A910" s="1">
+        <v>46119.833333333336</v>
+      </c>
+      <c r="B910" s="4">
+        <v>32.02708333333333</v>
+      </c>
+      <c r="C910" s="4">
+        <v>38.353390990770777</v>
+      </c>
+      <c r="D910" s="4">
+        <v>38.20188406403183</v>
+      </c>
+    </row>
+    <row r="911" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A911" s="1">
+        <v>46119.875</v>
+      </c>
+      <c r="B911" s="4">
+        <v>31.946041981379192</v>
+      </c>
+      <c r="C911" s="4">
+        <v>38.284241860602805</v>
+      </c>
+      <c r="D911" s="4">
+        <v>38.121467589154634</v>
+      </c>
+    </row>
+    <row r="912" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A912" s="1">
+        <v>46119.916666666664</v>
+      </c>
+      <c r="B912" s="4">
+        <v>31.943268940998959</v>
+      </c>
+      <c r="C912" s="4">
+        <v>38.276804601578483</v>
+      </c>
+      <c r="D912" s="4">
+        <v>38.103749656588903</v>
+      </c>
+    </row>
+    <row r="913" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A913" s="1">
+        <v>46119.958333333336</v>
+      </c>
+      <c r="B913" s="4">
+        <v>31.955518788131279</v>
+      </c>
+      <c r="C913" s="4">
+        <v>38.260313002268475</v>
+      </c>
+      <c r="D913" s="4">
+        <v>38.094744016860204</v>
+      </c>
+    </row>
+    <row r="914" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A914" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B914" s="4">
+        <v>31.933433423917116</v>
+      </c>
+      <c r="C914" s="4">
+        <v>38.267733997768829</v>
+      </c>
+      <c r="D914" s="4">
+        <v>38.093182990623866</v>
+      </c>
+    </row>
+    <row r="915" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A915" s="1">
+        <v>46120.041666666664</v>
+      </c>
+      <c r="B915" s="4">
+        <v>31.992818901273939</v>
+      </c>
+      <c r="C915" s="4">
+        <v>38.291125558923788</v>
+      </c>
+      <c r="D915" s="4">
+        <v>38.112049130275516</v>
+      </c>
+    </row>
+    <row r="916" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A916" s="1">
+        <v>46120.083333333336</v>
+      </c>
+      <c r="B916" s="4">
+        <v>31.98245882458157</v>
+      </c>
+      <c r="C916" s="4">
+        <v>38.292337177417892</v>
+      </c>
+      <c r="D916" s="4">
+        <v>38.100528302894148</v>
+      </c>
+    </row>
+    <row r="917" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A917" s="1">
+        <v>46120.125</v>
+      </c>
+      <c r="B917" s="4">
+        <v>31.963500403298273</v>
+      </c>
+      <c r="C917" s="4">
+        <v>38.299478832880659</v>
+      </c>
+      <c r="D917" s="4">
+        <v>38.109377526876628</v>
+      </c>
+    </row>
+    <row r="918" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A918" s="1">
+        <v>46120.166666666664</v>
+      </c>
+      <c r="B918" s="4">
+        <v>31.978583024342853</v>
+      </c>
+      <c r="C918" s="4">
+        <v>38.285780784818861</v>
+      </c>
+      <c r="D918" s="4">
+        <v>38.134497518194628</v>
+      </c>
+    </row>
+    <row r="919" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A919" s="1">
+        <v>46120.208333333336</v>
+      </c>
+      <c r="B919" s="4">
+        <v>32.052939708144571</v>
+      </c>
+      <c r="C919" s="4">
+        <v>38.374952555949392</v>
+      </c>
+      <c r="D919" s="4">
+        <v>38.202579090441539</v>
+      </c>
+    </row>
+    <row r="920" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A920" s="1">
+        <v>46120.25</v>
+      </c>
+      <c r="B920" s="4">
+        <v>32.0339355080216</v>
+      </c>
+      <c r="C920" s="4">
+        <v>38.358850594439538</v>
+      </c>
+      <c r="D920" s="4">
+        <v>38.214936927757655</v>
+      </c>
+    </row>
+    <row r="921" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A921" s="1">
+        <v>46120.291666666664</v>
+      </c>
+      <c r="B921" s="4">
+        <v>32.003750324249268</v>
+      </c>
+      <c r="C921" s="4">
+        <v>38.332046224806042</v>
+      </c>
+      <c r="D921" s="4">
+        <v>38.163540503438249</v>
+      </c>
+    </row>
+    <row r="922" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A922" s="1">
+        <v>46120.333333333336</v>
+      </c>
+      <c r="B922" s="4">
+        <v>31.954270188013712</v>
+      </c>
+      <c r="C922" s="4">
+        <v>38.328369685664327</v>
+      </c>
+      <c r="D922" s="4">
+        <v>38.184994694611603</v>
+      </c>
+    </row>
+    <row r="923" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A923" s="1">
+        <v>46120.375</v>
+      </c>
+      <c r="B923" s="4">
+        <v>31.936561902364094</v>
+      </c>
+      <c r="C923" s="4">
+        <v>38.353727863774161</v>
+      </c>
+      <c r="D923" s="4">
+        <v>38.234863195564863</v>
+      </c>
+    </row>
+    <row r="924" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A924" s="1">
+        <v>46120.416666666664</v>
+      </c>
+      <c r="B924" s="4">
+        <v>32.041093476613362</v>
+      </c>
+      <c r="C924" s="4">
+        <v>38.452908229827884</v>
+      </c>
+      <c r="D924" s="4">
+        <v>38.311775352462888</v>
+      </c>
+    </row>
+    <row r="925" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A925" s="1">
+        <v>46120.458333333336</v>
+      </c>
+      <c r="B925" s="4">
+        <v>32.132449229558311</v>
+      </c>
+      <c r="C925" s="4">
+        <v>38.5673285929362</v>
+      </c>
+      <c r="D925" s="4">
+        <v>38.460701745527757</v>
+      </c>
+    </row>
+    <row r="926" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A926" s="1">
+        <v>46120.5</v>
+      </c>
+      <c r="B926" s="4">
+        <v>32.212648526058402</v>
+      </c>
+      <c r="C926" s="4">
+        <v>38.672555478413898</v>
+      </c>
+      <c r="D926" s="4">
+        <v>38.56987072441008</v>
+      </c>
+    </row>
+    <row r="927" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A927" s="1">
+        <v>46120.541666666664</v>
+      </c>
+      <c r="B927" s="4">
+        <v>32.240541397154679</v>
+      </c>
+      <c r="C927" s="4">
+        <v>38.711560495694478</v>
+      </c>
+      <c r="D927" s="4">
+        <v>38.626097052858569</v>
+      </c>
+    </row>
+    <row r="928" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A928" s="1">
+        <v>46120.583333333336</v>
+      </c>
+      <c r="B928" s="4">
+        <v>32.237019401941545</v>
+      </c>
+      <c r="C928" s="4">
+        <v>38.697311131159466</v>
+      </c>
+      <c r="D928" s="4">
+        <v>38.741187020745656</v>
+      </c>
+    </row>
+    <row r="929" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A929" s="1">
+        <v>46120.625</v>
+      </c>
+      <c r="B929" s="4">
+        <v>32.21758870624361</v>
+      </c>
+      <c r="C929" s="4">
+        <v>38.668838889458598</v>
+      </c>
+      <c r="D929" s="4">
+        <v>38.595910232291466</v>
+      </c>
+    </row>
+    <row r="930" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A930" s="1">
+        <v>46120.666666666664</v>
+      </c>
+      <c r="B930" s="4">
+        <v>32.290286049615766</v>
+      </c>
+      <c r="C930" s="4">
+        <v>38.702857679212123</v>
+      </c>
+      <c r="D930" s="4">
+        <v>38.629592780533422</v>
+      </c>
+    </row>
+    <row r="931" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A931" s="1">
+        <v>46120.708333333336</v>
+      </c>
+      <c r="B931" s="4">
+        <v>32.323236468633013</v>
+      </c>
+      <c r="C931" s="4">
+        <v>38.712835080283028</v>
+      </c>
+      <c r="D931" s="4">
+        <v>38.6354749246129</v>
+      </c>
+    </row>
+    <row r="932" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A932" s="1">
+        <v>46120.75</v>
+      </c>
+      <c r="B932" s="4">
+        <v>32.295348342259722</v>
+      </c>
+      <c r="C932" s="4">
+        <v>38.677114601135251</v>
+      </c>
+      <c r="D932" s="4">
+        <v>38.587118103156911</v>
+      </c>
+    </row>
+    <row r="933" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A933" s="1">
+        <v>46120.791666666664</v>
+      </c>
+      <c r="B933" s="4">
+        <v>32.255013208919102</v>
+      </c>
+      <c r="C933" s="4">
+        <v>38.595459996178036</v>
+      </c>
+      <c r="D933" s="4">
+        <v>38.516631905618901</v>
+      </c>
+    </row>
+    <row r="934" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A934" s="1">
+        <v>46120.833333333336</v>
+      </c>
+      <c r="B934" s="4">
+        <v>32.202499357859296</v>
+      </c>
+      <c r="C934" s="4">
+        <v>38.544196623847597</v>
+      </c>
+      <c r="D934" s="4">
+        <v>38.427302595360729</v>
+      </c>
+    </row>
+    <row r="935" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A935" s="1">
+        <v>46120.875</v>
+      </c>
+      <c r="B935" s="4">
+        <v>32.21552012761434</v>
+      </c>
+      <c r="C935" s="4">
+        <v>38.522395247504825</v>
+      </c>
+      <c r="D935" s="4">
+        <v>38.369019430852781</v>
+      </c>
+    </row>
+    <row r="936" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A936" s="1">
+        <v>46120.916666666664</v>
+      </c>
+      <c r="B936" s="4">
+        <v>32.158874969482419</v>
+      </c>
+      <c r="C936" s="4">
+        <v>38.484899040975876</v>
+      </c>
+      <c r="D936" s="4">
+        <v>38.338132215294181</v>
+      </c>
+    </row>
+    <row r="937" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A937" s="1">
+        <v>46120.958333333336</v>
+      </c>
+      <c r="B937" s="4">
+        <v>32.153984389671912</v>
+      </c>
+      <c r="C937" s="4">
+        <v>38.467610822327288</v>
+      </c>
+      <c r="D937" s="4">
+        <v>38.309453325824087</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="72" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{53287BEE-B80B-48E3-AD0D-477F29B0DE09}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CA11160-D68B-4AFB-BD9C-B12386F57111}"/>
   <bookViews>
-    <workbookView xWindow="-16560" yWindow="-103" windowWidth="16663" windowHeight="8863" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12890,676 +12890,292 @@
       </c>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A890" s="1">
-        <v>46119</v>
-      </c>
-      <c r="B890" s="4">
-        <v>31.747291707992552</v>
-      </c>
-      <c r="C890" s="4">
-        <v>38.040231908162433</v>
-      </c>
-      <c r="D890" s="4">
-        <v>38.638023284640283</v>
-      </c>
+      <c r="A890" s="1"/>
+      <c r="B890" s="4"/>
+      <c r="C890" s="4"/>
+      <c r="D890" s="4"/>
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A891" s="1">
-        <v>46119.041666666664</v>
-      </c>
-      <c r="B891" s="4">
-        <v>31.732083606719971</v>
-      </c>
-      <c r="C891" s="4">
-        <v>38.029243329366047</v>
-      </c>
-      <c r="D891" s="4">
-        <v>38.618448845135049</v>
-      </c>
+      <c r="A891" s="1"/>
+      <c r="B891" s="4"/>
+      <c r="C891" s="4"/>
+      <c r="D891" s="4"/>
     </row>
     <row r="892" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A892" s="1">
-        <v>46119.083333333336</v>
-      </c>
-      <c r="B892" s="4">
-        <v>31.73663673400879</v>
-      </c>
-      <c r="C892" s="4">
-        <v>38.043819157282513</v>
-      </c>
-      <c r="D892" s="4">
-        <v>38.607787380691036</v>
-      </c>
+      <c r="A892" s="1"/>
+      <c r="B892" s="4"/>
+      <c r="C892" s="4"/>
+      <c r="D892" s="4"/>
     </row>
     <row r="893" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A893" s="1">
-        <v>46119.125</v>
-      </c>
-      <c r="B893" s="4">
-        <v>31.860515610376993</v>
-      </c>
-      <c r="C893" s="4">
-        <v>38.162665033340453</v>
-      </c>
-      <c r="D893" s="4">
-        <v>38.676612844406748</v>
-      </c>
+      <c r="A893" s="1"/>
+      <c r="B893" s="4"/>
+      <c r="C893" s="4"/>
+      <c r="D893" s="4"/>
     </row>
     <row r="894" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A894" s="1">
-        <v>46119.166666666664</v>
-      </c>
-      <c r="B894" s="4">
-        <v>31.872222455342612</v>
-      </c>
-      <c r="C894" s="4">
-        <v>38.182385667165121</v>
-      </c>
-      <c r="D894" s="4">
-        <v>38.744600901328717</v>
-      </c>
+      <c r="A894" s="1"/>
+      <c r="B894" s="4"/>
+      <c r="C894" s="4"/>
+      <c r="D894" s="4"/>
     </row>
     <row r="895" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A895" s="1">
-        <v>46119.208333333336</v>
-      </c>
-      <c r="B895" s="4">
-        <v>31.859166860580444</v>
-      </c>
-      <c r="C895" s="4">
-        <v>38.182774643670946</v>
-      </c>
-      <c r="D895" s="4">
-        <v>38.75499419233482</v>
-      </c>
+      <c r="A895" s="1"/>
+      <c r="B895" s="4"/>
+      <c r="C895" s="4"/>
+      <c r="D895" s="4"/>
     </row>
     <row r="896" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A896" s="1">
-        <v>46119.25</v>
-      </c>
-      <c r="B896" s="4">
-        <v>31.875</v>
-      </c>
-      <c r="C896" s="4">
-        <v>38.199359452156791</v>
-      </c>
-      <c r="D896" s="4">
-        <v>38.75434637376086</v>
-      </c>
+      <c r="A896" s="1"/>
+      <c r="B896" s="4"/>
+      <c r="C896" s="4"/>
+      <c r="D896" s="4"/>
     </row>
     <row r="897" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A897" s="1">
-        <v>46119.291666666664</v>
-      </c>
-      <c r="B897" s="4">
-        <v>31.831180047988891</v>
-      </c>
-      <c r="C897" s="4">
-        <v>38.181718977292377</v>
-      </c>
-      <c r="D897" s="4">
-        <v>38.71121773131356</v>
-      </c>
+      <c r="A897" s="1"/>
+      <c r="B897" s="4"/>
+      <c r="C897" s="4"/>
+      <c r="D897" s="4"/>
     </row>
     <row r="898" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A898" s="1">
-        <v>46119.333333333336</v>
-      </c>
-      <c r="B898" s="4">
-        <v>31.779600735505422</v>
-      </c>
-      <c r="C898" s="4">
-        <v>38.149109164151284</v>
-      </c>
-      <c r="D898" s="4">
-        <v>38.592661699146419</v>
-      </c>
+      <c r="A898" s="1"/>
+      <c r="B898" s="4"/>
+      <c r="C898" s="4"/>
+      <c r="D898" s="4"/>
     </row>
     <row r="899" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A899" s="1">
-        <v>46119.375</v>
-      </c>
-      <c r="B899" s="4">
-        <v>31.874635549386344</v>
-      </c>
-      <c r="C899" s="4">
-        <v>38.283650851972176</v>
-      </c>
-      <c r="D899" s="4">
-        <v>38.456244553631258</v>
-      </c>
+      <c r="A899" s="1"/>
+      <c r="B899" s="4"/>
+      <c r="C899" s="4"/>
+      <c r="D899" s="4"/>
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A900" s="1">
-        <v>46119.416666666664</v>
-      </c>
-      <c r="B900" s="4">
-        <v>32.102082602183025</v>
-      </c>
-      <c r="C900" s="4">
-        <v>38.515198294321699</v>
-      </c>
-      <c r="D900" s="4">
-        <v>38.383252471135378</v>
-      </c>
+      <c r="A900" s="1"/>
+      <c r="B900" s="4"/>
+      <c r="C900" s="4"/>
+      <c r="D900" s="4"/>
     </row>
     <row r="901" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A901" s="1">
-        <v>46119.458333333336</v>
-      </c>
-      <c r="B901" s="4">
-        <v>32.124791717529298</v>
-      </c>
-      <c r="C901" s="4">
-        <v>38.568759822845458</v>
-      </c>
-      <c r="D901" s="4">
-        <v>38.46647688814523</v>
-      </c>
+      <c r="A901" s="1"/>
+      <c r="B901" s="4"/>
+      <c r="C901" s="4"/>
+      <c r="D901" s="4"/>
     </row>
     <row r="902" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A902" s="1">
-        <v>46119.5</v>
-      </c>
-      <c r="B902" s="4">
-        <v>32.147999846140543</v>
-      </c>
-      <c r="C902" s="4">
-        <v>38.620547080039977</v>
-      </c>
-      <c r="D902" s="4">
-        <v>38.477683928689835</v>
-      </c>
+      <c r="A902" s="1"/>
+      <c r="B902" s="4"/>
+      <c r="C902" s="4"/>
+      <c r="D902" s="4"/>
     </row>
     <row r="903" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A903" s="1">
-        <v>46119.541666666664</v>
-      </c>
-      <c r="B903" s="4">
-        <v>32.172750263214112</v>
-      </c>
-      <c r="C903" s="4">
-        <v>38.628168066342674</v>
-      </c>
-      <c r="D903" s="4">
-        <v>38.506362652507548</v>
-      </c>
+      <c r="A903" s="1"/>
+      <c r="B903" s="4"/>
+      <c r="C903" s="4"/>
+      <c r="D903" s="4"/>
     </row>
     <row r="904" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A904" s="1">
-        <v>46119.583333333336</v>
-      </c>
-      <c r="B904" s="4">
-        <v>32.220291169484454</v>
-      </c>
-      <c r="C904" s="4">
-        <v>38.666492493947345</v>
-      </c>
-      <c r="D904" s="4">
-        <v>38.580102258757179</v>
-      </c>
+      <c r="A904" s="1"/>
+      <c r="B904" s="4"/>
+      <c r="C904" s="4"/>
+      <c r="D904" s="4"/>
     </row>
     <row r="905" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A905" s="1">
-        <v>46119.625</v>
-      </c>
-      <c r="B905" s="4">
-        <v>32.221511414993643</v>
-      </c>
-      <c r="C905" s="4">
-        <v>38.664074577548639</v>
-      </c>
-      <c r="D905" s="4">
-        <v>38.545399744562445</v>
-      </c>
+      <c r="A905" s="1"/>
+      <c r="B905" s="4"/>
+      <c r="C905" s="4"/>
+      <c r="D905" s="4"/>
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A906" s="1">
-        <v>46119.666666666664</v>
-      </c>
-      <c r="B906" s="4">
-        <v>32.271117947529227</v>
-      </c>
-      <c r="C906" s="4">
-        <v>38.694413643090058</v>
-      </c>
-      <c r="D906" s="4">
-        <v>38.543887786359491</v>
-      </c>
+      <c r="A906" s="1"/>
+      <c r="B906" s="4"/>
+      <c r="C906" s="4"/>
+      <c r="D906" s="4"/>
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A907" s="1">
-        <v>46119.708333333336</v>
-      </c>
-      <c r="B907" s="4">
-        <v>32.248661422948722</v>
-      </c>
-      <c r="C907" s="4">
-        <v>38.661180326673723</v>
-      </c>
-      <c r="D907" s="4">
-        <v>38.518073369705043</v>
-      </c>
+      <c r="A907" s="1"/>
+      <c r="B907" s="4"/>
+      <c r="C907" s="4"/>
+      <c r="D907" s="4"/>
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A908" s="1">
-        <v>46119.75</v>
-      </c>
-      <c r="B908" s="4">
-        <v>32.149958299001057</v>
-      </c>
-      <c r="C908" s="4">
-        <v>38.536391079425812</v>
-      </c>
-      <c r="D908" s="4">
-        <v>38.425548247565409</v>
-      </c>
+      <c r="A908" s="1"/>
+      <c r="B908" s="4"/>
+      <c r="C908" s="4"/>
+      <c r="D908" s="4"/>
     </row>
     <row r="909" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A909" s="1">
-        <v>46119.791666666664</v>
-      </c>
-      <c r="B909" s="4">
-        <v>32.064583333333331</v>
-      </c>
-      <c r="C909" s="4">
-        <v>38.400647946198781</v>
-      </c>
-      <c r="D909" s="4">
-        <v>38.295954228738943</v>
-      </c>
+      <c r="A909" s="1"/>
+      <c r="B909" s="4"/>
+      <c r="C909" s="4"/>
+      <c r="D909" s="4"/>
     </row>
     <row r="910" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A910" s="1">
-        <v>46119.833333333336</v>
-      </c>
-      <c r="B910" s="4">
-        <v>32.02708333333333</v>
-      </c>
-      <c r="C910" s="4">
-        <v>38.353390990770777</v>
-      </c>
-      <c r="D910" s="4">
-        <v>38.20188406403183</v>
-      </c>
+      <c r="A910" s="1"/>
+      <c r="B910" s="4"/>
+      <c r="C910" s="4"/>
+      <c r="D910" s="4"/>
     </row>
     <row r="911" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A911" s="1">
-        <v>46119.875</v>
-      </c>
-      <c r="B911" s="4">
-        <v>31.946041981379192</v>
-      </c>
-      <c r="C911" s="4">
-        <v>38.284241860602805</v>
-      </c>
-      <c r="D911" s="4">
-        <v>38.121467589154634</v>
-      </c>
+      <c r="A911" s="1"/>
+      <c r="B911" s="4"/>
+      <c r="C911" s="4"/>
+      <c r="D911" s="4"/>
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A912" s="1">
-        <v>46119.916666666664</v>
-      </c>
-      <c r="B912" s="4">
-        <v>31.943268940998959</v>
-      </c>
-      <c r="C912" s="4">
-        <v>38.276804601578483</v>
-      </c>
-      <c r="D912" s="4">
-        <v>38.103749656588903</v>
-      </c>
+      <c r="A912" s="1"/>
+      <c r="B912" s="4"/>
+      <c r="C912" s="4"/>
+      <c r="D912" s="4"/>
     </row>
     <row r="913" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A913" s="1">
-        <v>46119.958333333336</v>
-      </c>
-      <c r="B913" s="4">
-        <v>31.955518788131279</v>
-      </c>
-      <c r="C913" s="4">
-        <v>38.260313002268475</v>
-      </c>
-      <c r="D913" s="4">
-        <v>38.094744016860204</v>
-      </c>
+      <c r="A913" s="1"/>
+      <c r="B913" s="4"/>
+      <c r="C913" s="4"/>
+      <c r="D913" s="4"/>
     </row>
     <row r="914" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A914" s="1">
-        <v>46120</v>
-      </c>
-      <c r="B914" s="4">
-        <v>31.933433423917116</v>
-      </c>
-      <c r="C914" s="4">
-        <v>38.267733997768829</v>
-      </c>
-      <c r="D914" s="4">
-        <v>38.093182990623866</v>
-      </c>
+      <c r="A914" s="1"/>
+      <c r="B914" s="4"/>
+      <c r="C914" s="4"/>
+      <c r="D914" s="4"/>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A915" s="1">
-        <v>46120.041666666664</v>
-      </c>
-      <c r="B915" s="4">
-        <v>31.992818901273939</v>
-      </c>
-      <c r="C915" s="4">
-        <v>38.291125558923788</v>
-      </c>
-      <c r="D915" s="4">
-        <v>38.112049130275516</v>
-      </c>
+      <c r="A915" s="1"/>
+      <c r="B915" s="4"/>
+      <c r="C915" s="4"/>
+      <c r="D915" s="4"/>
     </row>
     <row r="916" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A916" s="1">
-        <v>46120.083333333336</v>
-      </c>
-      <c r="B916" s="4">
-        <v>31.98245882458157</v>
-      </c>
-      <c r="C916" s="4">
-        <v>38.292337177417892</v>
-      </c>
-      <c r="D916" s="4">
-        <v>38.100528302894148</v>
-      </c>
+      <c r="A916" s="1"/>
+      <c r="B916" s="4"/>
+      <c r="C916" s="4"/>
+      <c r="D916" s="4"/>
     </row>
     <row r="917" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A917" s="1">
-        <v>46120.125</v>
-      </c>
-      <c r="B917" s="4">
-        <v>31.963500403298273</v>
-      </c>
-      <c r="C917" s="4">
-        <v>38.299478832880659</v>
-      </c>
-      <c r="D917" s="4">
-        <v>38.109377526876628</v>
-      </c>
+      <c r="A917" s="1"/>
+      <c r="B917" s="4"/>
+      <c r="C917" s="4"/>
+      <c r="D917" s="4"/>
     </row>
     <row r="918" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A918" s="1">
-        <v>46120.166666666664</v>
-      </c>
-      <c r="B918" s="4">
-        <v>31.978583024342853</v>
-      </c>
-      <c r="C918" s="4">
-        <v>38.285780784818861</v>
-      </c>
-      <c r="D918" s="4">
-        <v>38.134497518194628</v>
-      </c>
+      <c r="A918" s="1"/>
+      <c r="B918" s="4"/>
+      <c r="C918" s="4"/>
+      <c r="D918" s="4"/>
     </row>
     <row r="919" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A919" s="1">
-        <v>46120.208333333336</v>
-      </c>
-      <c r="B919" s="4">
-        <v>32.052939708144571</v>
-      </c>
-      <c r="C919" s="4">
-        <v>38.374952555949392</v>
-      </c>
-      <c r="D919" s="4">
-        <v>38.202579090441539</v>
-      </c>
+      <c r="A919" s="1"/>
+      <c r="B919" s="4"/>
+      <c r="C919" s="4"/>
+      <c r="D919" s="4"/>
     </row>
     <row r="920" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A920" s="1">
-        <v>46120.25</v>
-      </c>
-      <c r="B920" s="4">
-        <v>32.0339355080216</v>
-      </c>
-      <c r="C920" s="4">
-        <v>38.358850594439538</v>
-      </c>
-      <c r="D920" s="4">
-        <v>38.214936927757655</v>
-      </c>
+      <c r="A920" s="1"/>
+      <c r="B920" s="4"/>
+      <c r="C920" s="4"/>
+      <c r="D920" s="4"/>
     </row>
     <row r="921" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A921" s="1">
-        <v>46120.291666666664</v>
-      </c>
-      <c r="B921" s="4">
-        <v>32.003750324249268</v>
-      </c>
-      <c r="C921" s="4">
-        <v>38.332046224806042</v>
-      </c>
-      <c r="D921" s="4">
-        <v>38.163540503438249</v>
-      </c>
+      <c r="A921" s="1"/>
+      <c r="B921" s="4"/>
+      <c r="C921" s="4"/>
+      <c r="D921" s="4"/>
     </row>
     <row r="922" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A922" s="1">
-        <v>46120.333333333336</v>
-      </c>
-      <c r="B922" s="4">
-        <v>31.954270188013712</v>
-      </c>
-      <c r="C922" s="4">
-        <v>38.328369685664327</v>
-      </c>
-      <c r="D922" s="4">
-        <v>38.184994694611603</v>
-      </c>
+      <c r="A922" s="1"/>
+      <c r="B922" s="4"/>
+      <c r="C922" s="4"/>
+      <c r="D922" s="4"/>
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A923" s="1">
-        <v>46120.375</v>
-      </c>
-      <c r="B923" s="4">
-        <v>31.936561902364094</v>
-      </c>
-      <c r="C923" s="4">
-        <v>38.353727863774161</v>
-      </c>
-      <c r="D923" s="4">
-        <v>38.234863195564863</v>
-      </c>
+      <c r="A923" s="1"/>
+      <c r="B923" s="4"/>
+      <c r="C923" s="4"/>
+      <c r="D923" s="4"/>
     </row>
     <row r="924" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A924" s="1">
-        <v>46120.416666666664</v>
-      </c>
-      <c r="B924" s="4">
-        <v>32.041093476613362</v>
-      </c>
-      <c r="C924" s="4">
-        <v>38.452908229827884</v>
-      </c>
-      <c r="D924" s="4">
-        <v>38.311775352462888</v>
-      </c>
+      <c r="A924" s="1"/>
+      <c r="B924" s="4"/>
+      <c r="C924" s="4"/>
+      <c r="D924" s="4"/>
     </row>
     <row r="925" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A925" s="1">
-        <v>46120.458333333336</v>
-      </c>
-      <c r="B925" s="4">
-        <v>32.132449229558311</v>
-      </c>
-      <c r="C925" s="4">
-        <v>38.5673285929362</v>
-      </c>
-      <c r="D925" s="4">
-        <v>38.460701745527757</v>
-      </c>
+      <c r="A925" s="1"/>
+      <c r="B925" s="4"/>
+      <c r="C925" s="4"/>
+      <c r="D925" s="4"/>
     </row>
     <row r="926" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A926" s="1">
-        <v>46120.5</v>
-      </c>
-      <c r="B926" s="4">
-        <v>32.212648526058402</v>
-      </c>
-      <c r="C926" s="4">
-        <v>38.672555478413898</v>
-      </c>
-      <c r="D926" s="4">
-        <v>38.56987072441008</v>
-      </c>
+      <c r="A926" s="1"/>
+      <c r="B926" s="4"/>
+      <c r="C926" s="4"/>
+      <c r="D926" s="4"/>
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A927" s="1">
-        <v>46120.541666666664</v>
-      </c>
-      <c r="B927" s="4">
-        <v>32.240541397154679</v>
-      </c>
-      <c r="C927" s="4">
-        <v>38.711560495694478</v>
-      </c>
-      <c r="D927" s="4">
-        <v>38.626097052858569</v>
-      </c>
+      <c r="A927" s="1"/>
+      <c r="B927" s="4"/>
+      <c r="C927" s="4"/>
+      <c r="D927" s="4"/>
     </row>
     <row r="928" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A928" s="1">
-        <v>46120.583333333336</v>
-      </c>
-      <c r="B928" s="4">
-        <v>32.237019401941545</v>
-      </c>
-      <c r="C928" s="4">
-        <v>38.697311131159466</v>
-      </c>
-      <c r="D928" s="4">
-        <v>38.741187020745656</v>
-      </c>
+      <c r="A928" s="1"/>
+      <c r="B928" s="4"/>
+      <c r="C928" s="4"/>
+      <c r="D928" s="4"/>
     </row>
     <row r="929" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A929" s="1">
-        <v>46120.625</v>
-      </c>
-      <c r="B929" s="4">
-        <v>32.21758870624361</v>
-      </c>
-      <c r="C929" s="4">
-        <v>38.668838889458598</v>
-      </c>
-      <c r="D929" s="4">
-        <v>38.595910232291466</v>
-      </c>
+      <c r="A929" s="1"/>
+      <c r="B929" s="4"/>
+      <c r="C929" s="4"/>
+      <c r="D929" s="4"/>
     </row>
     <row r="930" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A930" s="1">
-        <v>46120.666666666664</v>
-      </c>
-      <c r="B930" s="4">
-        <v>32.290286049615766</v>
-      </c>
-      <c r="C930" s="4">
-        <v>38.702857679212123</v>
-      </c>
-      <c r="D930" s="4">
-        <v>38.629592780533422</v>
-      </c>
+      <c r="A930" s="1"/>
+      <c r="B930" s="4"/>
+      <c r="C930" s="4"/>
+      <c r="D930" s="4"/>
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A931" s="1">
-        <v>46120.708333333336</v>
-      </c>
-      <c r="B931" s="4">
-        <v>32.323236468633013</v>
-      </c>
-      <c r="C931" s="4">
-        <v>38.712835080283028</v>
-      </c>
-      <c r="D931" s="4">
-        <v>38.6354749246129</v>
-      </c>
+      <c r="A931" s="1"/>
+      <c r="B931" s="4"/>
+      <c r="C931" s="4"/>
+      <c r="D931" s="4"/>
     </row>
     <row r="932" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A932" s="1">
-        <v>46120.75</v>
-      </c>
-      <c r="B932" s="4">
-        <v>32.295348342259722</v>
-      </c>
-      <c r="C932" s="4">
-        <v>38.677114601135251</v>
-      </c>
-      <c r="D932" s="4">
-        <v>38.587118103156911</v>
-      </c>
+      <c r="A932" s="1"/>
+      <c r="B932" s="4"/>
+      <c r="C932" s="4"/>
+      <c r="D932" s="4"/>
     </row>
     <row r="933" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A933" s="1">
-        <v>46120.791666666664</v>
-      </c>
-      <c r="B933" s="4">
-        <v>32.255013208919102</v>
-      </c>
-      <c r="C933" s="4">
-        <v>38.595459996178036</v>
-      </c>
-      <c r="D933" s="4">
-        <v>38.516631905618901</v>
-      </c>
+      <c r="A933" s="1"/>
+      <c r="B933" s="4"/>
+      <c r="C933" s="4"/>
+      <c r="D933" s="4"/>
     </row>
     <row r="934" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A934" s="1">
-        <v>46120.833333333336</v>
-      </c>
-      <c r="B934" s="4">
-        <v>32.202499357859296</v>
-      </c>
-      <c r="C934" s="4">
-        <v>38.544196623847597</v>
-      </c>
-      <c r="D934" s="4">
-        <v>38.427302595360729</v>
-      </c>
+      <c r="A934" s="1"/>
+      <c r="B934" s="4"/>
+      <c r="C934" s="4"/>
+      <c r="D934" s="4"/>
     </row>
     <row r="935" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A935" s="1">
-        <v>46120.875</v>
-      </c>
-      <c r="B935" s="4">
-        <v>32.21552012761434</v>
-      </c>
-      <c r="C935" s="4">
-        <v>38.522395247504825</v>
-      </c>
-      <c r="D935" s="4">
-        <v>38.369019430852781</v>
-      </c>
+      <c r="A935" s="1"/>
+      <c r="B935" s="4"/>
+      <c r="C935" s="4"/>
+      <c r="D935" s="4"/>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A936" s="1">
-        <v>46120.916666666664</v>
-      </c>
-      <c r="B936" s="4">
-        <v>32.158874969482419</v>
-      </c>
-      <c r="C936" s="4">
-        <v>38.484899040975876</v>
-      </c>
-      <c r="D936" s="4">
-        <v>38.338132215294181</v>
-      </c>
+      <c r="A936" s="1"/>
+      <c r="B936" s="4"/>
+      <c r="C936" s="4"/>
+      <c r="D936" s="4"/>
     </row>
     <row r="937" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A937" s="1">
-        <v>46120.958333333336</v>
-      </c>
-      <c r="B937" s="4">
-        <v>32.153984389671912</v>
-      </c>
-      <c r="C937" s="4">
-        <v>38.467610822327288</v>
-      </c>
-      <c r="D937" s="4">
-        <v>38.309453325824087</v>
-      </c>
+      <c r="A937" s="1"/>
+      <c r="B937" s="4"/>
+      <c r="C937" s="4"/>
+      <c r="D937" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="73" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CA11160-D68B-4AFB-BD9C-B12386F57111}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65855695-FABE-48F5-8F39-D2E1CA382407}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcOnSave="0"/>
+  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -111,10 +111,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -434,10 +430,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D937"/>
+  <dimension ref="A1:D972"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="45.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="46.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="26.77734375" bestFit="1" customWidth="1"/>
@@ -12890,292 +12886,1166 @@
       </c>
     </row>
     <row r="890" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A890" s="1"/>
-      <c r="B890" s="4"/>
-      <c r="C890" s="4"/>
-      <c r="D890" s="4"/>
+      <c r="A890" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B890" s="4">
+        <v>31.747291707992552</v>
+      </c>
+      <c r="C890" s="4">
+        <v>38.040231908162433</v>
+      </c>
+      <c r="D890" s="4">
+        <v>38.638023284640283</v>
+      </c>
     </row>
     <row r="891" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A891" s="1"/>
-      <c r="B891" s="4"/>
-      <c r="C891" s="4"/>
-      <c r="D891" s="4"/>
+      <c r="A891" s="1">
+        <v>46119.041666666664</v>
+      </c>
+      <c r="B891" s="4">
+        <v>31.732083606719971</v>
+      </c>
+      <c r="C891" s="4">
+        <v>38.029243329366047</v>
+      </c>
+      <c r="D891" s="4">
+        <v>38.618448845135049</v>
+      </c>
     </row>
     <row r="892" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A892" s="1"/>
-      <c r="B892" s="4"/>
-      <c r="C892" s="4"/>
-      <c r="D892" s="4"/>
+      <c r="A892" s="1">
+        <v>46119.083333333336</v>
+      </c>
+      <c r="B892" s="4">
+        <v>31.73663673400879</v>
+      </c>
+      <c r="C892" s="4">
+        <v>38.043819157282513</v>
+      </c>
+      <c r="D892" s="4">
+        <v>38.607787380691036</v>
+      </c>
     </row>
     <row r="893" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A893" s="1"/>
-      <c r="B893" s="4"/>
-      <c r="C893" s="4"/>
-      <c r="D893" s="4"/>
+      <c r="A893" s="1">
+        <v>46119.125</v>
+      </c>
+      <c r="B893" s="4">
+        <v>31.860515610376993</v>
+      </c>
+      <c r="C893" s="4">
+        <v>38.162665033340453</v>
+      </c>
+      <c r="D893" s="4">
+        <v>38.676612844406748</v>
+      </c>
     </row>
     <row r="894" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A894" s="1"/>
-      <c r="B894" s="4"/>
-      <c r="C894" s="4"/>
-      <c r="D894" s="4"/>
+      <c r="A894" s="1">
+        <v>46119.166666666664</v>
+      </c>
+      <c r="B894" s="4">
+        <v>31.872222455342612</v>
+      </c>
+      <c r="C894" s="4">
+        <v>38.182385667165121</v>
+      </c>
+      <c r="D894" s="4">
+        <v>38.744600901328717</v>
+      </c>
     </row>
     <row r="895" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A895" s="1"/>
-      <c r="B895" s="4"/>
-      <c r="C895" s="4"/>
-      <c r="D895" s="4"/>
+      <c r="A895" s="1">
+        <v>46119.208333333336</v>
+      </c>
+      <c r="B895" s="4">
+        <v>31.859166860580444</v>
+      </c>
+      <c r="C895" s="4">
+        <v>38.182774643670946</v>
+      </c>
+      <c r="D895" s="4">
+        <v>38.75499419233482</v>
+      </c>
     </row>
     <row r="896" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A896" s="1"/>
-      <c r="B896" s="4"/>
-      <c r="C896" s="4"/>
-      <c r="D896" s="4"/>
+      <c r="A896" s="1">
+        <v>46119.25</v>
+      </c>
+      <c r="B896" s="4">
+        <v>31.875</v>
+      </c>
+      <c r="C896" s="4">
+        <v>38.199359452156791</v>
+      </c>
+      <c r="D896" s="4">
+        <v>38.75434637376086</v>
+      </c>
     </row>
     <row r="897" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A897" s="1"/>
-      <c r="B897" s="4"/>
-      <c r="C897" s="4"/>
-      <c r="D897" s="4"/>
+      <c r="A897" s="1">
+        <v>46119.291666666664</v>
+      </c>
+      <c r="B897" s="4">
+        <v>31.831180047988891</v>
+      </c>
+      <c r="C897" s="4">
+        <v>38.181718977292377</v>
+      </c>
+      <c r="D897" s="4">
+        <v>38.71121773131356</v>
+      </c>
     </row>
     <row r="898" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A898" s="1"/>
-      <c r="B898" s="4"/>
-      <c r="C898" s="4"/>
-      <c r="D898" s="4"/>
+      <c r="A898" s="1">
+        <v>46119.333333333336</v>
+      </c>
+      <c r="B898" s="4">
+        <v>31.779600735505422</v>
+      </c>
+      <c r="C898" s="4">
+        <v>38.149109164151284</v>
+      </c>
+      <c r="D898" s="4">
+        <v>38.592661699146419</v>
+      </c>
     </row>
     <row r="899" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A899" s="1"/>
-      <c r="B899" s="4"/>
-      <c r="C899" s="4"/>
-      <c r="D899" s="4"/>
+      <c r="A899" s="1">
+        <v>46119.375</v>
+      </c>
+      <c r="B899" s="4">
+        <v>31.874635549386344</v>
+      </c>
+      <c r="C899" s="4">
+        <v>38.283650851972176</v>
+      </c>
+      <c r="D899" s="4">
+        <v>38.456244553631258</v>
+      </c>
     </row>
     <row r="900" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A900" s="1"/>
-      <c r="B900" s="4"/>
-      <c r="C900" s="4"/>
-      <c r="D900" s="4"/>
+      <c r="A900" s="1">
+        <v>46119.416666666664</v>
+      </c>
+      <c r="B900" s="4">
+        <v>32.102082602183025</v>
+      </c>
+      <c r="C900" s="4">
+        <v>38.515198294321699</v>
+      </c>
+      <c r="D900" s="4">
+        <v>38.383252471135378</v>
+      </c>
     </row>
     <row r="901" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A901" s="1"/>
-      <c r="B901" s="4"/>
-      <c r="C901" s="4"/>
-      <c r="D901" s="4"/>
+      <c r="A901" s="1">
+        <v>46119.458333333336</v>
+      </c>
+      <c r="B901" s="4">
+        <v>32.124791717529298</v>
+      </c>
+      <c r="C901" s="4">
+        <v>38.568759822845458</v>
+      </c>
+      <c r="D901" s="4">
+        <v>38.46647688814523</v>
+      </c>
     </row>
     <row r="902" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A902" s="1"/>
-      <c r="B902" s="4"/>
-      <c r="C902" s="4"/>
-      <c r="D902" s="4"/>
+      <c r="A902" s="1">
+        <v>46119.5</v>
+      </c>
+      <c r="B902" s="4">
+        <v>32.147999846140543</v>
+      </c>
+      <c r="C902" s="4">
+        <v>38.620547080039977</v>
+      </c>
+      <c r="D902" s="4">
+        <v>38.477683928689835</v>
+      </c>
     </row>
     <row r="903" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A903" s="1"/>
-      <c r="B903" s="4"/>
-      <c r="C903" s="4"/>
-      <c r="D903" s="4"/>
+      <c r="A903" s="1">
+        <v>46119.541666666664</v>
+      </c>
+      <c r="B903" s="4">
+        <v>32.172750263214112</v>
+      </c>
+      <c r="C903" s="4">
+        <v>38.628168066342674</v>
+      </c>
+      <c r="D903" s="4">
+        <v>38.506362652507548</v>
+      </c>
     </row>
     <row r="904" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A904" s="1"/>
-      <c r="B904" s="4"/>
-      <c r="C904" s="4"/>
-      <c r="D904" s="4"/>
+      <c r="A904" s="1">
+        <v>46119.583333333336</v>
+      </c>
+      <c r="B904" s="4">
+        <v>32.220291169484454</v>
+      </c>
+      <c r="C904" s="4">
+        <v>38.666492493947345</v>
+      </c>
+      <c r="D904" s="4">
+        <v>38.580102258757179</v>
+      </c>
     </row>
     <row r="905" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A905" s="1"/>
-      <c r="B905" s="4"/>
-      <c r="C905" s="4"/>
-      <c r="D905" s="4"/>
+      <c r="A905" s="1">
+        <v>46119.625</v>
+      </c>
+      <c r="B905" s="4">
+        <v>32.221511414993643</v>
+      </c>
+      <c r="C905" s="4">
+        <v>38.664074577548639</v>
+      </c>
+      <c r="D905" s="4">
+        <v>38.545399744562445</v>
+      </c>
     </row>
     <row r="906" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A906" s="1"/>
-      <c r="B906" s="4"/>
-      <c r="C906" s="4"/>
-      <c r="D906" s="4"/>
+      <c r="A906" s="1">
+        <v>46119.666666666664</v>
+      </c>
+      <c r="B906" s="4">
+        <v>32.271117947529227</v>
+      </c>
+      <c r="C906" s="4">
+        <v>38.694413643090058</v>
+      </c>
+      <c r="D906" s="4">
+        <v>38.543887786359491</v>
+      </c>
     </row>
     <row r="907" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A907" s="1"/>
-      <c r="B907" s="4"/>
-      <c r="C907" s="4"/>
-      <c r="D907" s="4"/>
+      <c r="A907" s="1">
+        <v>46119.708333333336</v>
+      </c>
+      <c r="B907" s="4">
+        <v>32.248661422948722</v>
+      </c>
+      <c r="C907" s="4">
+        <v>38.661180326673723</v>
+      </c>
+      <c r="D907" s="4">
+        <v>38.518073369705043</v>
+      </c>
     </row>
     <row r="908" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A908" s="1"/>
-      <c r="B908" s="4"/>
-      <c r="C908" s="4"/>
-      <c r="D908" s="4"/>
+      <c r="A908" s="1">
+        <v>46119.75</v>
+      </c>
+      <c r="B908" s="4">
+        <v>32.149958299001057</v>
+      </c>
+      <c r="C908" s="4">
+        <v>38.536391079425812</v>
+      </c>
+      <c r="D908" s="4">
+        <v>38.425548247565409</v>
+      </c>
     </row>
     <row r="909" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A909" s="1"/>
-      <c r="B909" s="4"/>
-      <c r="C909" s="4"/>
-      <c r="D909" s="4"/>
+      <c r="A909" s="1">
+        <v>46119.791666666664</v>
+      </c>
+      <c r="B909" s="4">
+        <v>32.064583333333331</v>
+      </c>
+      <c r="C909" s="4">
+        <v>38.400647946198781</v>
+      </c>
+      <c r="D909" s="4">
+        <v>38.295954228738943</v>
+      </c>
     </row>
     <row r="910" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A910" s="1"/>
-      <c r="B910" s="4"/>
-      <c r="C910" s="4"/>
-      <c r="D910" s="4"/>
+      <c r="A910" s="1">
+        <v>46119.833333333336</v>
+      </c>
+      <c r="B910" s="4">
+        <v>32.02708333333333</v>
+      </c>
+      <c r="C910" s="4">
+        <v>38.353390990770777</v>
+      </c>
+      <c r="D910" s="4">
+        <v>38.20188406403183</v>
+      </c>
     </row>
     <row r="911" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A911" s="1"/>
-      <c r="B911" s="4"/>
-      <c r="C911" s="4"/>
-      <c r="D911" s="4"/>
+      <c r="A911" s="1">
+        <v>46119.875</v>
+      </c>
+      <c r="B911" s="4">
+        <v>31.946041981379192</v>
+      </c>
+      <c r="C911" s="4">
+        <v>38.284241860602805</v>
+      </c>
+      <c r="D911" s="4">
+        <v>38.121467589154634</v>
+      </c>
     </row>
     <row r="912" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A912" s="1"/>
-      <c r="B912" s="4"/>
-      <c r="C912" s="4"/>
-      <c r="D912" s="4"/>
+      <c r="A912" s="1">
+        <v>46119.916666666664</v>
+      </c>
+      <c r="B912" s="4">
+        <v>31.943268940998959</v>
+      </c>
+      <c r="C912" s="4">
+        <v>38.276804601578483</v>
+      </c>
+      <c r="D912" s="4">
+        <v>38.103749656588903</v>
+      </c>
     </row>
     <row r="913" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A913" s="1"/>
-      <c r="B913" s="4"/>
-      <c r="C913" s="4"/>
-      <c r="D913" s="4"/>
+      <c r="A913" s="1">
+        <v>46119.958333333336</v>
+      </c>
+      <c r="B913" s="4">
+        <v>31.955518788131279</v>
+      </c>
+      <c r="C913" s="4">
+        <v>38.260313002268475</v>
+      </c>
+      <c r="D913" s="4">
+        <v>38.094744016860204</v>
+      </c>
     </row>
     <row r="914" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A914" s="1"/>
-      <c r="B914" s="4"/>
-      <c r="C914" s="4"/>
-      <c r="D914" s="4"/>
+      <c r="A914" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B914" s="4">
+        <v>31.933433423917116</v>
+      </c>
+      <c r="C914" s="4">
+        <v>38.267733997768829</v>
+      </c>
+      <c r="D914" s="4">
+        <v>38.093182990623866</v>
+      </c>
     </row>
     <row r="915" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A915" s="1"/>
-      <c r="B915" s="4"/>
-      <c r="C915" s="4"/>
-      <c r="D915" s="4"/>
+      <c r="A915" s="1">
+        <v>46120.041666666664</v>
+      </c>
+      <c r="B915" s="4">
+        <v>31.992818901273939</v>
+      </c>
+      <c r="C915" s="4">
+        <v>38.291125558923788</v>
+      </c>
+      <c r="D915" s="4">
+        <v>38.112049130275516</v>
+      </c>
     </row>
     <row r="916" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A916" s="1"/>
-      <c r="B916" s="4"/>
-      <c r="C916" s="4"/>
-      <c r="D916" s="4"/>
+      <c r="A916" s="1">
+        <v>46120.083333333336</v>
+      </c>
+      <c r="B916" s="4">
+        <v>31.98245882458157</v>
+      </c>
+      <c r="C916" s="4">
+        <v>38.292337177417892</v>
+      </c>
+      <c r="D916" s="4">
+        <v>38.100528302894148</v>
+      </c>
     </row>
     <row r="917" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A917" s="1"/>
-      <c r="B917" s="4"/>
-      <c r="C917" s="4"/>
-      <c r="D917" s="4"/>
+      <c r="A917" s="1">
+        <v>46120.125</v>
+      </c>
+      <c r="B917" s="4">
+        <v>31.963500403298273</v>
+      </c>
+      <c r="C917" s="4">
+        <v>38.299478832880659</v>
+      </c>
+      <c r="D917" s="4">
+        <v>38.109377526876628</v>
+      </c>
     </row>
     <row r="918" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A918" s="1"/>
-      <c r="B918" s="4"/>
-      <c r="C918" s="4"/>
-      <c r="D918" s="4"/>
+      <c r="A918" s="1">
+        <v>46120.166666666664</v>
+      </c>
+      <c r="B918" s="4">
+        <v>31.978583024342853</v>
+      </c>
+      <c r="C918" s="4">
+        <v>38.285780784818861</v>
+      </c>
+      <c r="D918" s="4">
+        <v>38.134497518194628</v>
+      </c>
     </row>
     <row r="919" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A919" s="1"/>
-      <c r="B919" s="4"/>
-      <c r="C919" s="4"/>
-      <c r="D919" s="4"/>
+      <c r="A919" s="1">
+        <v>46120.208333333336</v>
+      </c>
+      <c r="B919" s="4">
+        <v>32.052939708144571</v>
+      </c>
+      <c r="C919" s="4">
+        <v>38.374952555949392</v>
+      </c>
+      <c r="D919" s="4">
+        <v>38.202579090441539</v>
+      </c>
     </row>
     <row r="920" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A920" s="1"/>
-      <c r="B920" s="4"/>
-      <c r="C920" s="4"/>
-      <c r="D920" s="4"/>
+      <c r="A920" s="1">
+        <v>46120.25</v>
+      </c>
+      <c r="B920" s="4">
+        <v>32.0339355080216</v>
+      </c>
+      <c r="C920" s="4">
+        <v>38.358850594439538</v>
+      </c>
+      <c r="D920" s="4">
+        <v>38.214936927757655</v>
+      </c>
     </row>
     <row r="921" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A921" s="1"/>
-      <c r="B921" s="4"/>
-      <c r="C921" s="4"/>
-      <c r="D921" s="4"/>
+      <c r="A921" s="1">
+        <v>46120.291666666664</v>
+      </c>
+      <c r="B921" s="4">
+        <v>32.003750324249268</v>
+      </c>
+      <c r="C921" s="4">
+        <v>38.332046224806042</v>
+      </c>
+      <c r="D921" s="4">
+        <v>38.163540503438249</v>
+      </c>
     </row>
     <row r="922" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A922" s="1"/>
-      <c r="B922" s="4"/>
-      <c r="C922" s="4"/>
-      <c r="D922" s="4"/>
+      <c r="A922" s="1">
+        <v>46120.333333333336</v>
+      </c>
+      <c r="B922" s="4">
+        <v>31.954270188013712</v>
+      </c>
+      <c r="C922" s="4">
+        <v>38.328369685664327</v>
+      </c>
+      <c r="D922" s="4">
+        <v>38.184994694611603</v>
+      </c>
     </row>
     <row r="923" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A923" s="1"/>
-      <c r="B923" s="4"/>
-      <c r="C923" s="4"/>
-      <c r="D923" s="4"/>
+      <c r="A923" s="1">
+        <v>46120.375</v>
+      </c>
+      <c r="B923" s="4">
+        <v>31.936561902364094</v>
+      </c>
+      <c r="C923" s="4">
+        <v>38.353727863774161</v>
+      </c>
+      <c r="D923" s="4">
+        <v>38.234863195564863</v>
+      </c>
     </row>
     <row r="924" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A924" s="1"/>
-      <c r="B924" s="4"/>
-      <c r="C924" s="4"/>
-      <c r="D924" s="4"/>
+      <c r="A924" s="1">
+        <v>46120.416666666664</v>
+      </c>
+      <c r="B924" s="4">
+        <v>32.041093476613362</v>
+      </c>
+      <c r="C924" s="4">
+        <v>38.452908229827884</v>
+      </c>
+      <c r="D924" s="4">
+        <v>38.311775352462888</v>
+      </c>
     </row>
     <row r="925" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A925" s="1"/>
-      <c r="B925" s="4"/>
-      <c r="C925" s="4"/>
-      <c r="D925" s="4"/>
+      <c r="A925" s="1">
+        <v>46120.458333333336</v>
+      </c>
+      <c r="B925" s="4">
+        <v>32.132449229558311</v>
+      </c>
+      <c r="C925" s="4">
+        <v>38.5673285929362</v>
+      </c>
+      <c r="D925" s="4">
+        <v>38.460701745527757</v>
+      </c>
     </row>
     <row r="926" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A926" s="1"/>
-      <c r="B926" s="4"/>
-      <c r="C926" s="4"/>
-      <c r="D926" s="4"/>
+      <c r="A926" s="1">
+        <v>46120.5</v>
+      </c>
+      <c r="B926" s="4">
+        <v>32.212648526058402</v>
+      </c>
+      <c r="C926" s="4">
+        <v>38.672555478413898</v>
+      </c>
+      <c r="D926" s="4">
+        <v>38.56987072441008</v>
+      </c>
     </row>
     <row r="927" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A927" s="1"/>
-      <c r="B927" s="4"/>
-      <c r="C927" s="4"/>
-      <c r="D927" s="4"/>
+      <c r="A927" s="1">
+        <v>46120.541666666664</v>
+      </c>
+      <c r="B927" s="4">
+        <v>32.240541397154679</v>
+      </c>
+      <c r="C927" s="4">
+        <v>38.711560495694478</v>
+      </c>
+      <c r="D927" s="4">
+        <v>38.626097052858569</v>
+      </c>
     </row>
     <row r="928" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A928" s="1"/>
-      <c r="B928" s="4"/>
-      <c r="C928" s="4"/>
-      <c r="D928" s="4"/>
+      <c r="A928" s="1">
+        <v>46120.583333333336</v>
+      </c>
+      <c r="B928" s="4">
+        <v>32.237019401941545</v>
+      </c>
+      <c r="C928" s="4">
+        <v>38.697311131159466</v>
+      </c>
+      <c r="D928" s="4">
+        <v>38.741187020745656</v>
+      </c>
     </row>
     <row r="929" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A929" s="1"/>
-      <c r="B929" s="4"/>
-      <c r="C929" s="4"/>
-      <c r="D929" s="4"/>
+      <c r="A929" s="1">
+        <v>46120.625</v>
+      </c>
+      <c r="B929" s="4">
+        <v>32.21758870624361</v>
+      </c>
+      <c r="C929" s="4">
+        <v>38.668838889458598</v>
+      </c>
+      <c r="D929" s="4">
+        <v>38.595910232291466</v>
+      </c>
     </row>
     <row r="930" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A930" s="1"/>
-      <c r="B930" s="4"/>
-      <c r="C930" s="4"/>
-      <c r="D930" s="4"/>
+      <c r="A930" s="1">
+        <v>46120.666666666664</v>
+      </c>
+      <c r="B930" s="4">
+        <v>32.290286049615766</v>
+      </c>
+      <c r="C930" s="4">
+        <v>38.702857679212123</v>
+      </c>
+      <c r="D930" s="4">
+        <v>38.629592780533422</v>
+      </c>
     </row>
     <row r="931" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A931" s="1"/>
-      <c r="B931" s="4"/>
-      <c r="C931" s="4"/>
-      <c r="D931" s="4"/>
+      <c r="A931" s="1">
+        <v>46120.708333333336</v>
+      </c>
+      <c r="B931" s="4">
+        <v>32.323236468633013</v>
+      </c>
+      <c r="C931" s="4">
+        <v>38.712835080283028</v>
+      </c>
+      <c r="D931" s="4">
+        <v>38.6354749246129</v>
+      </c>
     </row>
     <row r="932" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A932" s="1"/>
-      <c r="B932" s="4"/>
-      <c r="C932" s="4"/>
-      <c r="D932" s="4"/>
+      <c r="A932" s="1">
+        <v>46120.75</v>
+      </c>
+      <c r="B932" s="4">
+        <v>32.295348342259722</v>
+      </c>
+      <c r="C932" s="4">
+        <v>38.677114601135251</v>
+      </c>
+      <c r="D932" s="4">
+        <v>38.587118103156911</v>
+      </c>
     </row>
     <row r="933" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A933" s="1"/>
-      <c r="B933" s="4"/>
-      <c r="C933" s="4"/>
-      <c r="D933" s="4"/>
+      <c r="A933" s="1">
+        <v>46120.791666666664</v>
+      </c>
+      <c r="B933" s="4">
+        <v>32.255013208919102</v>
+      </c>
+      <c r="C933" s="4">
+        <v>38.595459996178036</v>
+      </c>
+      <c r="D933" s="4">
+        <v>38.516631905618901</v>
+      </c>
     </row>
     <row r="934" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A934" s="1"/>
-      <c r="B934" s="4"/>
-      <c r="C934" s="4"/>
-      <c r="D934" s="4"/>
+      <c r="A934" s="1">
+        <v>46120.833333333336</v>
+      </c>
+      <c r="B934" s="4">
+        <v>32.202499357859296</v>
+      </c>
+      <c r="C934" s="4">
+        <v>38.544196623847597</v>
+      </c>
+      <c r="D934" s="4">
+        <v>38.427302595360729</v>
+      </c>
     </row>
     <row r="935" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A935" s="1"/>
-      <c r="B935" s="4"/>
-      <c r="C935" s="4"/>
-      <c r="D935" s="4"/>
+      <c r="A935" s="1">
+        <v>46120.875</v>
+      </c>
+      <c r="B935" s="4">
+        <v>32.21552012761434</v>
+      </c>
+      <c r="C935" s="4">
+        <v>38.522395247504825</v>
+      </c>
+      <c r="D935" s="4">
+        <v>38.369019430852781</v>
+      </c>
     </row>
     <row r="936" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A936" s="1"/>
-      <c r="B936" s="4"/>
-      <c r="C936" s="4"/>
-      <c r="D936" s="4"/>
+      <c r="A936" s="1">
+        <v>46120.916666666664</v>
+      </c>
+      <c r="B936" s="4">
+        <v>32.158874969482419</v>
+      </c>
+      <c r="C936" s="4">
+        <v>38.484899040975876</v>
+      </c>
+      <c r="D936" s="4">
+        <v>38.338132215294181</v>
+      </c>
     </row>
     <row r="937" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A937" s="1"/>
-      <c r="B937" s="4"/>
-      <c r="C937" s="4"/>
-      <c r="D937" s="4"/>
+      <c r="A937" s="1">
+        <v>46120.958333333336</v>
+      </c>
+      <c r="B937" s="4">
+        <v>32.153984389671912</v>
+      </c>
+      <c r="C937" s="4">
+        <v>38.467610822327288</v>
+      </c>
+      <c r="D937" s="4">
+        <v>38.309453325824087</v>
+      </c>
+    </row>
+    <row r="938" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A938" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B938" s="4">
+        <v>32.139981804662575</v>
+      </c>
+      <c r="C938" s="4">
+        <v>38.433130731769637</v>
+      </c>
+      <c r="D938" s="4">
+        <v>38.287466706175401</v>
+      </c>
+    </row>
+    <row r="939" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A939" s="1">
+        <v>46121.041666666664</v>
+      </c>
+      <c r="B939" s="4">
+        <v>32.168719664074125</v>
+      </c>
+      <c r="C939" s="4">
+        <v>38.472239716847739</v>
+      </c>
+      <c r="D939" s="4">
+        <v>38.299833614844864</v>
+      </c>
+    </row>
+    <row r="940" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A940" s="1">
+        <v>46121.083333333336</v>
+      </c>
+      <c r="B940" s="4">
+        <v>32.170415623982748</v>
+      </c>
+      <c r="C940" s="4">
+        <v>38.44541445614999</v>
+      </c>
+      <c r="D940" s="4">
+        <v>38.279582672825562</v>
+      </c>
+    </row>
+    <row r="941" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A941" s="1">
+        <v>46121.125</v>
+      </c>
+      <c r="B941" s="4">
+        <v>32.140000247955321</v>
+      </c>
+      <c r="C941" s="4">
+        <v>38.443343535640786</v>
+      </c>
+      <c r="D941" s="4">
+        <v>38.25790267387584</v>
+      </c>
+    </row>
+    <row r="942" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A942" s="1">
+        <v>46121.166666666664</v>
+      </c>
+      <c r="B942" s="4">
+        <v>32.152603228886925</v>
+      </c>
+      <c r="C942" s="4">
+        <v>38.437023703257246</v>
+      </c>
+      <c r="D942" s="4">
+        <v>38.294048990766207</v>
+      </c>
+    </row>
+    <row r="943" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A943" s="1">
+        <v>46121.208333333336</v>
+      </c>
+      <c r="B943" s="4">
+        <v>32.134461349911163</v>
+      </c>
+      <c r="C943" s="4">
+        <v>38.447291745079887</v>
+      </c>
+      <c r="D943" s="4">
+        <v>38.303354615105526</v>
+      </c>
+    </row>
+    <row r="944" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A944" s="1">
+        <v>46121.25</v>
+      </c>
+      <c r="B944" s="4">
+        <v>32.123292179460883</v>
+      </c>
+      <c r="C944" s="4">
+        <v>38.465482652452259</v>
+      </c>
+      <c r="D944" s="4">
+        <v>38.320798533321764</v>
+      </c>
+    </row>
+    <row r="945" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A945" s="1">
+        <v>46121.291666666664</v>
+      </c>
+      <c r="B945" s="4">
+        <v>32.128084828702974</v>
+      </c>
+      <c r="C945" s="4">
+        <v>38.464569702148438</v>
+      </c>
+      <c r="D945" s="4">
+        <v>38.326246761122</v>
+      </c>
+    </row>
+    <row r="946" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A946" s="1">
+        <v>46121.333333333336</v>
+      </c>
+      <c r="B946" s="4">
+        <v>32.118143724927712</v>
+      </c>
+      <c r="C946" s="4">
+        <v>38.464391797049004</v>
+      </c>
+      <c r="D946" s="4">
+        <v>38.335219107172094</v>
+      </c>
+    </row>
+    <row r="947" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A947" s="1">
+        <v>46121.375</v>
+      </c>
+      <c r="B947" s="4">
+        <v>32.116953976949056</v>
+      </c>
+      <c r="C947" s="4">
+        <v>38.482952537871242</v>
+      </c>
+      <c r="D947" s="4">
+        <v>38.367625748242403</v>
+      </c>
+    </row>
+    <row r="948" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A948" s="1">
+        <v>46121.416666666664</v>
+      </c>
+      <c r="B948" s="4">
+        <v>32.201180055406361</v>
+      </c>
+      <c r="C948" s="4">
+        <v>38.581262898445132</v>
+      </c>
+      <c r="D948" s="4">
+        <v>38.449065599249465</v>
+      </c>
+    </row>
+    <row r="949" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A949" s="1">
+        <v>46121.458333333336</v>
+      </c>
+      <c r="B949" s="4">
+        <v>32.264028856489396</v>
+      </c>
+      <c r="C949" s="4">
+        <v>38.670286115010576</v>
+      </c>
+      <c r="D949" s="4">
+        <v>38.559801455402102</v>
+      </c>
+    </row>
+    <row r="950" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A950" s="1">
+        <v>46121.5</v>
+      </c>
+      <c r="B950" s="4">
+        <v>32.313614791372544</v>
+      </c>
+      <c r="C950" s="4">
+        <v>38.732034642046145</v>
+      </c>
+      <c r="D950" s="4">
+        <v>38.642634281037424</v>
+      </c>
+    </row>
+    <row r="951" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A951" s="1">
+        <v>46121.541666666664</v>
+      </c>
+      <c r="B951" s="4">
+        <v>32.416593843957649</v>
+      </c>
+      <c r="C951" s="4">
+        <v>38.805932334800815</v>
+      </c>
+      <c r="D951" s="4">
+        <v>38.698090247108823</v>
+      </c>
+    </row>
+    <row r="952" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A952" s="1">
+        <v>46121.583333333336</v>
+      </c>
+      <c r="B952" s="4">
+        <v>32.415000867843631</v>
+      </c>
+      <c r="C952" s="4">
+        <v>38.859036985528533</v>
+      </c>
+      <c r="D952" s="4">
+        <v>38.738622715450475</v>
+      </c>
+    </row>
+    <row r="953" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A953" s="1">
+        <v>46121.625</v>
+      </c>
+      <c r="B953" s="4">
+        <v>32.417500305175778</v>
+      </c>
+      <c r="C953" s="4">
+        <v>38.824311079802342</v>
+      </c>
+      <c r="D953" s="4">
+        <v>38.726446087307394</v>
+      </c>
+    </row>
+    <row r="954" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A954" s="1">
+        <v>46121.666666666664</v>
+      </c>
+      <c r="B954" s="4">
+        <v>32.565893697225917</v>
+      </c>
+      <c r="C954" s="4">
+        <v>38.972916726271315</v>
+      </c>
+      <c r="D954" s="4">
+        <v>38.825513368694097</v>
+      </c>
+    </row>
+    <row r="955" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A955" s="1">
+        <v>46121.708333333336</v>
+      </c>
+      <c r="B955" s="4">
+        <v>32.52528698760549</v>
+      </c>
+      <c r="C955" s="4">
+        <v>38.918008339405063</v>
+      </c>
+      <c r="D955" s="4">
+        <v>38.796561081873946</v>
+      </c>
+    </row>
+    <row r="956" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A956" s="1">
+        <v>46121.75</v>
+      </c>
+      <c r="B956" s="4">
+        <v>32.416319677564836</v>
+      </c>
+      <c r="C956" s="4">
+        <v>38.823574670155843</v>
+      </c>
+      <c r="D956" s="4">
+        <v>38.696040297671708</v>
+      </c>
+    </row>
+    <row r="957" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A957" s="1">
+        <v>46121.791666666664</v>
+      </c>
+      <c r="B957" s="4">
+        <v>32.39680455052261</v>
+      </c>
+      <c r="C957" s="4">
+        <v>38.774798544247943</v>
+      </c>
+      <c r="D957" s="4">
+        <v>38.637952190382258</v>
+      </c>
+    </row>
+    <row r="958" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A958" s="1">
+        <v>46121.833333333336</v>
+      </c>
+      <c r="B958" s="4">
+        <v>32.352523960326963</v>
+      </c>
+      <c r="C958" s="4">
+        <v>38.686727607459346</v>
+      </c>
+      <c r="D958" s="4">
+        <v>38.551759378287265</v>
+      </c>
+    </row>
+    <row r="959" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A959" s="1">
+        <v>46121.875</v>
+      </c>
+      <c r="B959" s="4">
+        <v>32.287755226205896</v>
+      </c>
+      <c r="C959" s="4">
+        <v>38.622672728488318</v>
+      </c>
+      <c r="D959" s="4">
+        <v>38.47303096388886</v>
+      </c>
+    </row>
+    <row r="960" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A960" s="1">
+        <v>46121.916666666664</v>
+      </c>
+      <c r="B960" s="4">
+        <v>32.214999914169312</v>
+      </c>
+      <c r="C960" s="4">
+        <v>38.546539317237006</v>
+      </c>
+      <c r="D960" s="4">
+        <v>38.383019583549199</v>
+      </c>
+    </row>
+    <row r="961" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A961" s="1">
+        <v>46121.958333333336</v>
+      </c>
+      <c r="B961" s="4">
+        <v>32.184375286102295</v>
+      </c>
+      <c r="C961" s="4">
+        <v>38.51662693235609</v>
+      </c>
+      <c r="D961" s="4">
+        <v>38.358878620233646</v>
+      </c>
+    </row>
+    <row r="962" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A962" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B962" s="4">
+        <v>32.137766150272256</v>
+      </c>
+      <c r="C962" s="4">
+        <v>38.455583623250327</v>
+      </c>
+      <c r="D962" s="4">
+        <v>38.327050375822012</v>
+      </c>
+    </row>
+    <row r="963" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A963" s="1">
+        <v>46122.041666666664</v>
+      </c>
+      <c r="B963" s="4">
+        <v>32.117374175485935</v>
+      </c>
+      <c r="C963" s="4">
+        <v>38.427707831064858</v>
+      </c>
+      <c r="D963" s="4">
+        <v>38.296059179077155</v>
+      </c>
+    </row>
+    <row r="964" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A964" s="1">
+        <v>46122.083333333336</v>
+      </c>
+      <c r="B964" s="4">
+        <v>32.131527943081323</v>
+      </c>
+      <c r="C964" s="4">
+        <v>38.44765593210856</v>
+      </c>
+      <c r="D964" s="4">
+        <v>38.279252887981542</v>
+      </c>
+    </row>
+    <row r="965" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A965" s="1">
+        <v>46122.125</v>
+      </c>
+      <c r="B965" s="4">
+        <v>32.123064976646788</v>
+      </c>
+      <c r="C965" s="4">
+        <v>38.431149759048076</v>
+      </c>
+      <c r="D965" s="4">
+        <v>38.261499959154101</v>
+      </c>
+    </row>
+    <row r="966" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A966" s="1">
+        <v>46122.166666666664</v>
+      </c>
+      <c r="B966" s="4">
+        <v>32.109694479193003</v>
+      </c>
+      <c r="C966" s="4">
+        <v>38.402219586494645</v>
+      </c>
+      <c r="D966" s="4">
+        <v>38.295134468050719</v>
+      </c>
+    </row>
+    <row r="967" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A967" s="1">
+        <v>46122.208333333336</v>
+      </c>
+      <c r="B967" s="4">
+        <v>32.075780681769054</v>
+      </c>
+      <c r="C967" s="4">
+        <v>38.385745307726744</v>
+      </c>
+      <c r="D967" s="4">
+        <v>38.247780154448506</v>
+      </c>
+    </row>
+    <row r="968" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A968" s="1">
+        <v>46122.25</v>
+      </c>
+      <c r="B968" s="4">
+        <v>32.073124011357628</v>
+      </c>
+      <c r="C968" s="4">
+        <v>38.364160456480803</v>
+      </c>
+      <c r="D968" s="4">
+        <v>38.223644875605402</v>
+      </c>
+    </row>
+    <row r="969" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A969" s="1">
+        <v>46122.291666666664</v>
+      </c>
+      <c r="B969" s="4">
+        <v>32.056588379542035</v>
+      </c>
+      <c r="C969" s="4">
+        <v>38.385525880036539</v>
+      </c>
+      <c r="D969" s="4">
+        <v>38.234794728315237</v>
+      </c>
+    </row>
+    <row r="970" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A970" s="1">
+        <v>46122.333333333336</v>
+      </c>
+      <c r="B970" s="4">
+        <v>32.089609424273171</v>
+      </c>
+      <c r="C970" s="4">
+        <v>38.426822821299233</v>
+      </c>
+      <c r="D970" s="4">
+        <v>38.291033870050853</v>
+      </c>
+    </row>
+    <row r="971" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A971" s="1">
+        <v>46122.375</v>
+      </c>
+      <c r="B971" s="4">
+        <v>32.123384912808739</v>
+      </c>
+      <c r="C971" s="4">
+        <v>38.495677185058597</v>
+      </c>
+      <c r="D971" s="4">
+        <v>38.376849793105336</v>
+      </c>
+    </row>
+    <row r="972" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A972" s="1">
+        <v>46122.416666666664</v>
+      </c>
+      <c r="B972" s="4">
+        <v>32.146251296997072</v>
+      </c>
+      <c r="C972" s="4">
+        <v>38.557386578453915</v>
+      </c>
+      <c r="D972" s="4">
+        <v>38.366726301007425</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026 1-21 March Number.xlsx
+++ b/2026 1-21 March Number.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blcppower-my.sharepoint.com/personal/natthaphong_m_blcp_co_th/Documents/BLCP/ATSM 2026/Hot Season/Claude/Fore github/blcp-hotseason-tracking/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{65855695-FABE-48F5-8F39-D2E1CA382407}"/>
+  <xr:revisionPtr revIDLastSave="78" documentId="8_{DFC32D05-94C8-4DA2-A566-2308CAAE7D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E62294F-D127-47BB-B762-07CDA855CECB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" xr2:uid="{84CD358A-30A5-448D-BFC1-D6EF37F91320}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" calcCompleted="0" calcOnSave="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -430,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{163996B5-F150-4C6F-BB02-87F4A8F0CBD4}">
-  <dimension ref="A1:D972"/>
+  <dimension ref="A1:D1118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.109375" bestFit="1" customWidth="1"/>
@@ -14047,6 +14047,2050 @@
         <v>38.366726301007425</v>
       </c>
     </row>
+    <row r="973" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A973" s="1">
+        <v>46122.458333333336</v>
+      </c>
+      <c r="B973" s="4">
+        <v>32.253264013926191</v>
+      </c>
+      <c r="C973" s="4">
+        <v>38.647805653678049</v>
+      </c>
+      <c r="D973" s="4">
+        <v>38.255187798327178</v>
+      </c>
+    </row>
+    <row r="974" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A974" s="1">
+        <v>46122.5</v>
+      </c>
+      <c r="B974" s="4">
+        <v>32.302153046925859</v>
+      </c>
+      <c r="C974" s="4">
+        <v>38.740484550264149</v>
+      </c>
+      <c r="D974" s="4">
+        <v>38.338142625490825</v>
+      </c>
+    </row>
+    <row r="975" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A975" s="1">
+        <v>46122.541666666664</v>
+      </c>
+      <c r="B975" s="4">
+        <v>32.364375813802084</v>
+      </c>
+      <c r="C975" s="4">
+        <v>38.798333856794571</v>
+      </c>
+      <c r="D975" s="4">
+        <v>38.430907325250132</v>
+      </c>
+    </row>
+    <row r="976" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A976" s="1">
+        <v>46122.583333333336</v>
+      </c>
+      <c r="B976" s="4">
+        <v>32.423455822751635</v>
+      </c>
+      <c r="C976" s="4">
+        <v>38.847334739896986</v>
+      </c>
+      <c r="D976" s="4">
+        <v>38.465666500977839</v>
+      </c>
+    </row>
+    <row r="977" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A977" s="1">
+        <v>46122.625</v>
+      </c>
+      <c r="B977" s="4">
+        <v>32.458182678733557</v>
+      </c>
+      <c r="C977" s="4">
+        <v>38.905575210518307</v>
+      </c>
+      <c r="D977" s="4">
+        <v>38.505751862458276</v>
+      </c>
+    </row>
+    <row r="978" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A978" s="1">
+        <v>46122.666666666664</v>
+      </c>
+      <c r="B978" s="4">
+        <v>32.526665782928468</v>
+      </c>
+      <c r="C978" s="4">
+        <v>38.973827469348905</v>
+      </c>
+      <c r="D978" s="4">
+        <v>38.547459456539059</v>
+      </c>
+    </row>
+    <row r="979" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A979" s="1">
+        <v>46122.708333333336</v>
+      </c>
+      <c r="B979" s="4">
+        <v>32.531458123524985</v>
+      </c>
+      <c r="C979" s="4">
+        <v>38.967932229571872</v>
+      </c>
+      <c r="D979" s="4">
+        <v>38.588234834649484</v>
+      </c>
+    </row>
+    <row r="980" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A980" s="1">
+        <v>46122.75</v>
+      </c>
+      <c r="B980" s="4">
+        <v>32.460415935516359</v>
+      </c>
+      <c r="C980" s="4">
+        <v>38.902586809794109</v>
+      </c>
+      <c r="D980" s="4">
+        <v>38.512110012967732</v>
+      </c>
+    </row>
+    <row r="981" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A981" s="1">
+        <v>46122.791666666664</v>
+      </c>
+      <c r="B981" s="4">
+        <v>32.374166234334311</v>
+      </c>
+      <c r="C981" s="4">
+        <v>38.802311013236881</v>
+      </c>
+      <c r="D981" s="4">
+        <v>38.409661431602153</v>
+      </c>
+    </row>
+    <row r="982" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A982" s="1">
+        <v>46122.833333333336</v>
+      </c>
+      <c r="B982" s="4">
+        <v>32.30104166666667</v>
+      </c>
+      <c r="C982" s="4">
+        <v>38.681836704980761</v>
+      </c>
+      <c r="D982" s="4">
+        <v>38.302744276958101</v>
+      </c>
+    </row>
+    <row r="983" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A983" s="1">
+        <v>46122.875</v>
+      </c>
+      <c r="B983" s="4">
+        <v>32.250416088104245</v>
+      </c>
+      <c r="C983" s="4">
+        <v>38.628693891608194</v>
+      </c>
+      <c r="D983" s="4">
+        <v>38.219618643709467</v>
+      </c>
+    </row>
+    <row r="984" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A984" s="1">
+        <v>46122.916666666664</v>
+      </c>
+      <c r="B984" s="4">
+        <v>32.179907338354326</v>
+      </c>
+      <c r="C984" s="4">
+        <v>38.545462659752893</v>
+      </c>
+      <c r="D984" s="4">
+        <v>38.167731114326749</v>
+      </c>
+    </row>
+    <row r="985" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A985" s="1">
+        <v>46122.958333333336</v>
+      </c>
+      <c r="B985" s="4">
+        <v>32.132500298817952</v>
+      </c>
+      <c r="C985" s="4">
+        <v>38.460951538085936</v>
+      </c>
+      <c r="D985" s="4">
+        <v>38.081766178026868</v>
+      </c>
+    </row>
+    <row r="986" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A986" s="1">
+        <v>46123</v>
+      </c>
+      <c r="B986" s="4">
+        <v>32.136406918366752</v>
+      </c>
+      <c r="C986" s="4">
+        <v>38.452114725112914</v>
+      </c>
+      <c r="D986" s="4">
+        <v>38.047196423217272</v>
+      </c>
+    </row>
+    <row r="987" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A987" s="1">
+        <v>46123.041666666664</v>
+      </c>
+      <c r="B987" s="4">
+        <v>32.087760841846467</v>
+      </c>
+      <c r="C987" s="4">
+        <v>38.400767542975295</v>
+      </c>
+      <c r="D987" s="4">
+        <v>38.018452564694087</v>
+      </c>
+    </row>
+    <row r="988" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A988" s="1">
+        <v>46123.083333333336</v>
+      </c>
+      <c r="B988" s="4">
+        <v>32.087916851043701</v>
+      </c>
+      <c r="C988" s="4">
+        <v>38.367421032133556</v>
+      </c>
+      <c r="D988" s="4">
+        <v>37.993636280470675</v>
+      </c>
+    </row>
+    <row r="989" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A989" s="1">
+        <v>46123.125</v>
+      </c>
+      <c r="B989" s="4">
+        <v>32.096457513173419</v>
+      </c>
+      <c r="C989" s="4">
+        <v>38.370743595759073</v>
+      </c>
+      <c r="D989" s="4">
+        <v>37.966561615460385</v>
+      </c>
+    </row>
+    <row r="990" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A990" s="1">
+        <v>46123.166666666664</v>
+      </c>
+      <c r="B990" s="4">
+        <v>32.043125295639037</v>
+      </c>
+      <c r="C990" s="4">
+        <v>38.347713727951053</v>
+      </c>
+      <c r="D990" s="4">
+        <v>37.947369821112488</v>
+      </c>
+    </row>
+    <row r="991" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A991" s="1">
+        <v>46123.208333333336</v>
+      </c>
+      <c r="B991" s="4">
+        <v>31.992707697550454</v>
+      </c>
+      <c r="C991" s="4">
+        <v>38.316198088328044</v>
+      </c>
+      <c r="D991" s="4">
+        <v>37.927703060159232</v>
+      </c>
+    </row>
+    <row r="992" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A992" s="1">
+        <v>46123.25</v>
+      </c>
+      <c r="B992" s="4">
+        <v>31.976874287923177</v>
+      </c>
+      <c r="C992" s="4">
+        <v>38.28369219744647</v>
+      </c>
+      <c r="D992" s="4">
+        <v>37.941895411912142</v>
+      </c>
+    </row>
+    <row r="993" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A993" s="1">
+        <v>46123.291666666664</v>
+      </c>
+      <c r="B993" s="4">
+        <v>31.962083228429158</v>
+      </c>
+      <c r="C993" s="4">
+        <v>38.30734952644066</v>
+      </c>
+      <c r="D993" s="4">
+        <v>37.943357123395707</v>
+      </c>
+    </row>
+    <row r="994" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A994" s="1">
+        <v>46123.333333333336</v>
+      </c>
+      <c r="B994" s="4">
+        <v>32.032083352406822</v>
+      </c>
+      <c r="C994" s="4">
+        <v>38.362499650319414</v>
+      </c>
+      <c r="D994" s="4">
+        <v>38.003289070457136</v>
+      </c>
+    </row>
+    <row r="995" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A995" s="1">
+        <v>46123.375</v>
+      </c>
+      <c r="B995" s="4">
+        <v>32.053819041781956</v>
+      </c>
+      <c r="C995" s="4">
+        <v>38.394948196411136</v>
+      </c>
+      <c r="D995" s="4">
+        <v>38.052455470345237</v>
+      </c>
+    </row>
+    <row r="996" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A996" s="1">
+        <v>46123.416666666664</v>
+      </c>
+      <c r="B996" s="4">
+        <v>32.071333218178552</v>
+      </c>
+      <c r="C996" s="4">
+        <v>38.442210222173621</v>
+      </c>
+      <c r="D996" s="4">
+        <v>38.117965132767729</v>
+      </c>
+    </row>
+    <row r="997" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A997" s="1">
+        <v>46123.458333333336</v>
+      </c>
+      <c r="B997" s="4">
+        <v>32.246930227781597</v>
+      </c>
+      <c r="C997" s="4">
+        <v>38.637385725092003</v>
+      </c>
+      <c r="D997" s="4">
+        <v>38.267927670764557</v>
+      </c>
+    </row>
+    <row r="998" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A998" s="1">
+        <v>46123.5</v>
+      </c>
+      <c r="B998" s="4">
+        <v>32.378321153977339</v>
+      </c>
+      <c r="C998" s="4">
+        <v>38.769153976440428</v>
+      </c>
+      <c r="D998" s="4">
+        <v>38.434030961306789</v>
+      </c>
+    </row>
+    <row r="999" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A999" s="1">
+        <v>46123.541666666664</v>
+      </c>
+      <c r="B999" s="4">
+        <v>32.427443012536742</v>
+      </c>
+      <c r="C999" s="4">
+        <v>38.83445853551229</v>
+      </c>
+      <c r="D999" s="4">
+        <v>38.52593643854398</v>
+      </c>
+    </row>
+    <row r="1000" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1000" s="1">
+        <v>46123.583333333336</v>
+      </c>
+      <c r="B1000" s="4">
+        <v>32.422777811686196</v>
+      </c>
+      <c r="C1000" s="4">
+        <v>38.865358859697977</v>
+      </c>
+      <c r="D1000" s="4">
+        <v>38.536803560908631</v>
+      </c>
+    </row>
+    <row r="1001" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1001" s="1">
+        <v>46123.625</v>
+      </c>
+      <c r="B1001" s="4">
+        <v>32.444166056315105</v>
+      </c>
+      <c r="C1001" s="4">
+        <v>38.872960109180873</v>
+      </c>
+      <c r="D1001" s="4">
+        <v>38.535132054670086</v>
+      </c>
+    </row>
+    <row r="1002" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1002" s="1">
+        <v>46123.666666666664</v>
+      </c>
+      <c r="B1002" s="4">
+        <v>32.469768616005226</v>
+      </c>
+      <c r="C1002" s="4">
+        <v>38.903652166437219</v>
+      </c>
+      <c r="D1002" s="4">
+        <v>38.59597270759155</v>
+      </c>
+    </row>
+    <row r="1003" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1003" s="1">
+        <v>46123.708333333336</v>
+      </c>
+      <c r="B1003" s="4">
+        <v>32.425022669191712</v>
+      </c>
+      <c r="C1003" s="4">
+        <v>38.858487194202567</v>
+      </c>
+      <c r="D1003" s="4">
+        <v>38.520458596707165</v>
+      </c>
+    </row>
+    <row r="1004" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1004" s="1">
+        <v>46123.75</v>
+      </c>
+      <c r="B1004" s="4">
+        <v>32.505791912078855</v>
+      </c>
+      <c r="C1004" s="4">
+        <v>38.945867245262441</v>
+      </c>
+      <c r="D1004" s="4">
+        <v>38.56805973919225</v>
+      </c>
+    </row>
+    <row r="1005" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1005" s="1">
+        <v>46123.791666666664</v>
+      </c>
+      <c r="B1005" s="4">
+        <v>32.423583132425946</v>
+      </c>
+      <c r="C1005" s="4">
+        <v>38.836373515858675</v>
+      </c>
+      <c r="D1005" s="4">
+        <v>38.475438226408507</v>
+      </c>
+    </row>
+    <row r="1006" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1006" s="1">
+        <v>46123.833333333336</v>
+      </c>
+      <c r="B1006" s="4">
+        <v>32.37984613117419</v>
+      </c>
+      <c r="C1006" s="4">
+        <v>38.760234419504805</v>
+      </c>
+      <c r="D1006" s="4">
+        <v>38.429762667421535</v>
+      </c>
+    </row>
+    <row r="1007" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1007" s="1">
+        <v>46123.875</v>
+      </c>
+      <c r="B1007" s="4">
+        <v>32.273695147664924</v>
+      </c>
+      <c r="C1007" s="4">
+        <v>38.64557720820109</v>
+      </c>
+      <c r="D1007" s="4">
+        <v>38.333734962008158</v>
+      </c>
+    </row>
+    <row r="1008" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1008" s="1">
+        <v>46123.916666666664</v>
+      </c>
+      <c r="B1008" s="4">
+        <v>32.270584017435709</v>
+      </c>
+      <c r="C1008" s="4">
+        <v>38.618053178619917</v>
+      </c>
+      <c r="D1008" s="4">
+        <v>38.270035013756029</v>
+      </c>
+    </row>
+    <row r="1009" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1009" s="1">
+        <v>46123.958333333336</v>
+      </c>
+      <c r="B1009" s="4">
+        <v>32.256813170115151</v>
+      </c>
+      <c r="C1009" s="4">
+        <v>38.576877321834459</v>
+      </c>
+      <c r="D1009" s="4">
+        <v>38.235918557995184</v>
+      </c>
+    </row>
+    <row r="1010" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1010" s="1">
+        <v>46124</v>
+      </c>
+      <c r="B1010" s="4">
+        <v>32.242812315622963</v>
+      </c>
+      <c r="C1010" s="4">
+        <v>38.570468173556854</v>
+      </c>
+      <c r="D1010" s="4">
+        <v>38.197246530366982</v>
+      </c>
+    </row>
+    <row r="1011" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1011" s="1">
+        <v>46124.041666666664</v>
+      </c>
+      <c r="B1011" s="4">
+        <v>32.180417505900067</v>
+      </c>
+      <c r="C1011" s="4">
+        <v>38.501198120117188</v>
+      </c>
+      <c r="D1011" s="4">
+        <v>38.149427784475733</v>
+      </c>
+    </row>
+    <row r="1012" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1012" s="1">
+        <v>46124.083333333336</v>
+      </c>
+      <c r="B1012" s="4">
+        <v>32.144791825612387</v>
+      </c>
+      <c r="C1012" s="4">
+        <v>38.446771176656085</v>
+      </c>
+      <c r="D1012" s="4">
+        <v>38.128664485310189</v>
+      </c>
+    </row>
+    <row r="1013" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1013" s="1">
+        <v>46124.125</v>
+      </c>
+      <c r="B1013" s="4">
+        <v>32.13355878723992</v>
+      </c>
+      <c r="C1013" s="4">
+        <v>38.43973939683702</v>
+      </c>
+      <c r="D1013" s="4">
+        <v>38.110470382511963</v>
+      </c>
+    </row>
+    <row r="1014" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1014" s="1">
+        <v>46124.166666666664</v>
+      </c>
+      <c r="B1014" s="4">
+        <v>32.120189661449857</v>
+      </c>
+      <c r="C1014" s="4">
+        <v>38.427335641464751</v>
+      </c>
+      <c r="D1014" s="4">
+        <v>38.117724107078644</v>
+      </c>
+    </row>
+    <row r="1015" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1015" s="1">
+        <v>46124.208333333336</v>
+      </c>
+      <c r="B1015" s="4">
+        <v>32.119523859659829</v>
+      </c>
+      <c r="C1015" s="4">
+        <v>38.45396858021833</v>
+      </c>
+      <c r="D1015" s="4">
+        <v>38.128289272919204</v>
+      </c>
+    </row>
+    <row r="1016" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1016" s="1">
+        <v>46124.25</v>
+      </c>
+      <c r="B1016" s="4">
+        <v>32.139225847880049</v>
+      </c>
+      <c r="C1016" s="4">
+        <v>38.448159768846303</v>
+      </c>
+      <c r="D1016" s="4">
+        <v>38.141213483561749</v>
+      </c>
+    </row>
+    <row r="1017" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1017" s="1">
+        <v>46124.291666666664</v>
+      </c>
+      <c r="B1017" s="4">
+        <v>32.143852778194713</v>
+      </c>
+      <c r="C1017" s="4">
+        <v>38.321866652700635</v>
+      </c>
+      <c r="D1017" s="4">
+        <v>38.154894341565814</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1018" s="1">
+        <v>46124.333333333336</v>
+      </c>
+      <c r="B1018" s="4">
+        <v>32.136461158674585</v>
+      </c>
+      <c r="C1018" s="4">
+        <v>36.83425348864661</v>
+      </c>
+      <c r="D1018" s="4">
+        <v>36.745514411783162</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1019" s="1">
+        <v>46124.375</v>
+      </c>
+      <c r="B1019" s="4">
+        <v>32.192813142140707</v>
+      </c>
+      <c r="C1019" s="4">
+        <v>37.879627121819389</v>
+      </c>
+      <c r="D1019" s="4">
+        <v>37.295784947678619</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1020" s="1">
+        <v>46124.416666666664</v>
+      </c>
+      <c r="B1020" s="4">
+        <v>32.304375425974527</v>
+      </c>
+      <c r="C1020" s="4">
+        <v>38.650313504536946</v>
+      </c>
+      <c r="D1020" s="4">
+        <v>38.342265323264726</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1021" s="1">
+        <v>46124.458333333336</v>
+      </c>
+      <c r="B1021" s="4">
+        <v>32.37645727793376</v>
+      </c>
+      <c r="C1021" s="4">
+        <v>38.726700464884438</v>
+      </c>
+      <c r="D1021" s="4">
+        <v>38.459672025278763</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1022" s="1">
+        <v>46124.5</v>
+      </c>
+      <c r="B1022" s="4">
+        <v>32.473749732971193</v>
+      </c>
+      <c r="C1022" s="4">
+        <v>38.851152210904836</v>
+      </c>
+      <c r="D1022" s="4">
+        <v>38.585424407379946</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1023" s="1">
+        <v>46124.541666666664</v>
+      </c>
+      <c r="B1023" s="4">
+        <v>32.562291804949446</v>
+      </c>
+      <c r="C1023" s="4">
+        <v>38.940070533991459</v>
+      </c>
+      <c r="D1023" s="4">
+        <v>38.654203240563433</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1024" s="1">
+        <v>46124.583333333336</v>
+      </c>
+      <c r="B1024" s="4">
+        <v>32.627916089693706</v>
+      </c>
+      <c r="C1024" s="4">
+        <v>39.041086024329772</v>
+      </c>
+      <c r="D1024" s="4">
+        <v>38.751359173670934</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1025" s="1">
+        <v>46124.625</v>
+      </c>
+      <c r="B1025" s="4">
+        <v>32.746042315165205</v>
+      </c>
+      <c r="C1025" s="4">
+        <v>39.159849749008814</v>
+      </c>
+      <c r="D1025" s="4">
+        <v>38.886181937378488</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1026" s="1">
+        <v>46124.666666666664</v>
+      </c>
+      <c r="B1026" s="4">
+        <v>32.785536361875991</v>
+      </c>
+      <c r="C1026" s="4">
+        <v>39.212954420418967</v>
+      </c>
+      <c r="D1026" s="4">
+        <v>38.978481861975744</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1027" s="1">
+        <v>46124.708333333336</v>
+      </c>
+      <c r="B1027" s="4">
+        <v>32.730772949400404</v>
+      </c>
+      <c r="C1027" s="4">
+        <v>39.170497349330361</v>
+      </c>
+      <c r="D1027" s="4">
+        <v>38.9291622735361</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1028" s="1">
+        <v>46124.75</v>
+      </c>
+      <c r="B1028" s="4">
+        <v>32.76556642623175</v>
+      </c>
+      <c r="C1028" s="4">
+        <v>39.20672375361125</v>
+      </c>
+      <c r="D1028" s="4">
+        <v>38.925979928777018</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1029" s="1">
+        <v>46124.791666666664</v>
+      </c>
+      <c r="B1029" s="4">
+        <v>32.745209089914958</v>
+      </c>
+      <c r="C1029" s="4">
+        <v>39.171734727223715</v>
+      </c>
+      <c r="D1029" s="4">
+        <v>38.871093748185714</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1030" s="1">
+        <v>46124.833333333336</v>
+      </c>
+      <c r="B1030" s="4">
+        <v>32.604375251134236</v>
+      </c>
+      <c r="C1030" s="4">
+        <v>39.00856954574585</v>
+      </c>
+      <c r="D1030" s="4">
+        <v>38.714749977445265</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1031" s="1">
+        <v>46124.875</v>
+      </c>
+      <c r="B1031" s="4">
+        <v>32.52791660626729</v>
+      </c>
+      <c r="C1031" s="4">
+        <v>38.926956180289942</v>
+      </c>
+      <c r="D1031" s="4">
+        <v>38.641346111280768</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1032" s="1">
+        <v>46124.916666666664</v>
+      </c>
+      <c r="B1032" s="4">
+        <v>32.464166736602785</v>
+      </c>
+      <c r="C1032" s="4">
+        <v>38.819942601521817</v>
+      </c>
+      <c r="D1032" s="4">
+        <v>38.564273148086038</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1033" s="1">
+        <v>46124.958333333336</v>
+      </c>
+      <c r="B1033" s="4">
+        <v>32.432306970196002</v>
+      </c>
+      <c r="C1033" s="4">
+        <v>38.757489664996108</v>
+      </c>
+      <c r="D1033" s="4">
+        <v>38.489476763356215</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1034" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B1034" s="4">
+        <v>32.372068360411092</v>
+      </c>
+      <c r="C1034" s="4">
+        <v>38.672582013871931</v>
+      </c>
+      <c r="D1034" s="4">
+        <v>38.422326163958019</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1035" s="1">
+        <v>46125.041666666664</v>
+      </c>
+      <c r="B1035" s="4">
+        <v>32.327362092336017</v>
+      </c>
+      <c r="C1035" s="4">
+        <v>38.614053175184459</v>
+      </c>
+      <c r="D1035" s="4">
+        <v>38.354643747918793</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1036" s="1">
+        <v>46125.083333333336</v>
+      </c>
+      <c r="B1036" s="4">
+        <v>32.294305790795221</v>
+      </c>
+      <c r="C1036" s="4">
+        <v>38.565138965182832</v>
+      </c>
+      <c r="D1036" s="4">
+        <v>38.312623434257596</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1037" s="1">
+        <v>46125.125</v>
+      </c>
+      <c r="B1037" s="4">
+        <v>32.262106404481109</v>
+      </c>
+      <c r="C1037" s="4">
+        <v>38.527283130751712</v>
+      </c>
+      <c r="D1037" s="4">
+        <v>38.286691793059823</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1038" s="1">
+        <v>46125.166666666664</v>
+      </c>
+      <c r="B1038" s="4">
+        <v>32.272615630538375</v>
+      </c>
+      <c r="C1038" s="4">
+        <v>38.566057302157084</v>
+      </c>
+      <c r="D1038" s="4">
+        <v>38.285870456996633</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1039" s="1">
+        <v>46125.208333333336</v>
+      </c>
+      <c r="B1039" s="4">
+        <v>32.292309993284718</v>
+      </c>
+      <c r="C1039" s="4">
+        <v>38.572179747687443</v>
+      </c>
+      <c r="D1039" s="4">
+        <v>38.278279370658332</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1040" s="1">
+        <v>46125.25</v>
+      </c>
+      <c r="B1040" s="4">
+        <v>32.340468509991965</v>
+      </c>
+      <c r="C1040" s="4">
+        <v>38.625344948709746</v>
+      </c>
+      <c r="D1040" s="4">
+        <v>38.332904144682921</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1041" s="1">
+        <v>46125.291666666664</v>
+      </c>
+      <c r="B1041" s="4">
+        <v>32.375207901000977</v>
+      </c>
+      <c r="C1041" s="4">
+        <v>38.663838720910348</v>
+      </c>
+      <c r="D1041" s="4">
+        <v>38.376469126156699</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1042" s="1">
+        <v>46125.333333333336</v>
+      </c>
+      <c r="B1042" s="4">
+        <v>32.37520850499471</v>
+      </c>
+      <c r="C1042" s="4">
+        <v>38.679128021106386</v>
+      </c>
+      <c r="D1042" s="4">
+        <v>38.418054125043788</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1043" s="1">
+        <v>46125.375</v>
+      </c>
+      <c r="B1043" s="4">
+        <v>32.376249927944606</v>
+      </c>
+      <c r="C1043" s="4">
+        <v>38.685559453462297</v>
+      </c>
+      <c r="D1043" s="4">
+        <v>38.414419644291563</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1044" s="1">
+        <v>46125.416666666664</v>
+      </c>
+      <c r="B1044" s="4">
+        <v>32.417833718193904</v>
+      </c>
+      <c r="C1044" s="4">
+        <v>38.721432789166769</v>
+      </c>
+      <c r="D1044" s="4">
+        <v>38.471306716288836</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1045" s="1">
+        <v>46125.458333333336</v>
+      </c>
+      <c r="B1045" s="4">
+        <v>32.478068269093832</v>
+      </c>
+      <c r="C1045" s="4">
+        <v>38.775272284235278</v>
+      </c>
+      <c r="D1045" s="4">
+        <v>38.516134278652025</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1046" s="1">
+        <v>46125.5</v>
+      </c>
+      <c r="B1046" s="4">
+        <v>32.550555928548178</v>
+      </c>
+      <c r="C1046" s="4">
+        <v>38.86585559511942</v>
+      </c>
+      <c r="D1046" s="4">
+        <v>38.619649495611917</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1047" s="1">
+        <v>46125.541666666664</v>
+      </c>
+      <c r="B1047" s="4">
+        <v>32.593105766989964</v>
+      </c>
+      <c r="C1047" s="4">
+        <v>38.925218874613442</v>
+      </c>
+      <c r="D1047" s="4">
+        <v>38.696874132858802</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1048" s="1">
+        <v>46125.583333333336</v>
+      </c>
+      <c r="B1048" s="4">
+        <v>32.663143819751163</v>
+      </c>
+      <c r="C1048" s="4">
+        <v>39.024323018391925</v>
+      </c>
+      <c r="D1048" s="4">
+        <v>38.79291834326915</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1049" s="1">
+        <v>46125.625</v>
+      </c>
+      <c r="B1049" s="4">
+        <v>32.798694523997689</v>
+      </c>
+      <c r="C1049" s="4">
+        <v>39.180659410688612</v>
+      </c>
+      <c r="D1049" s="4">
+        <v>38.913544732095133</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1050" s="1">
+        <v>46125.666666666664</v>
+      </c>
+      <c r="B1050" s="4">
+        <v>32.849225226215928</v>
+      </c>
+      <c r="C1050" s="4">
+        <v>39.265540333588916</v>
+      </c>
+      <c r="D1050" s="4">
+        <v>39.006395783357213</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1051" s="1">
+        <v>46125.708333333336</v>
+      </c>
+      <c r="B1051" s="4">
+        <v>32.826250807444254</v>
+      </c>
+      <c r="C1051" s="4">
+        <v>39.248332046137918</v>
+      </c>
+      <c r="D1051" s="4">
+        <v>39.01062838499044</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1052" s="1">
+        <v>46125.75</v>
+      </c>
+      <c r="B1052" s="4">
+        <v>32.815383455488416</v>
+      </c>
+      <c r="C1052" s="4">
+        <v>39.247204600440128</v>
+      </c>
+      <c r="D1052" s="4">
+        <v>38.843033133256618</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1053" s="1">
+        <v>46125.791666666664</v>
+      </c>
+      <c r="B1053" s="4">
+        <v>32.751076592339409</v>
+      </c>
+      <c r="C1053" s="4">
+        <v>39.166801753119813</v>
+      </c>
+      <c r="D1053" s="4">
+        <v>38.807241316340082</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1054" s="1">
+        <v>46125.833333333336</v>
+      </c>
+      <c r="B1054" s="4">
+        <v>32.656469891741388</v>
+      </c>
+      <c r="C1054" s="4">
+        <v>39.065316111700881</v>
+      </c>
+      <c r="D1054" s="4">
+        <v>38.728903849120577</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1055" s="1">
+        <v>46125.875</v>
+      </c>
+      <c r="B1055" s="4">
+        <v>32.605821115830366</v>
+      </c>
+      <c r="C1055" s="4">
+        <v>38.995782057444252</v>
+      </c>
+      <c r="D1055" s="4">
+        <v>38.64686586025978</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1056" s="1">
+        <v>46125.916666666664</v>
+      </c>
+      <c r="B1056" s="4">
+        <v>32.549166742960615</v>
+      </c>
+      <c r="C1056" s="4">
+        <v>38.900060733159386</v>
+      </c>
+      <c r="D1056" s="4">
+        <v>38.624286362170324</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1057" s="1">
+        <v>46125.958333333336</v>
+      </c>
+      <c r="B1057" s="4">
+        <v>32.484790738423662</v>
+      </c>
+      <c r="C1057" s="4">
+        <v>38.83158325719404</v>
+      </c>
+      <c r="D1057" s="4">
+        <v>38.598438007979212</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1058" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B1058" s="4">
+        <v>32.462915833791094</v>
+      </c>
+      <c r="C1058" s="4">
+        <v>38.770548460661246</v>
+      </c>
+      <c r="D1058" s="4">
+        <v>38.542563685306554</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1059" s="1">
+        <v>46126.041666666664</v>
+      </c>
+      <c r="B1059" s="4">
+        <v>32.460833549499512</v>
+      </c>
+      <c r="C1059" s="4">
+        <v>38.773119781956531</v>
+      </c>
+      <c r="D1059" s="4">
+        <v>38.508800702757306</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1060" s="1">
+        <v>46126.083333333336</v>
+      </c>
+      <c r="B1060" s="4">
+        <v>32.476563119888304</v>
+      </c>
+      <c r="C1060" s="4">
+        <v>38.77138876385159</v>
+      </c>
+      <c r="D1060" s="4">
+        <v>38.496152745848313</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1061" s="1">
+        <v>46126.125</v>
+      </c>
+      <c r="B1061" s="4">
+        <v>32.430938164393105</v>
+      </c>
+      <c r="C1061" s="4">
+        <v>38.705486732059057</v>
+      </c>
+      <c r="D1061" s="4">
+        <v>38.475215656791711</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1062" s="1">
+        <v>46126.166666666664</v>
+      </c>
+      <c r="B1062" s="4">
+        <v>32.404999732971191</v>
+      </c>
+      <c r="C1062" s="4">
+        <v>38.690224779569185</v>
+      </c>
+      <c r="D1062" s="4">
+        <v>38.454159681143082</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1063" s="1">
+        <v>46126.208333333336</v>
+      </c>
+      <c r="B1063" s="4">
+        <v>32.37729075749715</v>
+      </c>
+      <c r="C1063" s="4">
+        <v>38.68265143364583</v>
+      </c>
+      <c r="D1063" s="4">
+        <v>38.438865808563975</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1064" s="1">
+        <v>46126.25</v>
+      </c>
+      <c r="B1064" s="4">
+        <v>32.364821315947033</v>
+      </c>
+      <c r="C1064" s="4">
+        <v>38.685526886692749</v>
+      </c>
+      <c r="D1064" s="4">
+        <v>38.433936536156033</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1065" s="1">
+        <v>46126.291666666664</v>
+      </c>
+      <c r="B1065" s="4">
+        <v>32.356427437918526</v>
+      </c>
+      <c r="C1065" s="4">
+        <v>38.68102422820197</v>
+      </c>
+      <c r="D1065" s="4">
+        <v>38.429273916945583</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1066" s="1">
+        <v>46126.333333333336</v>
+      </c>
+      <c r="B1066" s="4">
+        <v>32.360154843330385</v>
+      </c>
+      <c r="C1066" s="4">
+        <v>38.687934509913127</v>
+      </c>
+      <c r="D1066" s="4">
+        <v>38.449221042269926</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1067" s="1">
+        <v>46126.375</v>
+      </c>
+      <c r="B1067" s="4">
+        <v>32.448831893148878</v>
+      </c>
+      <c r="C1067" s="4">
+        <v>38.745094822614618</v>
+      </c>
+      <c r="D1067" s="4">
+        <v>38.499222702179608</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1068" s="1">
+        <v>46126.416666666664</v>
+      </c>
+      <c r="B1068" s="4">
+        <v>32.522678445634391</v>
+      </c>
+      <c r="C1068" s="4">
+        <v>38.828950835496954</v>
+      </c>
+      <c r="D1068" s="4">
+        <v>38.567113580827609</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1069" s="1">
+        <v>46126.458333333336</v>
+      </c>
+      <c r="B1069" s="4">
+        <v>32.597708495457965</v>
+      </c>
+      <c r="C1069" s="4">
+        <v>38.918125351270042</v>
+      </c>
+      <c r="D1069" s="4">
+        <v>38.6909379343032</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1070" s="1">
+        <v>46126.5</v>
+      </c>
+      <c r="B1070" s="4">
+        <v>32.644148641392803</v>
+      </c>
+      <c r="C1070" s="4">
+        <v>38.987422005335489</v>
+      </c>
+      <c r="D1070" s="4">
+        <v>38.782169685854946</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1071" s="1">
+        <v>46126.541666666664</v>
+      </c>
+      <c r="B1071" s="4">
+        <v>32.691476593846858</v>
+      </c>
+      <c r="C1071" s="4">
+        <v>39.04294272263845</v>
+      </c>
+      <c r="D1071" s="4">
+        <v>38.842671745285102</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1072" s="1">
+        <v>46126.583333333336</v>
+      </c>
+      <c r="B1072" s="4">
+        <v>32.816736369662813</v>
+      </c>
+      <c r="C1072" s="4">
+        <v>39.177404507346779</v>
+      </c>
+      <c r="D1072" s="4">
+        <v>38.914040704994385</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1073" s="1">
+        <v>46126.625</v>
+      </c>
+      <c r="B1073" s="4">
+        <v>32.940823302193294</v>
+      </c>
+      <c r="C1073" s="4">
+        <v>39.308248019402726</v>
+      </c>
+      <c r="D1073" s="4">
+        <v>39.053120269424724</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1074" s="1">
+        <v>46126.666666666664</v>
+      </c>
+      <c r="B1074" s="4">
+        <v>32.893644550363852</v>
+      </c>
+      <c r="C1074" s="4">
+        <v>39.298496658007302</v>
+      </c>
+      <c r="D1074" s="4">
+        <v>39.055772812077429</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1075" s="1">
+        <v>46126.708333333336</v>
+      </c>
+      <c r="B1075" s="4">
+        <v>32.823164897384466</v>
+      </c>
+      <c r="C1075" s="4">
+        <v>39.220521252950036</v>
+      </c>
+      <c r="D1075" s="4">
+        <v>38.997587842786281</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1076" s="1">
+        <v>46126.75</v>
+      </c>
+      <c r="B1076" s="4">
+        <v>32.784386374694961</v>
+      </c>
+      <c r="C1076" s="4">
+        <v>39.193280982971189</v>
+      </c>
+      <c r="D1076" s="4">
+        <v>38.954044550123669</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1077" s="1">
+        <v>46126.791666666664</v>
+      </c>
+      <c r="B1077" s="4">
+        <v>32.763538868086677</v>
+      </c>
+      <c r="C1077" s="4">
+        <v>39.158579186030799</v>
+      </c>
+      <c r="D1077" s="4">
+        <v>38.938601301201203</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1078" s="1">
+        <v>46126.833333333336</v>
+      </c>
+      <c r="B1078" s="4">
+        <v>32.690557882899327</v>
+      </c>
+      <c r="C1078" s="4">
+        <v>39.109546204975672</v>
+      </c>
+      <c r="D1078" s="4">
+        <v>38.89694361373445</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1079" s="1">
+        <v>46126.875</v>
+      </c>
+      <c r="B1079" s="4">
+        <v>32.65985791910262</v>
+      </c>
+      <c r="C1079" s="4">
+        <v>39.072708209355675</v>
+      </c>
+      <c r="D1079" s="4">
+        <v>38.84995993549893</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1080" s="1">
+        <v>46126.916666666664</v>
+      </c>
+      <c r="B1080" s="4">
+        <v>32.608124319712324</v>
+      </c>
+      <c r="C1080" s="4">
+        <v>38.978125508626299</v>
+      </c>
+      <c r="D1080" s="4">
+        <v>38.777325144507536</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1081" s="1">
+        <v>46126.958333333336</v>
+      </c>
+      <c r="B1081" s="4">
+        <v>32.544166866938276</v>
+      </c>
+      <c r="C1081" s="4">
+        <v>38.901503172374909</v>
+      </c>
+      <c r="D1081" s="4">
+        <v>38.688702221497699</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1082" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B1082" s="4">
+        <v>32.532291666666666</v>
+      </c>
+      <c r="C1082" s="4">
+        <v>38.847038357598436</v>
+      </c>
+      <c r="D1082" s="4">
+        <v>38.650288500182327</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1083" s="1">
+        <v>46127.041666666664</v>
+      </c>
+      <c r="B1083" s="4">
+        <v>32.533819802602132</v>
+      </c>
+      <c r="C1083" s="4">
+        <v>38.86081657233062</v>
+      </c>
+      <c r="D1083" s="4">
+        <v>38.667454251491279</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1084" s="1">
+        <v>46127.083333333336</v>
+      </c>
+      <c r="B1084" s="4">
+        <v>32.549642814908708</v>
+      </c>
+      <c r="C1084" s="4">
+        <v>38.85818513266566</v>
+      </c>
+      <c r="D1084" s="4">
+        <v>38.652786957851092</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1085" s="1">
+        <v>46127.125</v>
+      </c>
+      <c r="B1085" s="4">
+        <v>32.568163139706563</v>
+      </c>
+      <c r="C1085" s="4">
+        <v>38.844326088283999</v>
+      </c>
+      <c r="D1085" s="4">
+        <v>38.61692972452245</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1086" s="1">
+        <v>46127.166666666664</v>
+      </c>
+      <c r="B1086" s="4">
+        <v>32.578438914861437</v>
+      </c>
+      <c r="C1086" s="4">
+        <v>38.859737926568741</v>
+      </c>
+      <c r="D1086" s="4">
+        <v>38.607206053339056</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1087" s="1">
+        <v>46127.208333333336</v>
+      </c>
+      <c r="B1087" s="4">
+        <v>32.525143836094784</v>
+      </c>
+      <c r="C1087" s="4">
+        <v>38.831979796301319</v>
+      </c>
+      <c r="D1087" s="4">
+        <v>38.609231623539003</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1088" s="1">
+        <v>46127.25</v>
+      </c>
+      <c r="B1088" s="4">
+        <v>32.502291329701741</v>
+      </c>
+      <c r="C1088" s="4">
+        <v>38.82578911100115</v>
+      </c>
+      <c r="D1088" s="4">
+        <v>38.600245396290426</v>
+      </c>
+    </row>
+    <row r="1089" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1089" s="1">
+        <v>46127.291666666664</v>
+      </c>
+      <c r="B1089" s="4">
+        <v>32.490069601270889</v>
+      </c>
+      <c r="C1089" s="4">
+        <v>38.819531504313154</v>
+      </c>
+      <c r="D1089" s="4">
+        <v>38.57854170320357</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1090" s="1">
+        <v>46127.333333333336</v>
+      </c>
+      <c r="B1090" s="4">
+        <v>32.50085660616557</v>
+      </c>
+      <c r="C1090" s="4">
+        <v>38.827441875139876</v>
+      </c>
+      <c r="D1090" s="4">
+        <v>38.601968752799223</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1091" s="1">
+        <v>46127.375</v>
+      </c>
+      <c r="B1091" s="4">
+        <v>32.523865228229099</v>
+      </c>
+      <c r="C1091" s="4">
+        <v>38.857558035850523</v>
+      </c>
+      <c r="D1091" s="4">
+        <v>38.640834128862998</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1092" s="1">
+        <v>46127.416666666664</v>
+      </c>
+      <c r="B1092" s="4">
+        <v>32.535916909111869</v>
+      </c>
+      <c r="C1092" s="4">
+        <v>38.855885092417402</v>
+      </c>
+      <c r="D1092" s="4">
+        <v>38.686027747498585</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1093" s="1">
+        <v>46127.458333333336</v>
+      </c>
+      <c r="B1093" s="4">
+        <v>32.66033383687337</v>
+      </c>
+      <c r="C1093" s="4">
+        <v>38.982014078564113</v>
+      </c>
+      <c r="D1093" s="4">
+        <v>38.772193601488695</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1094" s="1">
+        <v>46127.5</v>
+      </c>
+      <c r="B1094" s="4">
+        <v>32.766569479774027</v>
+      </c>
+      <c r="C1094" s="4">
+        <v>39.108606326681937</v>
+      </c>
+      <c r="D1094" s="4">
+        <v>38.902894377806618</v>
+      </c>
+    </row>
+    <row r="1095" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1095" s="1">
+        <v>46127.541666666664</v>
+      </c>
+      <c r="B1095" s="4">
+        <v>32.772777587559375</v>
+      </c>
+      <c r="C1095" s="4">
+        <v>39.117195790964402</v>
+      </c>
+      <c r="D1095" s="4">
+        <v>38.92229899986252</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1096" s="1">
+        <v>46127.583333333336</v>
+      </c>
+      <c r="B1096" s="4">
+        <v>32.885238656543549</v>
+      </c>
+      <c r="C1096" s="4">
+        <v>39.221401778134435</v>
+      </c>
+      <c r="D1096" s="4">
+        <v>38.989455852896029</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1097" s="1">
+        <v>46127.625</v>
+      </c>
+      <c r="B1097" s="4">
+        <v>32.98613048735119</v>
+      </c>
+      <c r="C1097" s="4">
+        <v>39.360051790873207</v>
+      </c>
+      <c r="D1097" s="4">
+        <v>39.09672846111431</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1098" s="1">
+        <v>46127.666666666664</v>
+      </c>
+      <c r="B1098" s="4">
+        <v>32.955743285587857</v>
+      </c>
+      <c r="C1098" s="4">
+        <v>39.326495116097583</v>
+      </c>
+      <c r="D1098" s="4">
+        <v>39.092227209819946</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1099" s="1">
+        <v>46127.708333333336</v>
+      </c>
+      <c r="B1099" s="4">
+        <v>32.897166366577146</v>
+      </c>
+      <c r="C1099" s="4">
+        <v>39.268618600027906</v>
+      </c>
+      <c r="D1099" s="4">
+        <v>39.029343373110883</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1100" s="1">
+        <v>46127.75</v>
+      </c>
+      <c r="B1100" s="4">
+        <v>32.848976342983732</v>
+      </c>
+      <c r="C1100" s="4">
+        <v>39.250805559158323</v>
+      </c>
+      <c r="D1100" s="4">
+        <v>39.00661950172352</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1101" s="1">
+        <v>46127.791666666664</v>
+      </c>
+      <c r="B1101" s="4">
+        <v>32.783142264669131</v>
+      </c>
+      <c r="C1101" s="4">
+        <v>39.20338086400713</v>
+      </c>
+      <c r="D1101" s="4">
+        <v>38.973175154485695</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1102" s="1">
+        <v>46127.833333333336</v>
+      </c>
+      <c r="B1102" s="4">
+        <v>32.76758102591014</v>
+      </c>
+      <c r="C1102" s="4">
+        <v>39.174032361166823</v>
+      </c>
+      <c r="D1102" s="4">
+        <v>38.937505997487499</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1103" s="1">
+        <v>46127.875</v>
+      </c>
+      <c r="B1103" s="4">
+        <v>32.725844354982726</v>
+      </c>
+      <c r="C1103" s="4">
+        <v>39.115260086059571</v>
+      </c>
+      <c r="D1103" s="4">
+        <v>38.864541644499923</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1104" s="1">
+        <v>46127.916666666664</v>
+      </c>
+      <c r="B1104" s="4">
+        <v>32.634502322585497</v>
+      </c>
+      <c r="C1104" s="4">
+        <v>38.996614462534588</v>
+      </c>
+      <c r="D1104" s="4">
+        <v>38.765043650015599</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1105" s="1">
+        <v>46127.958333333336</v>
+      </c>
+      <c r="B1105" s="4">
+        <v>32.602715896573201</v>
+      </c>
+      <c r="C1105" s="4">
+        <v>38.948398470878601</v>
+      </c>
+      <c r="D1105" s="4">
+        <v>38.700821379638327</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1106" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1106" s="4">
+        <v>32.524656329435459</v>
+      </c>
+      <c r="C1106" s="4">
+        <v>38.873007798194884</v>
+      </c>
+      <c r="D1106" s="4">
+        <v>38.631583245044489</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1107" s="1">
+        <v>46128.041666666664</v>
+      </c>
+      <c r="B1107" s="4">
+        <v>32.495625082651777</v>
+      </c>
+      <c r="C1107" s="4">
+        <v>38.821781326293944</v>
+      </c>
+      <c r="D1107" s="4">
+        <v>38.59523625287185</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1108" s="1">
+        <v>46128.083333333336</v>
+      </c>
+      <c r="B1108" s="4">
+        <v>32.447499561309812</v>
+      </c>
+      <c r="C1108" s="4">
+        <v>38.780484619776409</v>
+      </c>
+      <c r="D1108" s="4">
+        <v>38.557552802962384</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1109" s="1">
+        <v>46128.125</v>
+      </c>
+      <c r="B1109" s="4">
+        <v>32.428791637420652</v>
+      </c>
+      <c r="C1109" s="4">
+        <v>38.741484181086221</v>
+      </c>
+      <c r="D1109" s="4">
+        <v>38.505324557425901</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1110" s="1">
+        <v>46128.166666666664</v>
+      </c>
+      <c r="B1110" s="4">
+        <v>32.426625169118246</v>
+      </c>
+      <c r="C1110" s="4">
+        <v>38.731770928700762</v>
+      </c>
+      <c r="D1110" s="4">
+        <v>38.474673323304287</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1111" s="1">
+        <v>46128.208333333336</v>
+      </c>
+      <c r="B1111" s="4">
+        <v>32.415208276112871</v>
+      </c>
+      <c r="C1111" s="4">
+        <v>38.732916736602782</v>
+      </c>
+      <c r="D1111" s="4">
+        <v>38.458775219536427</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1112" s="1">
+        <v>46128.25</v>
+      </c>
+      <c r="B1112" s="4">
+        <v>32.386198854446413</v>
+      </c>
+      <c r="C1112" s="4">
+        <v>38.721041949590045</v>
+      </c>
+      <c r="D1112" s="4">
+        <v>38.46354132875566</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1113" s="1">
+        <v>46128.291666666664</v>
+      </c>
+      <c r="B1113" s="4">
+        <v>32.355808329163935</v>
+      </c>
+      <c r="C1113" s="4">
+        <v>38.727941604760979</v>
+      </c>
+      <c r="D1113" s="4">
+        <v>38.491314891989575</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1114" s="1">
+        <v>46128.333333333336</v>
+      </c>
+      <c r="B1114" s="4">
+        <v>32.359139101128832</v>
+      </c>
+      <c r="C1114" s="4">
+        <v>38.724646087181874</v>
+      </c>
+      <c r="D1114" s="4">
+        <v>38.524742138551844</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1115" s="1">
+        <v>46128.375</v>
+      </c>
+      <c r="B1115" s="4">
+        <v>32.423031392013819</v>
+      </c>
+      <c r="C1115" s="4">
+        <v>38.803166946386675</v>
+      </c>
+      <c r="D1115" s="4">
+        <v>38.672411088435673</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1116" s="1">
+        <v>46128.416666666664</v>
+      </c>
+      <c r="B1116" s="4">
+        <v>32.435960622977099</v>
+      </c>
+      <c r="C1116" s="4">
+        <v>38.837893080100038</v>
+      </c>
+      <c r="D1116" s="4">
+        <v>38.901453505859664</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1117" s="1">
+        <v>46128.458333333336</v>
+      </c>
+      <c r="B1117" s="4">
+        <v>32.461874654557967</v>
+      </c>
+      <c r="C1117" s="4">
+        <v>38.844083601633706</v>
+      </c>
+      <c r="D1117" s="4">
+        <v>38.963039422718168</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1118" s="1">
+        <v>46128.5</v>
+      </c>
+      <c r="B1118" s="4">
+        <v>32.563402281867134</v>
+      </c>
+      <c r="C1118" s="4">
+        <v>38.891672159830726</v>
+      </c>
+      <c r="D1118" s="4">
+        <v>38.777052142355174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
